--- a/docs/BD_DD_updated.xlsx
+++ b/docs/BD_DD_updated.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lemyvinh/Projects/ECommerce/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14AB7BE-F3EB-9C40-88A6-43547C3FD49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{779C0128-48DA-D742-99BF-E9E60AEFBEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BD - Basic Design" sheetId="1" r:id="rId1"/>
     <sheet name="DD - Detail Design" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="1395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="1395">
   <si>
     <t>DOCUMENT 2: BASIC DESIGN (BD) — TECHHUB E-COMMERCE PLATFORM</t>
   </si>
@@ -4691,13 +4692,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4706,29 +4700,36 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5003,7 +5004,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="2" max="2" width="19.1640625" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5015,53 +5016,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -5070,18 +5071,18 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -5090,18 +5091,18 @@
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -5110,18 +5111,18 @@
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -5130,18 +5131,18 @@
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -5150,18 +5151,18 @@
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -5170,18 +5171,18 @@
       <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -5190,18 +5191,18 @@
       <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
@@ -5210,18 +5211,18 @@
       <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
@@ -5230,18 +5231,18 @@
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -5250,18 +5251,18 @@
       <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
@@ -5270,18 +5271,18 @@
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
@@ -5290,18 +5291,18 @@
       <c r="B16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
@@ -5310,18 +5311,18 @@
       <c r="B17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
@@ -5330,18 +5331,18 @@
       <c r="B18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
@@ -5350,18 +5351,18 @@
       <c r="B19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
     </row>
     <row r="20" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
@@ -5370,18 +5371,18 @@
       <c r="B20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
@@ -5390,38 +5391,38 @@
       <c r="B21" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-    </row>
-    <row r="22" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+    </row>
+    <row r="22" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
     </row>
     <row r="23" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
@@ -5430,196 +5431,196 @@
       <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
     </row>
     <row r="28" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
     </row>
     <row r="29" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
     </row>
     <row r="34" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
     </row>
     <row r="36" spans="1:12" ht="149.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="37" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6346,20 +6347,20 @@
     </row>
     <row r="56" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="57" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
-      <c r="J57" s="30"/>
-      <c r="K57" s="30"/>
-      <c r="L57" s="30"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="33"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="33"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="33"/>
     </row>
     <row r="58" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="18" t="s">
@@ -6449,7 +6450,9 @@
       <c r="A62" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="B62" s="2"/>
+      <c r="B62" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="C62" s="2" t="s">
         <v>196</v>
       </c>
@@ -6637,56 +6640,56 @@
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="35" t="s">
+      <c r="A74" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
-      <c r="J74" s="30"/>
-      <c r="K74" s="30"/>
-      <c r="L74" s="30"/>
+      <c r="B74" s="33"/>
+      <c r="C74" s="33"/>
+      <c r="D74" s="33"/>
+      <c r="E74" s="33"/>
+      <c r="F74" s="33"/>
+      <c r="G74" s="33"/>
+      <c r="H74" s="33"/>
+      <c r="I74" s="33"/>
+      <c r="J74" s="33"/>
+      <c r="K74" s="33"/>
+      <c r="L74" s="33"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B75" s="32" t="s">
+      <c r="B75" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="C75" s="33"/>
-      <c r="D75" s="33"/>
-      <c r="E75" s="33"/>
-      <c r="F75" s="33"/>
-      <c r="G75" s="33"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="33"/>
-      <c r="J75" s="33"/>
-      <c r="K75" s="33"/>
-      <c r="L75" s="34"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
+      <c r="J75" s="30"/>
+      <c r="K75" s="30"/>
+      <c r="L75" s="31"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B76" s="39" t="s">
+      <c r="B76" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="C76" s="33"/>
-      <c r="D76" s="33"/>
-      <c r="E76" s="33"/>
-      <c r="F76" s="33"/>
-      <c r="G76" s="33"/>
-      <c r="H76" s="33"/>
-      <c r="I76" s="33"/>
-      <c r="J76" s="33"/>
-      <c r="K76" s="33"/>
-      <c r="L76" s="34"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
+      <c r="K76" s="30"/>
+      <c r="L76" s="31"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="10" t="s">
@@ -6695,34 +6698,34 @@
       <c r="B77" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C77" s="33"/>
-      <c r="D77" s="33"/>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="33"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="33"/>
-      <c r="J77" s="33"/>
-      <c r="K77" s="33"/>
-      <c r="L77" s="34"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="30"/>
+      <c r="K77" s="30"/>
+      <c r="L77" s="31"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B78" s="39" t="s">
+      <c r="B78" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="C78" s="33"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="33"/>
-      <c r="H78" s="33"/>
-      <c r="I78" s="33"/>
-      <c r="J78" s="33"/>
-      <c r="K78" s="33"/>
-      <c r="L78" s="34"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="30"/>
+      <c r="J78" s="30"/>
+      <c r="K78" s="30"/>
+      <c r="L78" s="31"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="10" t="s">
@@ -6731,34 +6734,34 @@
       <c r="B79" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="C79" s="33"/>
-      <c r="D79" s="33"/>
-      <c r="E79" s="33"/>
-      <c r="F79" s="33"/>
-      <c r="G79" s="33"/>
-      <c r="H79" s="33"/>
-      <c r="I79" s="33"/>
-      <c r="J79" s="33"/>
-      <c r="K79" s="33"/>
-      <c r="L79" s="34"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
+      <c r="J79" s="30"/>
+      <c r="K79" s="30"/>
+      <c r="L79" s="31"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B80" s="39" t="s">
+      <c r="B80" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="C80" s="33"/>
-      <c r="D80" s="33"/>
-      <c r="E80" s="33"/>
-      <c r="F80" s="33"/>
-      <c r="G80" s="33"/>
-      <c r="H80" s="33"/>
-      <c r="I80" s="33"/>
-      <c r="J80" s="33"/>
-      <c r="K80" s="33"/>
-      <c r="L80" s="34"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="30"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="30"/>
+      <c r="L80" s="31"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="10" t="s">
@@ -6767,34 +6770,34 @@
       <c r="B81" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="C81" s="33"/>
-      <c r="D81" s="33"/>
-      <c r="E81" s="33"/>
-      <c r="F81" s="33"/>
-      <c r="G81" s="33"/>
-      <c r="H81" s="33"/>
-      <c r="I81" s="33"/>
-      <c r="J81" s="33"/>
-      <c r="K81" s="33"/>
-      <c r="L81" s="34"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="30"/>
+      <c r="I81" s="30"/>
+      <c r="J81" s="30"/>
+      <c r="K81" s="30"/>
+      <c r="L81" s="31"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B82" s="39" t="s">
+      <c r="B82" s="38" t="s">
         <v>223</v>
       </c>
-      <c r="C82" s="33"/>
-      <c r="D82" s="33"/>
-      <c r="E82" s="33"/>
-      <c r="F82" s="33"/>
-      <c r="G82" s="33"/>
-      <c r="H82" s="33"/>
-      <c r="I82" s="33"/>
-      <c r="J82" s="33"/>
-      <c r="K82" s="33"/>
-      <c r="L82" s="34"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
+      <c r="G82" s="30"/>
+      <c r="H82" s="30"/>
+      <c r="I82" s="30"/>
+      <c r="J82" s="30"/>
+      <c r="K82" s="30"/>
+      <c r="L82" s="31"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="10" t="s">
@@ -6803,34 +6806,34 @@
       <c r="B83" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="C83" s="33"/>
-      <c r="D83" s="33"/>
-      <c r="E83" s="33"/>
-      <c r="F83" s="33"/>
-      <c r="G83" s="33"/>
-      <c r="H83" s="33"/>
-      <c r="I83" s="33"/>
-      <c r="J83" s="33"/>
-      <c r="K83" s="33"/>
-      <c r="L83" s="34"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
+      <c r="H83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="30"/>
+      <c r="K83" s="30"/>
+      <c r="L83" s="31"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B84" s="39" t="s">
+      <c r="B84" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="C84" s="33"/>
-      <c r="D84" s="33"/>
-      <c r="E84" s="33"/>
-      <c r="F84" s="33"/>
-      <c r="G84" s="33"/>
-      <c r="H84" s="33"/>
-      <c r="I84" s="33"/>
-      <c r="J84" s="33"/>
-      <c r="K84" s="33"/>
-      <c r="L84" s="34"/>
+      <c r="C84" s="30"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="30"/>
+      <c r="H84" s="30"/>
+      <c r="I84" s="30"/>
+      <c r="J84" s="30"/>
+      <c r="K84" s="30"/>
+      <c r="L84" s="31"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="10" t="s">
@@ -6839,16 +6842,16 @@
       <c r="B85" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="C85" s="33"/>
-      <c r="D85" s="33"/>
-      <c r="E85" s="33"/>
-      <c r="F85" s="33"/>
-      <c r="G85" s="33"/>
-      <c r="H85" s="33"/>
-      <c r="I85" s="33"/>
-      <c r="J85" s="33"/>
-      <c r="K85" s="33"/>
-      <c r="L85" s="34"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
+      <c r="H85" s="30"/>
+      <c r="I85" s="30"/>
+      <c r="J85" s="30"/>
+      <c r="K85" s="30"/>
+      <c r="L85" s="31"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="10" t="s">
@@ -6857,16 +6860,16 @@
       <c r="B86" s="37" t="s">
         <v>231</v>
       </c>
-      <c r="C86" s="33"/>
-      <c r="D86" s="33"/>
-      <c r="E86" s="33"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="33"/>
-      <c r="H86" s="33"/>
-      <c r="I86" s="33"/>
-      <c r="J86" s="33"/>
-      <c r="K86" s="33"/>
-      <c r="L86" s="34"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="30"/>
+      <c r="K86" s="30"/>
+      <c r="L86" s="31"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="10" t="s">
@@ -6875,16 +6878,16 @@
       <c r="B87" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="C87" s="33"/>
-      <c r="D87" s="33"/>
-      <c r="E87" s="33"/>
-      <c r="F87" s="33"/>
-      <c r="G87" s="33"/>
-      <c r="H87" s="33"/>
-      <c r="I87" s="33"/>
-      <c r="J87" s="33"/>
-      <c r="K87" s="33"/>
-      <c r="L87" s="34"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
+      <c r="J87" s="30"/>
+      <c r="K87" s="30"/>
+      <c r="L87" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="47">
@@ -6896,6 +6899,14 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B79:L79"/>
     <mergeCell ref="C11:L11"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="C6:L6"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="C5:L5"/>
     <mergeCell ref="B87:L87"/>
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="B34:L34"/>
@@ -6906,25 +6917,15 @@
     <mergeCell ref="B76:L76"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="B33:L33"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C19:L19"/>
     <mergeCell ref="B86:L86"/>
-    <mergeCell ref="C18:L18"/>
     <mergeCell ref="B77:L77"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="C6:L6"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="C5:L5"/>
     <mergeCell ref="B82:L82"/>
     <mergeCell ref="B78:L78"/>
     <mergeCell ref="B29:L29"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="C16:L16"/>
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="C8:L8"/>
-    <mergeCell ref="C17:L17"/>
     <mergeCell ref="B81:L81"/>
+    <mergeCell ref="B75:L75"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="C23:L23"/>
     <mergeCell ref="C7:L7"/>
     <mergeCell ref="A74:L74"/>
     <mergeCell ref="B27:L27"/>
@@ -6932,9 +6933,11 @@
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="B35:L35"/>
     <mergeCell ref="B26:L26"/>
-    <mergeCell ref="B75:L75"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="C16:L16"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C8:L8"/>
+    <mergeCell ref="C17:L17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6954,124 +6957,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="4" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="34"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="31"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="34"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="31"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="40" t="s">
         <v>239</v>
       </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="34"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="34"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="31"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="34"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="31"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="34"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="31"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="34"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="31"/>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="26" t="s">
@@ -7105,11 +7108,11 @@
       <c r="A18" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="26" t="s">
@@ -7151,11 +7154,11 @@
       <c r="A23" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="26" t="s">
@@ -7241,11 +7244,11 @@
       <c r="A30" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="26" t="s">
@@ -7299,55 +7302,55 @@
       <c r="A36" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="34"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="31"/>
     </row>
     <row r="37" spans="1:6" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="42" t="s">
         <v>283</v>
       </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="34"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="31"/>
     </row>
     <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="34"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="31"/>
     </row>
     <row r="40" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B40" s="42" t="s">
+      <c r="B40" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="34"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="31"/>
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="34"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="31"/>
     </row>
     <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="26" t="s">
@@ -7497,11 +7500,11 @@
       <c r="A53" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B53" s="33"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="34"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="31"/>
     </row>
     <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="26" t="s">
@@ -7615,11 +7618,11 @@
       <c r="A64" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
-      <c r="F64" s="34"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="31"/>
     </row>
     <row r="65" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="26" t="s">
@@ -7737,11 +7740,11 @@
       <c r="A73" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B73" s="33"/>
-      <c r="C73" s="33"/>
-      <c r="D73" s="33"/>
-      <c r="E73" s="33"/>
-      <c r="F73" s="34"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="30"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="30"/>
+      <c r="F73" s="31"/>
     </row>
     <row r="74" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="26" t="s">
@@ -7817,123 +7820,123 @@
       <c r="A80" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B80" s="33"/>
-      <c r="C80" s="33"/>
-      <c r="D80" s="33"/>
-      <c r="E80" s="33"/>
-      <c r="F80" s="34"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="31"/>
     </row>
     <row r="81" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B81" s="42" t="s">
+      <c r="B81" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="C81" s="33"/>
-      <c r="D81" s="33"/>
-      <c r="E81" s="33"/>
-      <c r="F81" s="34"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="31"/>
     </row>
     <row r="84" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="40" t="s">
+      <c r="A84" s="43" t="s">
         <v>370</v>
       </c>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-      <c r="F84" s="30"/>
+      <c r="B84" s="33"/>
+      <c r="C84" s="33"/>
+      <c r="D84" s="33"/>
+      <c r="E84" s="33"/>
+      <c r="F84" s="33"/>
     </row>
     <row r="85" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B85" s="33"/>
-      <c r="C85" s="33"/>
-      <c r="D85" s="33"/>
-      <c r="E85" s="33"/>
-      <c r="F85" s="34"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="31"/>
     </row>
     <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B86" s="42" t="s">
+      <c r="B86" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C86" s="33"/>
-      <c r="D86" s="33"/>
-      <c r="E86" s="33"/>
-      <c r="F86" s="34"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="31"/>
     </row>
     <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B87" s="42" t="s">
+      <c r="B87" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C87" s="33"/>
-      <c r="D87" s="33"/>
-      <c r="E87" s="33"/>
-      <c r="F87" s="34"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="31"/>
     </row>
     <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B88" s="42" t="s">
+      <c r="B88" s="40" t="s">
         <v>371</v>
       </c>
-      <c r="C88" s="33"/>
-      <c r="D88" s="33"/>
-      <c r="E88" s="33"/>
-      <c r="F88" s="34"/>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="31"/>
     </row>
     <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B89" s="42" t="s">
+      <c r="B89" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="C89" s="33"/>
-      <c r="D89" s="33"/>
-      <c r="E89" s="33"/>
-      <c r="F89" s="34"/>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="30"/>
+      <c r="F89" s="31"/>
     </row>
     <row r="91" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B91" s="33"/>
-      <c r="C91" s="33"/>
-      <c r="D91" s="33"/>
-      <c r="E91" s="33"/>
-      <c r="F91" s="34"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="30"/>
+      <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="B92" s="42" t="s">
+      <c r="B92" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="C92" s="33"/>
-      <c r="D92" s="33"/>
-      <c r="E92" s="33"/>
-      <c r="F92" s="34"/>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="31"/>
     </row>
     <row r="94" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B94" s="33"/>
-      <c r="C94" s="33"/>
-      <c r="D94" s="33"/>
-      <c r="E94" s="33"/>
-      <c r="F94" s="34"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="31"/>
     </row>
     <row r="95" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="26" t="s">
@@ -7967,11 +7970,11 @@
       <c r="A98" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B98" s="33"/>
-      <c r="C98" s="33"/>
-      <c r="D98" s="33"/>
-      <c r="E98" s="33"/>
-      <c r="F98" s="34"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="30"/>
+      <c r="D98" s="30"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="31"/>
     </row>
     <row r="99" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="26" t="s">
@@ -8013,11 +8016,11 @@
       <c r="A103" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B103" s="33"/>
-      <c r="C103" s="33"/>
-      <c r="D103" s="33"/>
-      <c r="E103" s="33"/>
-      <c r="F103" s="34"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="30"/>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="31"/>
     </row>
     <row r="104" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="26" t="s">
@@ -8071,11 +8074,11 @@
       <c r="A108" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B108" s="33"/>
-      <c r="C108" s="33"/>
-      <c r="D108" s="33"/>
-      <c r="E108" s="33"/>
-      <c r="F108" s="34"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="30"/>
+      <c r="D108" s="30"/>
+      <c r="E108" s="30"/>
+      <c r="F108" s="31"/>
     </row>
     <row r="109" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="26" t="s">
@@ -8117,55 +8120,55 @@
       <c r="A113" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B113" s="33"/>
-      <c r="C113" s="33"/>
-      <c r="D113" s="33"/>
-      <c r="E113" s="33"/>
-      <c r="F113" s="34"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="31"/>
     </row>
     <row r="114" spans="1:6" ht="117" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B114" s="43" t="s">
+      <c r="B114" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="C114" s="33"/>
-      <c r="D114" s="33"/>
-      <c r="E114" s="33"/>
-      <c r="F114" s="34"/>
+      <c r="C114" s="30"/>
+      <c r="D114" s="30"/>
+      <c r="E114" s="30"/>
+      <c r="F114" s="31"/>
     </row>
     <row r="116" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B116" s="33"/>
-      <c r="C116" s="33"/>
-      <c r="D116" s="33"/>
-      <c r="E116" s="33"/>
-      <c r="F116" s="34"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="30"/>
+      <c r="D116" s="30"/>
+      <c r="E116" s="30"/>
+      <c r="F116" s="31"/>
     </row>
     <row r="117" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B117" s="42" t="s">
+      <c r="B117" s="40" t="s">
         <v>383</v>
       </c>
-      <c r="C117" s="33"/>
-      <c r="D117" s="33"/>
-      <c r="E117" s="33"/>
-      <c r="F117" s="34"/>
+      <c r="C117" s="30"/>
+      <c r="D117" s="30"/>
+      <c r="E117" s="30"/>
+      <c r="F117" s="31"/>
     </row>
     <row r="119" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B119" s="33"/>
-      <c r="C119" s="33"/>
-      <c r="D119" s="33"/>
-      <c r="E119" s="33"/>
-      <c r="F119" s="34"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+      <c r="D119" s="30"/>
+      <c r="E119" s="30"/>
+      <c r="F119" s="31"/>
     </row>
     <row r="120" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="26" t="s">
@@ -8315,11 +8318,11 @@
       <c r="A130" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B130" s="33"/>
-      <c r="C130" s="33"/>
-      <c r="D130" s="33"/>
-      <c r="E130" s="33"/>
-      <c r="F130" s="34"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="30"/>
+      <c r="D130" s="30"/>
+      <c r="E130" s="30"/>
+      <c r="F130" s="31"/>
     </row>
     <row r="131" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="26" t="s">
@@ -8445,11 +8448,11 @@
       <c r="A142" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B142" s="33"/>
-      <c r="C142" s="33"/>
-      <c r="D142" s="33"/>
-      <c r="E142" s="33"/>
-      <c r="F142" s="34"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="30"/>
+      <c r="D142" s="30"/>
+      <c r="E142" s="30"/>
+      <c r="F142" s="31"/>
     </row>
     <row r="143" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="26" t="s">
@@ -8519,11 +8522,11 @@
       <c r="A148" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B148" s="33"/>
-      <c r="C148" s="33"/>
-      <c r="D148" s="33"/>
-      <c r="E148" s="33"/>
-      <c r="F148" s="34"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="30"/>
+      <c r="D148" s="30"/>
+      <c r="E148" s="30"/>
+      <c r="F148" s="31"/>
     </row>
     <row r="149" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="26" t="s">
@@ -8585,123 +8588,123 @@
       <c r="A154" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B154" s="33"/>
-      <c r="C154" s="33"/>
-      <c r="D154" s="33"/>
-      <c r="E154" s="33"/>
-      <c r="F154" s="34"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="30"/>
+      <c r="D154" s="30"/>
+      <c r="E154" s="30"/>
+      <c r="F154" s="31"/>
     </row>
     <row r="155" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B155" s="42" t="s">
+      <c r="B155" s="40" t="s">
         <v>417</v>
       </c>
-      <c r="C155" s="33"/>
-      <c r="D155" s="33"/>
-      <c r="E155" s="33"/>
-      <c r="F155" s="34"/>
+      <c r="C155" s="30"/>
+      <c r="D155" s="30"/>
+      <c r="E155" s="30"/>
+      <c r="F155" s="31"/>
     </row>
     <row r="158" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="40" t="s">
+      <c r="A158" s="43" t="s">
         <v>418</v>
       </c>
-      <c r="B158" s="30"/>
-      <c r="C158" s="30"/>
-      <c r="D158" s="30"/>
-      <c r="E158" s="30"/>
-      <c r="F158" s="30"/>
+      <c r="B158" s="33"/>
+      <c r="C158" s="33"/>
+      <c r="D158" s="33"/>
+      <c r="E158" s="33"/>
+      <c r="F158" s="33"/>
     </row>
     <row r="159" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B159" s="33"/>
-      <c r="C159" s="33"/>
-      <c r="D159" s="33"/>
-      <c r="E159" s="33"/>
-      <c r="F159" s="34"/>
+      <c r="B159" s="30"/>
+      <c r="C159" s="30"/>
+      <c r="D159" s="30"/>
+      <c r="E159" s="30"/>
+      <c r="F159" s="31"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B160" s="42" t="s">
+      <c r="B160" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C160" s="33"/>
-      <c r="D160" s="33"/>
-      <c r="E160" s="33"/>
-      <c r="F160" s="34"/>
+      <c r="C160" s="30"/>
+      <c r="D160" s="30"/>
+      <c r="E160" s="30"/>
+      <c r="F160" s="31"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B161" s="42" t="s">
+      <c r="B161" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C161" s="33"/>
-      <c r="D161" s="33"/>
-      <c r="E161" s="33"/>
-      <c r="F161" s="34"/>
+      <c r="C161" s="30"/>
+      <c r="D161" s="30"/>
+      <c r="E161" s="30"/>
+      <c r="F161" s="31"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B162" s="42" t="s">
+      <c r="B162" s="40" t="s">
         <v>419</v>
       </c>
-      <c r="C162" s="33"/>
-      <c r="D162" s="33"/>
-      <c r="E162" s="33"/>
-      <c r="F162" s="34"/>
+      <c r="C162" s="30"/>
+      <c r="D162" s="30"/>
+      <c r="E162" s="30"/>
+      <c r="F162" s="31"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B163" s="42" t="s">
+      <c r="B163" s="40" t="s">
         <v>420</v>
       </c>
-      <c r="C163" s="33"/>
-      <c r="D163" s="33"/>
-      <c r="E163" s="33"/>
-      <c r="F163" s="34"/>
+      <c r="C163" s="30"/>
+      <c r="D163" s="30"/>
+      <c r="E163" s="30"/>
+      <c r="F163" s="31"/>
     </row>
     <row r="164" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B164" s="33"/>
-      <c r="C164" s="33"/>
-      <c r="D164" s="33"/>
-      <c r="E164" s="33"/>
-      <c r="F164" s="34"/>
+      <c r="B164" s="30"/>
+      <c r="C164" s="30"/>
+      <c r="D164" s="30"/>
+      <c r="E164" s="30"/>
+      <c r="F164" s="31"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B165" s="42" t="s">
+      <c r="B165" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="C165" s="33"/>
-      <c r="D165" s="33"/>
-      <c r="E165" s="33"/>
-      <c r="F165" s="34"/>
+      <c r="C165" s="30"/>
+      <c r="D165" s="30"/>
+      <c r="E165" s="30"/>
+      <c r="F165" s="31"/>
     </row>
     <row r="166" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B166" s="33"/>
-      <c r="C166" s="33"/>
-      <c r="D166" s="33"/>
-      <c r="E166" s="33"/>
-      <c r="F166" s="34"/>
+      <c r="B166" s="30"/>
+      <c r="C166" s="30"/>
+      <c r="D166" s="30"/>
+      <c r="E166" s="30"/>
+      <c r="F166" s="31"/>
     </row>
     <row r="167" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="26" t="s">
@@ -8729,11 +8732,11 @@
       <c r="A169" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B169" s="33"/>
-      <c r="C169" s="33"/>
-      <c r="D169" s="33"/>
-      <c r="E169" s="33"/>
-      <c r="F169" s="34"/>
+      <c r="B169" s="30"/>
+      <c r="C169" s="30"/>
+      <c r="D169" s="30"/>
+      <c r="E169" s="30"/>
+      <c r="F169" s="31"/>
     </row>
     <row r="170" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="26" t="s">
@@ -8767,11 +8770,11 @@
       <c r="A173" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B173" s="33"/>
-      <c r="C173" s="33"/>
-      <c r="D173" s="33"/>
-      <c r="E173" s="33"/>
-      <c r="F173" s="34"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
+      <c r="D173" s="30"/>
+      <c r="E173" s="30"/>
+      <c r="F173" s="31"/>
     </row>
     <row r="174" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="26" t="s">
@@ -8809,11 +8812,11 @@
       <c r="A176" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B176" s="33"/>
-      <c r="C176" s="33"/>
-      <c r="D176" s="33"/>
-      <c r="E176" s="33"/>
-      <c r="F176" s="34"/>
+      <c r="B176" s="30"/>
+      <c r="C176" s="30"/>
+      <c r="D176" s="30"/>
+      <c r="E176" s="30"/>
+      <c r="F176" s="31"/>
     </row>
     <row r="177" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="26" t="s">
@@ -8851,55 +8854,55 @@
       <c r="A180" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B180" s="33"/>
-      <c r="C180" s="33"/>
-      <c r="D180" s="33"/>
-      <c r="E180" s="33"/>
-      <c r="F180" s="34"/>
+      <c r="B180" s="30"/>
+      <c r="C180" s="30"/>
+      <c r="D180" s="30"/>
+      <c r="E180" s="30"/>
+      <c r="F180" s="31"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B181" s="43" t="s">
+      <c r="B181" s="42" t="s">
         <v>429</v>
       </c>
-      <c r="C181" s="33"/>
-      <c r="D181" s="33"/>
-      <c r="E181" s="33"/>
-      <c r="F181" s="34"/>
+      <c r="C181" s="30"/>
+      <c r="D181" s="30"/>
+      <c r="E181" s="30"/>
+      <c r="F181" s="31"/>
     </row>
     <row r="182" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B182" s="33"/>
-      <c r="C182" s="33"/>
-      <c r="D182" s="33"/>
-      <c r="E182" s="33"/>
-      <c r="F182" s="34"/>
+      <c r="B182" s="30"/>
+      <c r="C182" s="30"/>
+      <c r="D182" s="30"/>
+      <c r="E182" s="30"/>
+      <c r="F182" s="31"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B183" s="42" t="s">
+      <c r="B183" s="40" t="s">
         <v>430</v>
       </c>
-      <c r="C183" s="33"/>
-      <c r="D183" s="33"/>
-      <c r="E183" s="33"/>
-      <c r="F183" s="34"/>
+      <c r="C183" s="30"/>
+      <c r="D183" s="30"/>
+      <c r="E183" s="30"/>
+      <c r="F183" s="31"/>
     </row>
     <row r="184" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B184" s="33"/>
-      <c r="C184" s="33"/>
-      <c r="D184" s="33"/>
-      <c r="E184" s="33"/>
-      <c r="F184" s="34"/>
+      <c r="B184" s="30"/>
+      <c r="C184" s="30"/>
+      <c r="D184" s="30"/>
+      <c r="E184" s="30"/>
+      <c r="F184" s="31"/>
     </row>
     <row r="185" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="26" t="s">
@@ -9005,11 +9008,11 @@
       <c r="A192" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B192" s="33"/>
-      <c r="C192" s="33"/>
-      <c r="D192" s="33"/>
-      <c r="E192" s="33"/>
-      <c r="F192" s="34"/>
+      <c r="B192" s="30"/>
+      <c r="C192" s="30"/>
+      <c r="D192" s="30"/>
+      <c r="E192" s="30"/>
+      <c r="F192" s="31"/>
     </row>
     <row r="193" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="26" t="s">
@@ -9119,11 +9122,11 @@
       <c r="A202" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B202" s="33"/>
-      <c r="C202" s="33"/>
-      <c r="D202" s="33"/>
-      <c r="E202" s="33"/>
-      <c r="F202" s="34"/>
+      <c r="B202" s="30"/>
+      <c r="C202" s="30"/>
+      <c r="D202" s="30"/>
+      <c r="E202" s="30"/>
+      <c r="F202" s="31"/>
     </row>
     <row r="203" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="26" t="s">
@@ -9205,11 +9208,11 @@
       <c r="A208" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B208" s="33"/>
-      <c r="C208" s="33"/>
-      <c r="D208" s="33"/>
-      <c r="E208" s="33"/>
-      <c r="F208" s="34"/>
+      <c r="B208" s="30"/>
+      <c r="C208" s="30"/>
+      <c r="D208" s="30"/>
+      <c r="E208" s="30"/>
+      <c r="F208" s="31"/>
     </row>
     <row r="209" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="26" t="s">
@@ -9257,23 +9260,23 @@
       <c r="A212" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B212" s="33"/>
-      <c r="C212" s="33"/>
-      <c r="D212" s="33"/>
-      <c r="E212" s="33"/>
-      <c r="F212" s="34"/>
+      <c r="B212" s="30"/>
+      <c r="C212" s="30"/>
+      <c r="D212" s="30"/>
+      <c r="E212" s="30"/>
+      <c r="F212" s="31"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B213" s="42" t="s">
+      <c r="B213" s="40" t="s">
         <v>456</v>
       </c>
-      <c r="C213" s="33"/>
-      <c r="D213" s="33"/>
-      <c r="E213" s="33"/>
-      <c r="F213" s="34"/>
+      <c r="C213" s="30"/>
+      <c r="D213" s="30"/>
+      <c r="E213" s="30"/>
+      <c r="F213" s="31"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" s="7"/>
@@ -9297,91 +9300,91 @@
       <c r="A216" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B216" s="33"/>
-      <c r="C216" s="33"/>
-      <c r="D216" s="33"/>
-      <c r="E216" s="33"/>
-      <c r="F216" s="34"/>
+      <c r="B216" s="30"/>
+      <c r="C216" s="30"/>
+      <c r="D216" s="30"/>
+      <c r="E216" s="30"/>
+      <c r="F216" s="31"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B217" s="42" t="s">
+      <c r="B217" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C217" s="33"/>
-      <c r="D217" s="33"/>
-      <c r="E217" s="33"/>
-      <c r="F217" s="34"/>
+      <c r="C217" s="30"/>
+      <c r="D217" s="30"/>
+      <c r="E217" s="30"/>
+      <c r="F217" s="31"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B218" s="42" t="s">
+      <c r="B218" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C218" s="33"/>
-      <c r="D218" s="33"/>
-      <c r="E218" s="33"/>
-      <c r="F218" s="34"/>
+      <c r="C218" s="30"/>
+      <c r="D218" s="30"/>
+      <c r="E218" s="30"/>
+      <c r="F218" s="31"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B219" s="42" t="s">
+      <c r="B219" s="40" t="s">
         <v>458</v>
       </c>
-      <c r="C219" s="33"/>
-      <c r="D219" s="33"/>
-      <c r="E219" s="33"/>
-      <c r="F219" s="34"/>
+      <c r="C219" s="30"/>
+      <c r="D219" s="30"/>
+      <c r="E219" s="30"/>
+      <c r="F219" s="31"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B220" s="42" t="s">
+      <c r="B220" s="40" t="s">
         <v>459</v>
       </c>
-      <c r="C220" s="33"/>
-      <c r="D220" s="33"/>
-      <c r="E220" s="33"/>
-      <c r="F220" s="34"/>
+      <c r="C220" s="30"/>
+      <c r="D220" s="30"/>
+      <c r="E220" s="30"/>
+      <c r="F220" s="31"/>
     </row>
     <row r="221" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B221" s="33"/>
-      <c r="C221" s="33"/>
-      <c r="D221" s="33"/>
-      <c r="E221" s="33"/>
-      <c r="F221" s="34"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="30"/>
+      <c r="D221" s="30"/>
+      <c r="E221" s="30"/>
+      <c r="F221" s="31"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B222" s="42" t="s">
+      <c r="B222" s="40" t="s">
         <v>460</v>
       </c>
-      <c r="C222" s="33"/>
-      <c r="D222" s="33"/>
-      <c r="E222" s="33"/>
-      <c r="F222" s="34"/>
+      <c r="C222" s="30"/>
+      <c r="D222" s="30"/>
+      <c r="E222" s="30"/>
+      <c r="F222" s="31"/>
     </row>
     <row r="223" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B223" s="33"/>
-      <c r="C223" s="33"/>
-      <c r="D223" s="33"/>
-      <c r="E223" s="33"/>
-      <c r="F223" s="34"/>
+      <c r="B223" s="30"/>
+      <c r="C223" s="30"/>
+      <c r="D223" s="30"/>
+      <c r="E223" s="30"/>
+      <c r="F223" s="31"/>
     </row>
     <row r="224" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="26" t="s">
@@ -9412,11 +9415,11 @@
       <c r="A226" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B226" s="33"/>
-      <c r="C226" s="33"/>
-      <c r="D226" s="33"/>
-      <c r="E226" s="33"/>
-      <c r="F226" s="34"/>
+      <c r="B226" s="30"/>
+      <c r="C226" s="30"/>
+      <c r="D226" s="30"/>
+      <c r="E226" s="30"/>
+      <c r="F226" s="31"/>
     </row>
     <row r="227" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="26" t="s">
@@ -9454,11 +9457,11 @@
       <c r="A230" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B230" s="33"/>
-      <c r="C230" s="33"/>
-      <c r="D230" s="33"/>
-      <c r="E230" s="33"/>
-      <c r="F230" s="34"/>
+      <c r="B230" s="30"/>
+      <c r="C230" s="30"/>
+      <c r="D230" s="30"/>
+      <c r="E230" s="30"/>
+      <c r="F230" s="31"/>
     </row>
     <row r="231" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="26" t="s">
@@ -9492,11 +9495,11 @@
       <c r="A233" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B233" s="33"/>
-      <c r="C233" s="33"/>
-      <c r="D233" s="33"/>
-      <c r="E233" s="33"/>
-      <c r="F233" s="34"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="30"/>
+      <c r="D233" s="30"/>
+      <c r="E233" s="30"/>
+      <c r="F233" s="31"/>
     </row>
     <row r="234" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="26" t="s">
@@ -9526,55 +9529,55 @@
       <c r="A237" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B237" s="33"/>
-      <c r="C237" s="33"/>
-      <c r="D237" s="33"/>
-      <c r="E237" s="33"/>
-      <c r="F237" s="34"/>
+      <c r="B237" s="30"/>
+      <c r="C237" s="30"/>
+      <c r="D237" s="30"/>
+      <c r="E237" s="30"/>
+      <c r="F237" s="31"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B238" s="43" t="s">
+      <c r="B238" s="42" t="s">
         <v>468</v>
       </c>
-      <c r="C238" s="33"/>
-      <c r="D238" s="33"/>
-      <c r="E238" s="33"/>
-      <c r="F238" s="34"/>
+      <c r="C238" s="30"/>
+      <c r="D238" s="30"/>
+      <c r="E238" s="30"/>
+      <c r="F238" s="31"/>
     </row>
     <row r="239" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B239" s="33"/>
-      <c r="C239" s="33"/>
-      <c r="D239" s="33"/>
-      <c r="E239" s="33"/>
-      <c r="F239" s="34"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="30"/>
+      <c r="D239" s="30"/>
+      <c r="E239" s="30"/>
+      <c r="F239" s="31"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B240" s="42" t="s">
+      <c r="B240" s="40" t="s">
         <v>469</v>
       </c>
-      <c r="C240" s="33"/>
-      <c r="D240" s="33"/>
-      <c r="E240" s="33"/>
-      <c r="F240" s="34"/>
+      <c r="C240" s="30"/>
+      <c r="D240" s="30"/>
+      <c r="E240" s="30"/>
+      <c r="F240" s="31"/>
     </row>
     <row r="241" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B241" s="33"/>
-      <c r="C241" s="33"/>
-      <c r="D241" s="33"/>
-      <c r="E241" s="33"/>
-      <c r="F241" s="34"/>
+      <c r="B241" s="30"/>
+      <c r="C241" s="30"/>
+      <c r="D241" s="30"/>
+      <c r="E241" s="30"/>
+      <c r="F241" s="31"/>
     </row>
     <row r="242" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="26" t="s">
@@ -9668,11 +9671,11 @@
       <c r="A248" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B248" s="33"/>
-      <c r="C248" s="33"/>
-      <c r="D248" s="33"/>
-      <c r="E248" s="33"/>
-      <c r="F248" s="34"/>
+      <c r="B248" s="30"/>
+      <c r="C248" s="30"/>
+      <c r="D248" s="30"/>
+      <c r="E248" s="30"/>
+      <c r="F248" s="31"/>
     </row>
     <row r="249" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="26" t="s">
@@ -9742,11 +9745,11 @@
       <c r="A255" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B255" s="33"/>
-      <c r="C255" s="33"/>
-      <c r="D255" s="33"/>
-      <c r="E255" s="33"/>
-      <c r="F255" s="34"/>
+      <c r="B255" s="30"/>
+      <c r="C255" s="30"/>
+      <c r="D255" s="30"/>
+      <c r="E255" s="30"/>
+      <c r="F255" s="31"/>
     </row>
     <row r="256" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="26" t="s">
@@ -9798,11 +9801,11 @@
       <c r="A259" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B259" s="33"/>
-      <c r="C259" s="33"/>
-      <c r="D259" s="33"/>
-      <c r="E259" s="33"/>
-      <c r="F259" s="34"/>
+      <c r="B259" s="30"/>
+      <c r="C259" s="30"/>
+      <c r="D259" s="30"/>
+      <c r="E259" s="30"/>
+      <c r="F259" s="31"/>
     </row>
     <row r="260" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="26" t="s">
@@ -9836,128 +9839,128 @@
       <c r="A262" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B262" s="33"/>
-      <c r="C262" s="33"/>
-      <c r="D262" s="33"/>
-      <c r="E262" s="33"/>
-      <c r="F262" s="34"/>
+      <c r="B262" s="30"/>
+      <c r="C262" s="30"/>
+      <c r="D262" s="30"/>
+      <c r="E262" s="30"/>
+      <c r="F262" s="31"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B263" s="42" t="s">
+      <c r="B263" s="40" t="s">
         <v>483</v>
       </c>
-      <c r="C263" s="33"/>
-      <c r="D263" s="33"/>
-      <c r="E263" s="33"/>
-      <c r="F263" s="34"/>
+      <c r="C263" s="30"/>
+      <c r="D263" s="30"/>
+      <c r="E263" s="30"/>
+      <c r="F263" s="31"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264" s="28"/>
     </row>
     <row r="265" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="40" t="s">
+      <c r="A265" s="43" t="s">
         <v>484</v>
       </c>
-      <c r="B265" s="30"/>
-      <c r="C265" s="30"/>
-      <c r="D265" s="30"/>
-      <c r="E265" s="30"/>
-      <c r="F265" s="30"/>
+      <c r="B265" s="33"/>
+      <c r="C265" s="33"/>
+      <c r="D265" s="33"/>
+      <c r="E265" s="33"/>
+      <c r="F265" s="33"/>
     </row>
     <row r="266" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B266" s="33"/>
-      <c r="C266" s="33"/>
-      <c r="D266" s="33"/>
-      <c r="E266" s="33"/>
-      <c r="F266" s="34"/>
+      <c r="B266" s="30"/>
+      <c r="C266" s="30"/>
+      <c r="D266" s="30"/>
+      <c r="E266" s="30"/>
+      <c r="F266" s="31"/>
     </row>
     <row r="267" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B267" s="42" t="s">
+      <c r="B267" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C267" s="33"/>
-      <c r="D267" s="33"/>
-      <c r="E267" s="33"/>
-      <c r="F267" s="34"/>
+      <c r="C267" s="30"/>
+      <c r="D267" s="30"/>
+      <c r="E267" s="30"/>
+      <c r="F267" s="31"/>
     </row>
     <row r="268" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B268" s="42" t="s">
+      <c r="B268" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C268" s="33"/>
-      <c r="D268" s="33"/>
-      <c r="E268" s="33"/>
-      <c r="F268" s="34"/>
+      <c r="C268" s="30"/>
+      <c r="D268" s="30"/>
+      <c r="E268" s="30"/>
+      <c r="F268" s="31"/>
     </row>
     <row r="269" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B269" s="42" t="s">
+      <c r="B269" s="40" t="s">
         <v>485</v>
       </c>
-      <c r="C269" s="33"/>
-      <c r="D269" s="33"/>
-      <c r="E269" s="33"/>
-      <c r="F269" s="34"/>
+      <c r="C269" s="30"/>
+      <c r="D269" s="30"/>
+      <c r="E269" s="30"/>
+      <c r="F269" s="31"/>
     </row>
     <row r="270" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B270" s="42" t="s">
+      <c r="B270" s="40" t="s">
         <v>486</v>
       </c>
-      <c r="C270" s="33"/>
-      <c r="D270" s="33"/>
-      <c r="E270" s="33"/>
-      <c r="F270" s="34"/>
+      <c r="C270" s="30"/>
+      <c r="D270" s="30"/>
+      <c r="E270" s="30"/>
+      <c r="F270" s="31"/>
     </row>
     <row r="271" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="272" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B272" s="33"/>
-      <c r="C272" s="33"/>
-      <c r="D272" s="33"/>
-      <c r="E272" s="33"/>
-      <c r="F272" s="34"/>
+      <c r="B272" s="30"/>
+      <c r="C272" s="30"/>
+      <c r="D272" s="30"/>
+      <c r="E272" s="30"/>
+      <c r="F272" s="31"/>
     </row>
     <row r="273" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="B273" s="42" t="s">
+      <c r="B273" s="40" t="s">
         <v>487</v>
       </c>
-      <c r="C273" s="33"/>
-      <c r="D273" s="33"/>
-      <c r="E273" s="33"/>
-      <c r="F273" s="34"/>
+      <c r="C273" s="30"/>
+      <c r="D273" s="30"/>
+      <c r="E273" s="30"/>
+      <c r="F273" s="31"/>
     </row>
     <row r="274" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="275" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B275" s="33"/>
-      <c r="C275" s="33"/>
-      <c r="D275" s="33"/>
-      <c r="E275" s="33"/>
-      <c r="F275" s="34"/>
+      <c r="B275" s="30"/>
+      <c r="C275" s="30"/>
+      <c r="D275" s="30"/>
+      <c r="E275" s="30"/>
+      <c r="F275" s="31"/>
     </row>
     <row r="276" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="26" t="s">
@@ -9992,11 +9995,11 @@
       <c r="A279" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B279" s="33"/>
-      <c r="C279" s="33"/>
-      <c r="D279" s="33"/>
-      <c r="E279" s="33"/>
-      <c r="F279" s="34"/>
+      <c r="B279" s="30"/>
+      <c r="C279" s="30"/>
+      <c r="D279" s="30"/>
+      <c r="E279" s="30"/>
+      <c r="F279" s="31"/>
     </row>
     <row r="280" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="26" t="s">
@@ -10039,11 +10042,11 @@
       <c r="A284" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B284" s="33"/>
-      <c r="C284" s="33"/>
-      <c r="D284" s="33"/>
-      <c r="E284" s="33"/>
-      <c r="F284" s="34"/>
+      <c r="B284" s="30"/>
+      <c r="C284" s="30"/>
+      <c r="D284" s="30"/>
+      <c r="E284" s="30"/>
+      <c r="F284" s="31"/>
     </row>
     <row r="285" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="26" t="s">
@@ -10098,11 +10101,11 @@
       <c r="A289" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B289" s="33"/>
-      <c r="C289" s="33"/>
-      <c r="D289" s="33"/>
-      <c r="E289" s="33"/>
-      <c r="F289" s="34"/>
+      <c r="B289" s="30"/>
+      <c r="C289" s="30"/>
+      <c r="D289" s="30"/>
+      <c r="E289" s="30"/>
+      <c r="F289" s="31"/>
     </row>
     <row r="290" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="26" t="s">
@@ -10145,57 +10148,57 @@
       <c r="A294" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B294" s="33"/>
-      <c r="C294" s="33"/>
-      <c r="D294" s="33"/>
-      <c r="E294" s="33"/>
-      <c r="F294" s="34"/>
+      <c r="B294" s="30"/>
+      <c r="C294" s="30"/>
+      <c r="D294" s="30"/>
+      <c r="E294" s="30"/>
+      <c r="F294" s="31"/>
     </row>
     <row r="295" spans="1:6" ht="142.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B295" s="43" t="s">
+      <c r="B295" s="42" t="s">
         <v>500</v>
       </c>
-      <c r="C295" s="33"/>
-      <c r="D295" s="33"/>
-      <c r="E295" s="33"/>
-      <c r="F295" s="34"/>
+      <c r="C295" s="30"/>
+      <c r="D295" s="30"/>
+      <c r="E295" s="30"/>
+      <c r="F295" s="31"/>
     </row>
     <row r="296" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="297" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B297" s="33"/>
-      <c r="C297" s="33"/>
-      <c r="D297" s="33"/>
-      <c r="E297" s="33"/>
-      <c r="F297" s="34"/>
+      <c r="B297" s="30"/>
+      <c r="C297" s="30"/>
+      <c r="D297" s="30"/>
+      <c r="E297" s="30"/>
+      <c r="F297" s="31"/>
     </row>
     <row r="298" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B298" s="42" t="s">
+      <c r="B298" s="40" t="s">
         <v>501</v>
       </c>
-      <c r="C298" s="33"/>
-      <c r="D298" s="33"/>
-      <c r="E298" s="33"/>
-      <c r="F298" s="34"/>
+      <c r="C298" s="30"/>
+      <c r="D298" s="30"/>
+      <c r="E298" s="30"/>
+      <c r="F298" s="31"/>
     </row>
     <row r="299" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="300" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B300" s="33"/>
-      <c r="C300" s="33"/>
-      <c r="D300" s="33"/>
-      <c r="E300" s="33"/>
-      <c r="F300" s="34"/>
+      <c r="B300" s="30"/>
+      <c r="C300" s="30"/>
+      <c r="D300" s="30"/>
+      <c r="E300" s="30"/>
+      <c r="F300" s="31"/>
     </row>
     <row r="301" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="26" t="s">
@@ -10346,11 +10349,11 @@
       <c r="A311" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B311" s="33"/>
-      <c r="C311" s="33"/>
-      <c r="D311" s="33"/>
-      <c r="E311" s="33"/>
-      <c r="F311" s="34"/>
+      <c r="B311" s="30"/>
+      <c r="C311" s="30"/>
+      <c r="D311" s="30"/>
+      <c r="E311" s="30"/>
+      <c r="F311" s="31"/>
     </row>
     <row r="312" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="26" t="s">
@@ -10501,11 +10504,11 @@
       <c r="A325" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B325" s="33"/>
-      <c r="C325" s="33"/>
-      <c r="D325" s="33"/>
-      <c r="E325" s="33"/>
-      <c r="F325" s="34"/>
+      <c r="B325" s="30"/>
+      <c r="C325" s="30"/>
+      <c r="D325" s="30"/>
+      <c r="E325" s="30"/>
+      <c r="F325" s="31"/>
     </row>
     <row r="326" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="26" t="s">
@@ -10576,11 +10579,11 @@
       <c r="A331" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B331" s="33"/>
-      <c r="C331" s="33"/>
-      <c r="D331" s="33"/>
-      <c r="E331" s="33"/>
-      <c r="F331" s="34"/>
+      <c r="B331" s="30"/>
+      <c r="C331" s="30"/>
+      <c r="D331" s="30"/>
+      <c r="E331" s="30"/>
+      <c r="F331" s="31"/>
     </row>
     <row r="332" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="26" t="s">
@@ -10643,127 +10646,127 @@
       <c r="A337" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B337" s="33"/>
-      <c r="C337" s="33"/>
-      <c r="D337" s="33"/>
-      <c r="E337" s="33"/>
-      <c r="F337" s="34"/>
+      <c r="B337" s="30"/>
+      <c r="C337" s="30"/>
+      <c r="D337" s="30"/>
+      <c r="E337" s="30"/>
+      <c r="F337" s="31"/>
     </row>
     <row r="338" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B338" s="42" t="s">
+      <c r="B338" s="40" t="s">
         <v>547</v>
       </c>
-      <c r="C338" s="33"/>
-      <c r="D338" s="33"/>
-      <c r="E338" s="33"/>
-      <c r="F338" s="34"/>
+      <c r="C338" s="30"/>
+      <c r="D338" s="30"/>
+      <c r="E338" s="30"/>
+      <c r="F338" s="31"/>
     </row>
     <row r="339" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="340" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="341" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A341" s="40" t="s">
+      <c r="A341" s="43" t="s">
         <v>548</v>
       </c>
-      <c r="B341" s="30"/>
-      <c r="C341" s="30"/>
-      <c r="D341" s="30"/>
-      <c r="E341" s="30"/>
-      <c r="F341" s="30"/>
+      <c r="B341" s="33"/>
+      <c r="C341" s="33"/>
+      <c r="D341" s="33"/>
+      <c r="E341" s="33"/>
+      <c r="F341" s="33"/>
     </row>
     <row r="342" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B342" s="33"/>
-      <c r="C342" s="33"/>
-      <c r="D342" s="33"/>
-      <c r="E342" s="33"/>
-      <c r="F342" s="34"/>
+      <c r="B342" s="30"/>
+      <c r="C342" s="30"/>
+      <c r="D342" s="30"/>
+      <c r="E342" s="30"/>
+      <c r="F342" s="31"/>
     </row>
     <row r="343" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B343" s="42" t="s">
+      <c r="B343" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C343" s="33"/>
-      <c r="D343" s="33"/>
-      <c r="E343" s="33"/>
-      <c r="F343" s="34"/>
+      <c r="C343" s="30"/>
+      <c r="D343" s="30"/>
+      <c r="E343" s="30"/>
+      <c r="F343" s="31"/>
     </row>
     <row r="344" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B344" s="42" t="s">
+      <c r="B344" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C344" s="33"/>
-      <c r="D344" s="33"/>
-      <c r="E344" s="33"/>
-      <c r="F344" s="34"/>
+      <c r="C344" s="30"/>
+      <c r="D344" s="30"/>
+      <c r="E344" s="30"/>
+      <c r="F344" s="31"/>
     </row>
     <row r="345" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B345" s="42" t="s">
+      <c r="B345" s="40" t="s">
         <v>549</v>
       </c>
-      <c r="C345" s="33"/>
-      <c r="D345" s="33"/>
-      <c r="E345" s="33"/>
-      <c r="F345" s="34"/>
+      <c r="C345" s="30"/>
+      <c r="D345" s="30"/>
+      <c r="E345" s="30"/>
+      <c r="F345" s="31"/>
     </row>
     <row r="346" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B346" s="42" t="s">
+      <c r="B346" s="40" t="s">
         <v>550</v>
       </c>
-      <c r="C346" s="33"/>
-      <c r="D346" s="33"/>
-      <c r="E346" s="33"/>
-      <c r="F346" s="34"/>
+      <c r="C346" s="30"/>
+      <c r="D346" s="30"/>
+      <c r="E346" s="30"/>
+      <c r="F346" s="31"/>
     </row>
     <row r="347" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="348" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B348" s="33"/>
-      <c r="C348" s="33"/>
-      <c r="D348" s="33"/>
-      <c r="E348" s="33"/>
-      <c r="F348" s="34"/>
+      <c r="B348" s="30"/>
+      <c r="C348" s="30"/>
+      <c r="D348" s="30"/>
+      <c r="E348" s="30"/>
+      <c r="F348" s="31"/>
     </row>
     <row r="349" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="B349" s="42" t="s">
+      <c r="B349" s="40" t="s">
         <v>487</v>
       </c>
-      <c r="C349" s="33"/>
-      <c r="D349" s="33"/>
-      <c r="E349" s="33"/>
-      <c r="F349" s="34"/>
+      <c r="C349" s="30"/>
+      <c r="D349" s="30"/>
+      <c r="E349" s="30"/>
+      <c r="F349" s="31"/>
     </row>
     <row r="350" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="351" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B351" s="33"/>
-      <c r="C351" s="33"/>
-      <c r="D351" s="33"/>
-      <c r="E351" s="33"/>
-      <c r="F351" s="34"/>
+      <c r="B351" s="30"/>
+      <c r="C351" s="30"/>
+      <c r="D351" s="30"/>
+      <c r="E351" s="30"/>
+      <c r="F351" s="31"/>
     </row>
     <row r="352" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="26" t="s">
@@ -10797,11 +10800,11 @@
       <c r="A355" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B355" s="33"/>
-      <c r="C355" s="33"/>
-      <c r="D355" s="33"/>
-      <c r="E355" s="33"/>
-      <c r="F355" s="34"/>
+      <c r="B355" s="30"/>
+      <c r="C355" s="30"/>
+      <c r="D355" s="30"/>
+      <c r="E355" s="30"/>
+      <c r="F355" s="31"/>
     </row>
     <row r="356" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="26" t="s">
@@ -10844,11 +10847,11 @@
       <c r="A360" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B360" s="33"/>
-      <c r="C360" s="33"/>
-      <c r="D360" s="33"/>
-      <c r="E360" s="33"/>
-      <c r="F360" s="34"/>
+      <c r="B360" s="30"/>
+      <c r="C360" s="30"/>
+      <c r="D360" s="30"/>
+      <c r="E360" s="30"/>
+      <c r="F360" s="31"/>
     </row>
     <row r="361" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="26" t="s">
@@ -10919,11 +10922,11 @@
       <c r="A366" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B366" s="33"/>
-      <c r="C366" s="33"/>
-      <c r="D366" s="33"/>
-      <c r="E366" s="33"/>
-      <c r="F366" s="34"/>
+      <c r="B366" s="30"/>
+      <c r="C366" s="30"/>
+      <c r="D366" s="30"/>
+      <c r="E366" s="30"/>
+      <c r="F366" s="31"/>
     </row>
     <row r="367" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="26" t="s">
@@ -10966,57 +10969,57 @@
       <c r="A371" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B371" s="33"/>
-      <c r="C371" s="33"/>
-      <c r="D371" s="33"/>
-      <c r="E371" s="33"/>
-      <c r="F371" s="34"/>
+      <c r="B371" s="30"/>
+      <c r="C371" s="30"/>
+      <c r="D371" s="30"/>
+      <c r="E371" s="30"/>
+      <c r="F371" s="31"/>
     </row>
     <row r="372" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B372" s="43" t="s">
+      <c r="B372" s="42" t="s">
         <v>564</v>
       </c>
-      <c r="C372" s="33"/>
-      <c r="D372" s="33"/>
-      <c r="E372" s="33"/>
-      <c r="F372" s="34"/>
+      <c r="C372" s="30"/>
+      <c r="D372" s="30"/>
+      <c r="E372" s="30"/>
+      <c r="F372" s="31"/>
     </row>
     <row r="373" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="374" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B374" s="33"/>
-      <c r="C374" s="33"/>
-      <c r="D374" s="33"/>
-      <c r="E374" s="33"/>
-      <c r="F374" s="34"/>
+      <c r="B374" s="30"/>
+      <c r="C374" s="30"/>
+      <c r="D374" s="30"/>
+      <c r="E374" s="30"/>
+      <c r="F374" s="31"/>
     </row>
     <row r="375" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B375" s="42" t="s">
+      <c r="B375" s="40" t="s">
         <v>565</v>
       </c>
-      <c r="C375" s="33"/>
-      <c r="D375" s="33"/>
-      <c r="E375" s="33"/>
-      <c r="F375" s="34"/>
+      <c r="C375" s="30"/>
+      <c r="D375" s="30"/>
+      <c r="E375" s="30"/>
+      <c r="F375" s="31"/>
     </row>
     <row r="376" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="377" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B377" s="33"/>
-      <c r="C377" s="33"/>
-      <c r="D377" s="33"/>
-      <c r="E377" s="33"/>
-      <c r="F377" s="34"/>
+      <c r="B377" s="30"/>
+      <c r="C377" s="30"/>
+      <c r="D377" s="30"/>
+      <c r="E377" s="30"/>
+      <c r="F377" s="31"/>
     </row>
     <row r="378" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="26" t="s">
@@ -11198,11 +11201,11 @@
       <c r="A390" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B390" s="33"/>
-      <c r="C390" s="33"/>
-      <c r="D390" s="33"/>
-      <c r="E390" s="33"/>
-      <c r="F390" s="34"/>
+      <c r="B390" s="30"/>
+      <c r="C390" s="30"/>
+      <c r="D390" s="30"/>
+      <c r="E390" s="30"/>
+      <c r="F390" s="31"/>
     </row>
     <row r="391" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="26" t="s">
@@ -11365,11 +11368,11 @@
       <c r="A405" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B405" s="33"/>
-      <c r="C405" s="33"/>
-      <c r="D405" s="33"/>
-      <c r="E405" s="33"/>
-      <c r="F405" s="34"/>
+      <c r="B405" s="30"/>
+      <c r="C405" s="30"/>
+      <c r="D405" s="30"/>
+      <c r="E405" s="30"/>
+      <c r="F405" s="31"/>
     </row>
     <row r="406" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="26" t="s">
@@ -11472,11 +11475,11 @@
       <c r="A413" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B413" s="33"/>
-      <c r="C413" s="33"/>
-      <c r="D413" s="33"/>
-      <c r="E413" s="33"/>
-      <c r="F413" s="34"/>
+      <c r="B413" s="30"/>
+      <c r="C413" s="30"/>
+      <c r="D413" s="30"/>
+      <c r="E413" s="30"/>
+      <c r="F413" s="31"/>
     </row>
     <row r="414" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="26" t="s">
@@ -11553,126 +11556,126 @@
       <c r="A420" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B420" s="33"/>
-      <c r="C420" s="33"/>
-      <c r="D420" s="33"/>
-      <c r="E420" s="33"/>
-      <c r="F420" s="34"/>
+      <c r="B420" s="30"/>
+      <c r="C420" s="30"/>
+      <c r="D420" s="30"/>
+      <c r="E420" s="30"/>
+      <c r="F420" s="31"/>
     </row>
     <row r="421" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B421" s="42" t="s">
+      <c r="B421" s="40" t="s">
         <v>620</v>
       </c>
-      <c r="C421" s="33"/>
-      <c r="D421" s="33"/>
-      <c r="E421" s="33"/>
-      <c r="F421" s="34"/>
+      <c r="C421" s="30"/>
+      <c r="D421" s="30"/>
+      <c r="E421" s="30"/>
+      <c r="F421" s="31"/>
     </row>
     <row r="422" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="423" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="424" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A424" s="40" t="s">
+      <c r="A424" s="43" t="s">
         <v>621</v>
       </c>
-      <c r="B424" s="30"/>
-      <c r="C424" s="30"/>
-      <c r="D424" s="30"/>
-      <c r="E424" s="30"/>
-      <c r="F424" s="30"/>
+      <c r="B424" s="33"/>
+      <c r="C424" s="33"/>
+      <c r="D424" s="33"/>
+      <c r="E424" s="33"/>
+      <c r="F424" s="33"/>
     </row>
     <row r="425" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B425" s="33"/>
-      <c r="C425" s="33"/>
-      <c r="D425" s="33"/>
-      <c r="E425" s="33"/>
-      <c r="F425" s="34"/>
+      <c r="B425" s="30"/>
+      <c r="C425" s="30"/>
+      <c r="D425" s="30"/>
+      <c r="E425" s="30"/>
+      <c r="F425" s="31"/>
     </row>
     <row r="426" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B426" s="42" t="s">
+      <c r="B426" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C426" s="33"/>
-      <c r="D426" s="33"/>
-      <c r="E426" s="33"/>
-      <c r="F426" s="34"/>
+      <c r="C426" s="30"/>
+      <c r="D426" s="30"/>
+      <c r="E426" s="30"/>
+      <c r="F426" s="31"/>
     </row>
     <row r="427" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B427" s="42" t="s">
+      <c r="B427" s="40" t="s">
         <v>622</v>
       </c>
-      <c r="C427" s="33"/>
-      <c r="D427" s="33"/>
-      <c r="E427" s="33"/>
-      <c r="F427" s="34"/>
+      <c r="C427" s="30"/>
+      <c r="D427" s="30"/>
+      <c r="E427" s="30"/>
+      <c r="F427" s="31"/>
     </row>
     <row r="428" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B428" s="42" t="s">
+      <c r="B428" s="40" t="s">
         <v>623</v>
       </c>
-      <c r="C428" s="33"/>
-      <c r="D428" s="33"/>
-      <c r="E428" s="33"/>
-      <c r="F428" s="34"/>
+      <c r="C428" s="30"/>
+      <c r="D428" s="30"/>
+      <c r="E428" s="30"/>
+      <c r="F428" s="31"/>
     </row>
     <row r="429" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B429" s="42" t="s">
+      <c r="B429" s="40" t="s">
         <v>624</v>
       </c>
-      <c r="C429" s="33"/>
-      <c r="D429" s="33"/>
-      <c r="E429" s="33"/>
-      <c r="F429" s="34"/>
+      <c r="C429" s="30"/>
+      <c r="D429" s="30"/>
+      <c r="E429" s="30"/>
+      <c r="F429" s="31"/>
     </row>
     <row r="431" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B431" s="33"/>
-      <c r="C431" s="33"/>
-      <c r="D431" s="33"/>
-      <c r="E431" s="33"/>
-      <c r="F431" s="34"/>
+      <c r="B431" s="30"/>
+      <c r="C431" s="30"/>
+      <c r="D431" s="30"/>
+      <c r="E431" s="30"/>
+      <c r="F431" s="31"/>
     </row>
     <row r="432" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="B432" s="42" t="s">
+      <c r="B432" s="40" t="s">
         <v>625</v>
       </c>
-      <c r="C432" s="33"/>
-      <c r="D432" s="33"/>
-      <c r="E432" s="33"/>
-      <c r="F432" s="34"/>
+      <c r="C432" s="30"/>
+      <c r="D432" s="30"/>
+      <c r="E432" s="30"/>
+      <c r="F432" s="31"/>
     </row>
     <row r="433" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="434" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B434" s="33"/>
-      <c r="C434" s="33"/>
-      <c r="D434" s="33"/>
-      <c r="E434" s="33"/>
-      <c r="F434" s="34"/>
+      <c r="B434" s="30"/>
+      <c r="C434" s="30"/>
+      <c r="D434" s="30"/>
+      <c r="E434" s="30"/>
+      <c r="F434" s="31"/>
     </row>
     <row r="435" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="26" t="s">
@@ -11734,11 +11737,11 @@
       <c r="A440" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B440" s="33"/>
-      <c r="C440" s="33"/>
-      <c r="D440" s="33"/>
-      <c r="E440" s="33"/>
-      <c r="F440" s="34"/>
+      <c r="B440" s="30"/>
+      <c r="C440" s="30"/>
+      <c r="D440" s="30"/>
+      <c r="E440" s="30"/>
+      <c r="F440" s="31"/>
     </row>
     <row r="441" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="26" t="s">
@@ -11793,11 +11796,11 @@
       <c r="A446" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B446" s="33"/>
-      <c r="C446" s="33"/>
-      <c r="D446" s="33"/>
-      <c r="E446" s="33"/>
-      <c r="F446" s="34"/>
+      <c r="B446" s="30"/>
+      <c r="C446" s="30"/>
+      <c r="D446" s="30"/>
+      <c r="E446" s="30"/>
+      <c r="F446" s="31"/>
     </row>
     <row r="447" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="26" t="s">
@@ -11868,11 +11871,11 @@
       <c r="A452" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B452" s="33"/>
-      <c r="C452" s="33"/>
-      <c r="D452" s="33"/>
-      <c r="E452" s="33"/>
-      <c r="F452" s="34"/>
+      <c r="B452" s="30"/>
+      <c r="C452" s="30"/>
+      <c r="D452" s="30"/>
+      <c r="E452" s="30"/>
+      <c r="F452" s="31"/>
     </row>
     <row r="453" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="26" t="s">
@@ -11939,57 +11942,57 @@
       <c r="A459" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B459" s="33"/>
-      <c r="C459" s="33"/>
-      <c r="D459" s="33"/>
-      <c r="E459" s="33"/>
-      <c r="F459" s="34"/>
+      <c r="B459" s="30"/>
+      <c r="C459" s="30"/>
+      <c r="D459" s="30"/>
+      <c r="E459" s="30"/>
+      <c r="F459" s="31"/>
     </row>
     <row r="460" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B460" s="43" t="s">
+      <c r="B460" s="42" t="s">
         <v>652</v>
       </c>
-      <c r="C460" s="33"/>
-      <c r="D460" s="33"/>
-      <c r="E460" s="33"/>
-      <c r="F460" s="34"/>
+      <c r="C460" s="30"/>
+      <c r="D460" s="30"/>
+      <c r="E460" s="30"/>
+      <c r="F460" s="31"/>
     </row>
     <row r="461" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="462" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B462" s="33"/>
-      <c r="C462" s="33"/>
-      <c r="D462" s="33"/>
-      <c r="E462" s="33"/>
-      <c r="F462" s="34"/>
+      <c r="B462" s="30"/>
+      <c r="C462" s="30"/>
+      <c r="D462" s="30"/>
+      <c r="E462" s="30"/>
+      <c r="F462" s="31"/>
     </row>
     <row r="463" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B463" s="42" t="s">
+      <c r="B463" s="40" t="s">
         <v>653</v>
       </c>
-      <c r="C463" s="33"/>
-      <c r="D463" s="33"/>
-      <c r="E463" s="33"/>
-      <c r="F463" s="34"/>
+      <c r="C463" s="30"/>
+      <c r="D463" s="30"/>
+      <c r="E463" s="30"/>
+      <c r="F463" s="31"/>
     </row>
     <row r="464" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="465" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B465" s="33"/>
-      <c r="C465" s="33"/>
-      <c r="D465" s="33"/>
-      <c r="E465" s="33"/>
-      <c r="F465" s="34"/>
+      <c r="B465" s="30"/>
+      <c r="C465" s="30"/>
+      <c r="D465" s="30"/>
+      <c r="E465" s="30"/>
+      <c r="F465" s="31"/>
     </row>
     <row r="466" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="26" t="s">
@@ -12156,11 +12159,11 @@
       <c r="A477" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B477" s="33"/>
-      <c r="C477" s="33"/>
-      <c r="D477" s="33"/>
-      <c r="E477" s="33"/>
-      <c r="F477" s="34"/>
+      <c r="B477" s="30"/>
+      <c r="C477" s="30"/>
+      <c r="D477" s="30"/>
+      <c r="E477" s="30"/>
+      <c r="F477" s="31"/>
     </row>
     <row r="478" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="26" t="s">
@@ -12298,11 +12301,11 @@
       <c r="A490" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B490" s="33"/>
-      <c r="C490" s="33"/>
-      <c r="D490" s="33"/>
-      <c r="E490" s="33"/>
-      <c r="F490" s="34"/>
+      <c r="B490" s="30"/>
+      <c r="C490" s="30"/>
+      <c r="D490" s="30"/>
+      <c r="E490" s="30"/>
+      <c r="F490" s="31"/>
     </row>
     <row r="491" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="26" t="s">
@@ -12389,11 +12392,11 @@
       <c r="A497" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B497" s="33"/>
-      <c r="C497" s="33"/>
-      <c r="D497" s="33"/>
-      <c r="E497" s="33"/>
-      <c r="F497" s="34"/>
+      <c r="B497" s="30"/>
+      <c r="C497" s="30"/>
+      <c r="D497" s="30"/>
+      <c r="E497" s="30"/>
+      <c r="F497" s="31"/>
     </row>
     <row r="498" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="26" t="s">
@@ -12456,127 +12459,127 @@
       <c r="A503" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B503" s="33"/>
-      <c r="C503" s="33"/>
-      <c r="D503" s="33"/>
-      <c r="E503" s="33"/>
-      <c r="F503" s="34"/>
+      <c r="B503" s="30"/>
+      <c r="C503" s="30"/>
+      <c r="D503" s="30"/>
+      <c r="E503" s="30"/>
+      <c r="F503" s="31"/>
     </row>
     <row r="504" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B504" s="42" t="s">
+      <c r="B504" s="40" t="s">
         <v>700</v>
       </c>
-      <c r="C504" s="33"/>
-      <c r="D504" s="33"/>
-      <c r="E504" s="33"/>
-      <c r="F504" s="34"/>
+      <c r="C504" s="30"/>
+      <c r="D504" s="30"/>
+      <c r="E504" s="30"/>
+      <c r="F504" s="31"/>
     </row>
     <row r="505" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="506" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="507" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A507" s="40" t="s">
+      <c r="A507" s="43" t="s">
         <v>701</v>
       </c>
-      <c r="B507" s="30"/>
-      <c r="C507" s="30"/>
-      <c r="D507" s="30"/>
-      <c r="E507" s="30"/>
-      <c r="F507" s="30"/>
+      <c r="B507" s="33"/>
+      <c r="C507" s="33"/>
+      <c r="D507" s="33"/>
+      <c r="E507" s="33"/>
+      <c r="F507" s="33"/>
     </row>
     <row r="508" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B508" s="33"/>
-      <c r="C508" s="33"/>
-      <c r="D508" s="33"/>
-      <c r="E508" s="33"/>
-      <c r="F508" s="34"/>
+      <c r="B508" s="30"/>
+      <c r="C508" s="30"/>
+      <c r="D508" s="30"/>
+      <c r="E508" s="30"/>
+      <c r="F508" s="31"/>
     </row>
     <row r="509" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B509" s="42" t="s">
+      <c r="B509" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="C509" s="33"/>
-      <c r="D509" s="33"/>
-      <c r="E509" s="33"/>
-      <c r="F509" s="34"/>
+      <c r="C509" s="30"/>
+      <c r="D509" s="30"/>
+      <c r="E509" s="30"/>
+      <c r="F509" s="31"/>
     </row>
     <row r="510" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B510" s="42" t="s">
+      <c r="B510" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C510" s="33"/>
-      <c r="D510" s="33"/>
-      <c r="E510" s="33"/>
-      <c r="F510" s="34"/>
+      <c r="C510" s="30"/>
+      <c r="D510" s="30"/>
+      <c r="E510" s="30"/>
+      <c r="F510" s="31"/>
     </row>
     <row r="511" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B511" s="42" t="s">
+      <c r="B511" s="40" t="s">
         <v>702</v>
       </c>
-      <c r="C511" s="33"/>
-      <c r="D511" s="33"/>
-      <c r="E511" s="33"/>
-      <c r="F511" s="34"/>
+      <c r="C511" s="30"/>
+      <c r="D511" s="30"/>
+      <c r="E511" s="30"/>
+      <c r="F511" s="31"/>
     </row>
     <row r="512" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B512" s="42" t="s">
+      <c r="B512" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="C512" s="33"/>
-      <c r="D512" s="33"/>
-      <c r="E512" s="33"/>
-      <c r="F512" s="34"/>
+      <c r="C512" s="30"/>
+      <c r="D512" s="30"/>
+      <c r="E512" s="30"/>
+      <c r="F512" s="31"/>
     </row>
     <row r="513" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="514" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B514" s="33"/>
-      <c r="C514" s="33"/>
-      <c r="D514" s="33"/>
-      <c r="E514" s="33"/>
-      <c r="F514" s="34"/>
+      <c r="B514" s="30"/>
+      <c r="C514" s="30"/>
+      <c r="D514" s="30"/>
+      <c r="E514" s="30"/>
+      <c r="F514" s="31"/>
     </row>
     <row r="515" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="B515" s="42" t="s">
+      <c r="B515" s="40" t="s">
         <v>704</v>
       </c>
-      <c r="C515" s="33"/>
-      <c r="D515" s="33"/>
-      <c r="E515" s="33"/>
-      <c r="F515" s="34"/>
+      <c r="C515" s="30"/>
+      <c r="D515" s="30"/>
+      <c r="E515" s="30"/>
+      <c r="F515" s="31"/>
     </row>
     <row r="516" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="517" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B517" s="33"/>
-      <c r="C517" s="33"/>
-      <c r="D517" s="33"/>
-      <c r="E517" s="33"/>
-      <c r="F517" s="34"/>
+      <c r="B517" s="30"/>
+      <c r="C517" s="30"/>
+      <c r="D517" s="30"/>
+      <c r="E517" s="30"/>
+      <c r="F517" s="31"/>
     </row>
     <row r="518" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="26" t="s">
@@ -12639,11 +12642,11 @@
       <c r="A523" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B523" s="33"/>
-      <c r="C523" s="33"/>
-      <c r="D523" s="33"/>
-      <c r="E523" s="33"/>
-      <c r="F523" s="34"/>
+      <c r="B523" s="30"/>
+      <c r="C523" s="30"/>
+      <c r="D523" s="30"/>
+      <c r="E523" s="30"/>
+      <c r="F523" s="31"/>
     </row>
     <row r="524" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="26" t="s">
@@ -12686,11 +12689,11 @@
       <c r="A528" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B528" s="33"/>
-      <c r="C528" s="33"/>
-      <c r="D528" s="33"/>
-      <c r="E528" s="33"/>
-      <c r="F528" s="34"/>
+      <c r="B528" s="30"/>
+      <c r="C528" s="30"/>
+      <c r="D528" s="30"/>
+      <c r="E528" s="30"/>
+      <c r="F528" s="31"/>
     </row>
     <row r="529" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="26" t="s">
@@ -12824,11 +12827,11 @@
       <c r="A538" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B538" s="33"/>
-      <c r="C538" s="33"/>
-      <c r="D538" s="33"/>
-      <c r="E538" s="33"/>
-      <c r="F538" s="34"/>
+      <c r="B538" s="30"/>
+      <c r="C538" s="30"/>
+      <c r="D538" s="30"/>
+      <c r="E538" s="30"/>
+      <c r="F538" s="31"/>
     </row>
     <row r="539" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="26" t="s">
@@ -12882,57 +12885,57 @@
       <c r="A544" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B544" s="33"/>
-      <c r="C544" s="33"/>
-      <c r="D544" s="33"/>
-      <c r="E544" s="33"/>
-      <c r="F544" s="34"/>
+      <c r="B544" s="30"/>
+      <c r="C544" s="30"/>
+      <c r="D544" s="30"/>
+      <c r="E544" s="30"/>
+      <c r="F544" s="31"/>
     </row>
     <row r="545" spans="1:6" ht="142.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B545" s="43" t="s">
+      <c r="B545" s="42" t="s">
         <v>736</v>
       </c>
-      <c r="C545" s="33"/>
-      <c r="D545" s="33"/>
-      <c r="E545" s="33"/>
-      <c r="F545" s="34"/>
+      <c r="C545" s="30"/>
+      <c r="D545" s="30"/>
+      <c r="E545" s="30"/>
+      <c r="F545" s="31"/>
     </row>
     <row r="546" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="547" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B547" s="33"/>
-      <c r="C547" s="33"/>
-      <c r="D547" s="33"/>
-      <c r="E547" s="33"/>
-      <c r="F547" s="34"/>
+      <c r="B547" s="30"/>
+      <c r="C547" s="30"/>
+      <c r="D547" s="30"/>
+      <c r="E547" s="30"/>
+      <c r="F547" s="31"/>
     </row>
     <row r="548" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B548" s="42" t="s">
+      <c r="B548" s="40" t="s">
         <v>737</v>
       </c>
-      <c r="C548" s="33"/>
-      <c r="D548" s="33"/>
-      <c r="E548" s="33"/>
-      <c r="F548" s="34"/>
+      <c r="C548" s="30"/>
+      <c r="D548" s="30"/>
+      <c r="E548" s="30"/>
+      <c r="F548" s="31"/>
     </row>
     <row r="549" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="550" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B550" s="33"/>
-      <c r="C550" s="33"/>
-      <c r="D550" s="33"/>
-      <c r="E550" s="33"/>
-      <c r="F550" s="34"/>
+      <c r="B550" s="30"/>
+      <c r="C550" s="30"/>
+      <c r="D550" s="30"/>
+      <c r="E550" s="30"/>
+      <c r="F550" s="31"/>
     </row>
     <row r="551" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="26" t="s">
@@ -13066,11 +13069,11 @@
       <c r="A560" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B560" s="33"/>
-      <c r="C560" s="33"/>
-      <c r="D560" s="33"/>
-      <c r="E560" s="33"/>
-      <c r="F560" s="34"/>
+      <c r="B560" s="30"/>
+      <c r="C560" s="30"/>
+      <c r="D560" s="30"/>
+      <c r="E560" s="30"/>
+      <c r="F560" s="31"/>
     </row>
     <row r="561" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="26" t="s">
@@ -13173,11 +13176,11 @@
       <c r="A570" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B570" s="33"/>
-      <c r="C570" s="33"/>
-      <c r="D570" s="33"/>
-      <c r="E570" s="33"/>
-      <c r="F570" s="34"/>
+      <c r="B570" s="30"/>
+      <c r="C570" s="30"/>
+      <c r="D570" s="30"/>
+      <c r="E570" s="30"/>
+      <c r="F570" s="31"/>
     </row>
     <row r="571" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="26" t="s">
@@ -13248,11 +13251,11 @@
       <c r="A576" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B576" s="33"/>
-      <c r="C576" s="33"/>
-      <c r="D576" s="33"/>
-      <c r="E576" s="33"/>
-      <c r="F576" s="34"/>
+      <c r="B576" s="30"/>
+      <c r="C576" s="30"/>
+      <c r="D576" s="30"/>
+      <c r="E576" s="30"/>
+      <c r="F576" s="31"/>
     </row>
     <row r="577" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="26" t="s">
@@ -13329,126 +13332,126 @@
       <c r="A583" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B583" s="33"/>
-      <c r="C583" s="33"/>
-      <c r="D583" s="33"/>
-      <c r="E583" s="33"/>
-      <c r="F583" s="34"/>
+      <c r="B583" s="30"/>
+      <c r="C583" s="30"/>
+      <c r="D583" s="30"/>
+      <c r="E583" s="30"/>
+      <c r="F583" s="31"/>
     </row>
     <row r="584" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B584" s="42" t="s">
+      <c r="B584" s="40" t="s">
         <v>782</v>
       </c>
-      <c r="C584" s="33"/>
-      <c r="D584" s="33"/>
-      <c r="E584" s="33"/>
-      <c r="F584" s="34"/>
+      <c r="C584" s="30"/>
+      <c r="D584" s="30"/>
+      <c r="E584" s="30"/>
+      <c r="F584" s="31"/>
     </row>
     <row r="586" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="587" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A587" s="40" t="s">
+      <c r="A587" s="43" t="s">
         <v>783</v>
       </c>
-      <c r="B587" s="30"/>
-      <c r="C587" s="30"/>
-      <c r="D587" s="30"/>
-      <c r="E587" s="30"/>
-      <c r="F587" s="30"/>
+      <c r="B587" s="33"/>
+      <c r="C587" s="33"/>
+      <c r="D587" s="33"/>
+      <c r="E587" s="33"/>
+      <c r="F587" s="33"/>
     </row>
     <row r="588" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B588" s="33"/>
-      <c r="C588" s="33"/>
-      <c r="D588" s="33"/>
-      <c r="E588" s="33"/>
-      <c r="F588" s="34"/>
+      <c r="B588" s="30"/>
+      <c r="C588" s="30"/>
+      <c r="D588" s="30"/>
+      <c r="E588" s="30"/>
+      <c r="F588" s="31"/>
     </row>
     <row r="589" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B589" s="42" t="s">
+      <c r="B589" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C589" s="33"/>
-      <c r="D589" s="33"/>
-      <c r="E589" s="33"/>
-      <c r="F589" s="34"/>
+      <c r="C589" s="30"/>
+      <c r="D589" s="30"/>
+      <c r="E589" s="30"/>
+      <c r="F589" s="31"/>
     </row>
     <row r="590" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B590" s="42" t="s">
+      <c r="B590" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C590" s="33"/>
-      <c r="D590" s="33"/>
-      <c r="E590" s="33"/>
-      <c r="F590" s="34"/>
+      <c r="C590" s="30"/>
+      <c r="D590" s="30"/>
+      <c r="E590" s="30"/>
+      <c r="F590" s="31"/>
     </row>
     <row r="591" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B591" s="42" t="s">
+      <c r="B591" s="40" t="s">
         <v>784</v>
       </c>
-      <c r="C591" s="33"/>
-      <c r="D591" s="33"/>
-      <c r="E591" s="33"/>
-      <c r="F591" s="34"/>
+      <c r="C591" s="30"/>
+      <c r="D591" s="30"/>
+      <c r="E591" s="30"/>
+      <c r="F591" s="31"/>
     </row>
     <row r="592" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B592" s="42" t="s">
+      <c r="B592" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="C592" s="33"/>
-      <c r="D592" s="33"/>
-      <c r="E592" s="33"/>
-      <c r="F592" s="34"/>
+      <c r="C592" s="30"/>
+      <c r="D592" s="30"/>
+      <c r="E592" s="30"/>
+      <c r="F592" s="31"/>
     </row>
     <row r="593" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="594" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B594" s="33"/>
-      <c r="C594" s="33"/>
-      <c r="D594" s="33"/>
-      <c r="E594" s="33"/>
-      <c r="F594" s="34"/>
+      <c r="B594" s="30"/>
+      <c r="C594" s="30"/>
+      <c r="D594" s="30"/>
+      <c r="E594" s="30"/>
+      <c r="F594" s="31"/>
     </row>
     <row r="595" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="B595" s="42" t="s">
+      <c r="B595" s="40" t="s">
         <v>704</v>
       </c>
-      <c r="C595" s="33"/>
-      <c r="D595" s="33"/>
-      <c r="E595" s="33"/>
-      <c r="F595" s="34"/>
+      <c r="C595" s="30"/>
+      <c r="D595" s="30"/>
+      <c r="E595" s="30"/>
+      <c r="F595" s="31"/>
     </row>
     <row r="596" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="597" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B597" s="33"/>
-      <c r="C597" s="33"/>
-      <c r="D597" s="33"/>
-      <c r="E597" s="33"/>
-      <c r="F597" s="34"/>
+      <c r="B597" s="30"/>
+      <c r="C597" s="30"/>
+      <c r="D597" s="30"/>
+      <c r="E597" s="30"/>
+      <c r="F597" s="31"/>
     </row>
     <row r="598" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="26" t="s">
@@ -13483,11 +13486,11 @@
       <c r="A601" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B601" s="33"/>
-      <c r="C601" s="33"/>
-      <c r="D601" s="33"/>
-      <c r="E601" s="33"/>
-      <c r="F601" s="34"/>
+      <c r="B601" s="30"/>
+      <c r="C601" s="30"/>
+      <c r="D601" s="30"/>
+      <c r="E601" s="30"/>
+      <c r="F601" s="31"/>
     </row>
     <row r="602" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="26" t="s">
@@ -13530,11 +13533,11 @@
       <c r="A606" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B606" s="33"/>
-      <c r="C606" s="33"/>
-      <c r="D606" s="33"/>
-      <c r="E606" s="33"/>
-      <c r="F606" s="34"/>
+      <c r="B606" s="30"/>
+      <c r="C606" s="30"/>
+      <c r="D606" s="30"/>
+      <c r="E606" s="30"/>
+      <c r="F606" s="31"/>
     </row>
     <row r="607" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="26" t="s">
@@ -13589,11 +13592,11 @@
       <c r="A611" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B611" s="33"/>
-      <c r="C611" s="33"/>
-      <c r="D611" s="33"/>
-      <c r="E611" s="33"/>
-      <c r="F611" s="34"/>
+      <c r="B611" s="30"/>
+      <c r="C611" s="30"/>
+      <c r="D611" s="30"/>
+      <c r="E611" s="30"/>
+      <c r="F611" s="31"/>
     </row>
     <row r="612" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="26" t="s">
@@ -13648,56 +13651,56 @@
       <c r="A617" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B617" s="33"/>
-      <c r="C617" s="33"/>
-      <c r="D617" s="33"/>
-      <c r="E617" s="33"/>
-      <c r="F617" s="34"/>
+      <c r="B617" s="30"/>
+      <c r="C617" s="30"/>
+      <c r="D617" s="30"/>
+      <c r="E617" s="30"/>
+      <c r="F617" s="31"/>
     </row>
     <row r="618" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B618" s="43" t="s">
+      <c r="B618" s="42" t="s">
         <v>796</v>
       </c>
-      <c r="C618" s="33"/>
-      <c r="D618" s="33"/>
-      <c r="E618" s="33"/>
-      <c r="F618" s="34"/>
+      <c r="C618" s="30"/>
+      <c r="D618" s="30"/>
+      <c r="E618" s="30"/>
+      <c r="F618" s="31"/>
     </row>
     <row r="619" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="620" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B620" s="33"/>
-      <c r="C620" s="33"/>
-      <c r="D620" s="33"/>
-      <c r="E620" s="33"/>
-      <c r="F620" s="34"/>
+      <c r="B620" s="30"/>
+      <c r="C620" s="30"/>
+      <c r="D620" s="30"/>
+      <c r="E620" s="30"/>
+      <c r="F620" s="31"/>
     </row>
     <row r="621" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B621" s="42" t="s">
+      <c r="B621" s="40" t="s">
         <v>797</v>
       </c>
-      <c r="C621" s="33"/>
-      <c r="D621" s="33"/>
-      <c r="E621" s="33"/>
-      <c r="F621" s="34"/>
+      <c r="C621" s="30"/>
+      <c r="D621" s="30"/>
+      <c r="E621" s="30"/>
+      <c r="F621" s="31"/>
     </row>
     <row r="623" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B623" s="33"/>
-      <c r="C623" s="33"/>
-      <c r="D623" s="33"/>
-      <c r="E623" s="33"/>
-      <c r="F623" s="34"/>
+      <c r="B623" s="30"/>
+      <c r="C623" s="30"/>
+      <c r="D623" s="30"/>
+      <c r="E623" s="30"/>
+      <c r="F623" s="31"/>
     </row>
     <row r="624" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="26" t="s">
@@ -13831,11 +13834,11 @@
       <c r="A633" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B633" s="33"/>
-      <c r="C633" s="33"/>
-      <c r="D633" s="33"/>
-      <c r="E633" s="33"/>
-      <c r="F633" s="34"/>
+      <c r="B633" s="30"/>
+      <c r="C633" s="30"/>
+      <c r="D633" s="30"/>
+      <c r="E633" s="30"/>
+      <c r="F633" s="31"/>
     </row>
     <row r="634" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="26" t="s">
@@ -13961,11 +13964,11 @@
       <c r="A645" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B645" s="33"/>
-      <c r="C645" s="33"/>
-      <c r="D645" s="33"/>
-      <c r="E645" s="33"/>
-      <c r="F645" s="34"/>
+      <c r="B645" s="30"/>
+      <c r="C645" s="30"/>
+      <c r="D645" s="30"/>
+      <c r="E645" s="30"/>
+      <c r="F645" s="31"/>
     </row>
     <row r="646" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="26" t="s">
@@ -14035,11 +14038,11 @@
       <c r="A651" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B651" s="33"/>
-      <c r="C651" s="33"/>
-      <c r="D651" s="33"/>
-      <c r="E651" s="33"/>
-      <c r="F651" s="34"/>
+      <c r="B651" s="30"/>
+      <c r="C651" s="30"/>
+      <c r="D651" s="30"/>
+      <c r="E651" s="30"/>
+      <c r="F651" s="31"/>
     </row>
     <row r="652" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="26" t="s">
@@ -14087,126 +14090,126 @@
       <c r="A656" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B656" s="33"/>
-      <c r="C656" s="33"/>
-      <c r="D656" s="33"/>
-      <c r="E656" s="33"/>
-      <c r="F656" s="34"/>
+      <c r="B656" s="30"/>
+      <c r="C656" s="30"/>
+      <c r="D656" s="30"/>
+      <c r="E656" s="30"/>
+      <c r="F656" s="31"/>
     </row>
     <row r="657" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B657" s="42" t="s">
+      <c r="B657" s="40" t="s">
         <v>829</v>
       </c>
-      <c r="C657" s="33"/>
-      <c r="D657" s="33"/>
-      <c r="E657" s="33"/>
-      <c r="F657" s="34"/>
+      <c r="C657" s="30"/>
+      <c r="D657" s="30"/>
+      <c r="E657" s="30"/>
+      <c r="F657" s="31"/>
     </row>
     <row r="658" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="659" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="660" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A660" s="40" t="s">
+      <c r="A660" s="43" t="s">
         <v>830</v>
       </c>
-      <c r="B660" s="30"/>
-      <c r="C660" s="30"/>
-      <c r="D660" s="30"/>
-      <c r="E660" s="30"/>
-      <c r="F660" s="30"/>
+      <c r="B660" s="33"/>
+      <c r="C660" s="33"/>
+      <c r="D660" s="33"/>
+      <c r="E660" s="33"/>
+      <c r="F660" s="33"/>
     </row>
     <row r="661" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B661" s="33"/>
-      <c r="C661" s="33"/>
-      <c r="D661" s="33"/>
-      <c r="E661" s="33"/>
-      <c r="F661" s="34"/>
+      <c r="B661" s="30"/>
+      <c r="C661" s="30"/>
+      <c r="D661" s="30"/>
+      <c r="E661" s="30"/>
+      <c r="F661" s="31"/>
     </row>
     <row r="662" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B662" s="42" t="s">
+      <c r="B662" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C662" s="33"/>
-      <c r="D662" s="33"/>
-      <c r="E662" s="33"/>
-      <c r="F662" s="34"/>
+      <c r="C662" s="30"/>
+      <c r="D662" s="30"/>
+      <c r="E662" s="30"/>
+      <c r="F662" s="31"/>
     </row>
     <row r="663" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B663" s="42" t="s">
+      <c r="B663" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C663" s="33"/>
-      <c r="D663" s="33"/>
-      <c r="E663" s="33"/>
-      <c r="F663" s="34"/>
+      <c r="C663" s="30"/>
+      <c r="D663" s="30"/>
+      <c r="E663" s="30"/>
+      <c r="F663" s="31"/>
     </row>
     <row r="664" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B664" s="42" t="s">
+      <c r="B664" s="40" t="s">
         <v>831</v>
       </c>
-      <c r="C664" s="33"/>
-      <c r="D664" s="33"/>
-      <c r="E664" s="33"/>
-      <c r="F664" s="34"/>
+      <c r="C664" s="30"/>
+      <c r="D664" s="30"/>
+      <c r="E664" s="30"/>
+      <c r="F664" s="31"/>
     </row>
     <row r="665" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B665" s="42" t="s">
+      <c r="B665" s="40" t="s">
         <v>832</v>
       </c>
-      <c r="C665" s="33"/>
-      <c r="D665" s="33"/>
-      <c r="E665" s="33"/>
-      <c r="F665" s="34"/>
+      <c r="C665" s="30"/>
+      <c r="D665" s="30"/>
+      <c r="E665" s="30"/>
+      <c r="F665" s="31"/>
     </row>
     <row r="666" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="667" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B667" s="33"/>
-      <c r="C667" s="33"/>
-      <c r="D667" s="33"/>
-      <c r="E667" s="33"/>
-      <c r="F667" s="34"/>
+      <c r="B667" s="30"/>
+      <c r="C667" s="30"/>
+      <c r="D667" s="30"/>
+      <c r="E667" s="30"/>
+      <c r="F667" s="31"/>
     </row>
     <row r="668" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="B668" s="42" t="s">
+      <c r="B668" s="40" t="s">
         <v>487</v>
       </c>
-      <c r="C668" s="33"/>
-      <c r="D668" s="33"/>
-      <c r="E668" s="33"/>
-      <c r="F668" s="34"/>
+      <c r="C668" s="30"/>
+      <c r="D668" s="30"/>
+      <c r="E668" s="30"/>
+      <c r="F668" s="31"/>
     </row>
     <row r="670" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B670" s="33"/>
-      <c r="C670" s="33"/>
-      <c r="D670" s="33"/>
-      <c r="E670" s="33"/>
-      <c r="F670" s="34"/>
+      <c r="B670" s="30"/>
+      <c r="C670" s="30"/>
+      <c r="D670" s="30"/>
+      <c r="E670" s="30"/>
+      <c r="F670" s="31"/>
     </row>
     <row r="671" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="26" t="s">
@@ -14240,11 +14243,11 @@
       <c r="A674" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B674" s="33"/>
-      <c r="C674" s="33"/>
-      <c r="D674" s="33"/>
-      <c r="E674" s="33"/>
-      <c r="F674" s="34"/>
+      <c r="B674" s="30"/>
+      <c r="C674" s="30"/>
+      <c r="D674" s="30"/>
+      <c r="E674" s="30"/>
+      <c r="F674" s="31"/>
     </row>
     <row r="675" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="26" t="s">
@@ -14287,11 +14290,11 @@
       <c r="A679" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B679" s="33"/>
-      <c r="C679" s="33"/>
-      <c r="D679" s="33"/>
-      <c r="E679" s="33"/>
-      <c r="F679" s="34"/>
+      <c r="B679" s="30"/>
+      <c r="C679" s="30"/>
+      <c r="D679" s="30"/>
+      <c r="E679" s="30"/>
+      <c r="F679" s="31"/>
     </row>
     <row r="680" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="26" t="s">
@@ -14377,11 +14380,11 @@
       <c r="A686" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B686" s="33"/>
-      <c r="C686" s="33"/>
-      <c r="D686" s="33"/>
-      <c r="E686" s="33"/>
-      <c r="F686" s="34"/>
+      <c r="B686" s="30"/>
+      <c r="C686" s="30"/>
+      <c r="D686" s="30"/>
+      <c r="E686" s="30"/>
+      <c r="F686" s="31"/>
     </row>
     <row r="687" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="26" t="s">
@@ -14448,56 +14451,56 @@
       <c r="A693" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B693" s="33"/>
-      <c r="C693" s="33"/>
-      <c r="D693" s="33"/>
-      <c r="E693" s="33"/>
-      <c r="F693" s="34"/>
+      <c r="B693" s="30"/>
+      <c r="C693" s="30"/>
+      <c r="D693" s="30"/>
+      <c r="E693" s="30"/>
+      <c r="F693" s="31"/>
     </row>
     <row r="694" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B694" s="43" t="s">
+      <c r="B694" s="42" t="s">
         <v>849</v>
       </c>
-      <c r="C694" s="33"/>
-      <c r="D694" s="33"/>
-      <c r="E694" s="33"/>
-      <c r="F694" s="34"/>
+      <c r="C694" s="30"/>
+      <c r="D694" s="30"/>
+      <c r="E694" s="30"/>
+      <c r="F694" s="31"/>
     </row>
     <row r="696" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B696" s="33"/>
-      <c r="C696" s="33"/>
-      <c r="D696" s="33"/>
-      <c r="E696" s="33"/>
-      <c r="F696" s="34"/>
+      <c r="B696" s="30"/>
+      <c r="C696" s="30"/>
+      <c r="D696" s="30"/>
+      <c r="E696" s="30"/>
+      <c r="F696" s="31"/>
     </row>
     <row r="697" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B697" s="42" t="s">
+      <c r="B697" s="40" t="s">
         <v>850</v>
       </c>
-      <c r="C697" s="33"/>
-      <c r="D697" s="33"/>
-      <c r="E697" s="33"/>
-      <c r="F697" s="34"/>
+      <c r="C697" s="30"/>
+      <c r="D697" s="30"/>
+      <c r="E697" s="30"/>
+      <c r="F697" s="31"/>
     </row>
     <row r="698" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="699" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B699" s="33"/>
-      <c r="C699" s="33"/>
-      <c r="D699" s="33"/>
-      <c r="E699" s="33"/>
-      <c r="F699" s="34"/>
+      <c r="B699" s="30"/>
+      <c r="C699" s="30"/>
+      <c r="D699" s="30"/>
+      <c r="E699" s="30"/>
+      <c r="F699" s="31"/>
     </row>
     <row r="700" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="26" t="s">
@@ -14631,11 +14634,11 @@
       <c r="A709" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B709" s="33"/>
-      <c r="C709" s="33"/>
-      <c r="D709" s="33"/>
-      <c r="E709" s="33"/>
-      <c r="F709" s="34"/>
+      <c r="B709" s="30"/>
+      <c r="C709" s="30"/>
+      <c r="D709" s="30"/>
+      <c r="E709" s="30"/>
+      <c r="F709" s="31"/>
     </row>
     <row r="710" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="26" t="s">
@@ -14761,11 +14764,11 @@
       <c r="A721" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B721" s="33"/>
-      <c r="C721" s="33"/>
-      <c r="D721" s="33"/>
-      <c r="E721" s="33"/>
-      <c r="F721" s="34"/>
+      <c r="B721" s="30"/>
+      <c r="C721" s="30"/>
+      <c r="D721" s="30"/>
+      <c r="E721" s="30"/>
+      <c r="F721" s="31"/>
     </row>
     <row r="722" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="26" t="s">
@@ -14884,11 +14887,11 @@
       <c r="A730" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B730" s="33"/>
-      <c r="C730" s="33"/>
-      <c r="D730" s="33"/>
-      <c r="E730" s="33"/>
-      <c r="F730" s="34"/>
+      <c r="B730" s="30"/>
+      <c r="C730" s="30"/>
+      <c r="D730" s="30"/>
+      <c r="E730" s="30"/>
+      <c r="F730" s="31"/>
     </row>
     <row r="731" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="26" t="s">
@@ -14965,123 +14968,123 @@
       <c r="A737" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B737" s="33"/>
-      <c r="C737" s="33"/>
-      <c r="D737" s="33"/>
-      <c r="E737" s="33"/>
-      <c r="F737" s="34"/>
+      <c r="B737" s="30"/>
+      <c r="C737" s="30"/>
+      <c r="D737" s="30"/>
+      <c r="E737" s="30"/>
+      <c r="F737" s="31"/>
     </row>
     <row r="738" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A738" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B738" s="42" t="s">
+      <c r="B738" s="40" t="s">
         <v>892</v>
       </c>
-      <c r="C738" s="33"/>
-      <c r="D738" s="33"/>
-      <c r="E738" s="33"/>
-      <c r="F738" s="34"/>
+      <c r="C738" s="30"/>
+      <c r="D738" s="30"/>
+      <c r="E738" s="30"/>
+      <c r="F738" s="31"/>
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A741" s="40" t="s">
+      <c r="A741" s="43" t="s">
         <v>893</v>
       </c>
-      <c r="B741" s="30"/>
-      <c r="C741" s="30"/>
-      <c r="D741" s="30"/>
-      <c r="E741" s="30"/>
-      <c r="F741" s="30"/>
+      <c r="B741" s="33"/>
+      <c r="C741" s="33"/>
+      <c r="D741" s="33"/>
+      <c r="E741" s="33"/>
+      <c r="F741" s="33"/>
     </row>
     <row r="742" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A742" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B742" s="33"/>
-      <c r="C742" s="33"/>
-      <c r="D742" s="33"/>
-      <c r="E742" s="33"/>
-      <c r="F742" s="34"/>
+      <c r="B742" s="30"/>
+      <c r="C742" s="30"/>
+      <c r="D742" s="30"/>
+      <c r="E742" s="30"/>
+      <c r="F742" s="31"/>
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A743" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B743" s="42" t="s">
+      <c r="B743" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C743" s="33"/>
-      <c r="D743" s="33"/>
-      <c r="E743" s="33"/>
-      <c r="F743" s="34"/>
+      <c r="C743" s="30"/>
+      <c r="D743" s="30"/>
+      <c r="E743" s="30"/>
+      <c r="F743" s="31"/>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A744" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B744" s="42" t="s">
+      <c r="B744" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C744" s="33"/>
-      <c r="D744" s="33"/>
-      <c r="E744" s="33"/>
-      <c r="F744" s="34"/>
+      <c r="C744" s="30"/>
+      <c r="D744" s="30"/>
+      <c r="E744" s="30"/>
+      <c r="F744" s="31"/>
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A745" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B745" s="42" t="s">
+      <c r="B745" s="40" t="s">
         <v>894</v>
       </c>
-      <c r="C745" s="33"/>
-      <c r="D745" s="33"/>
-      <c r="E745" s="33"/>
-      <c r="F745" s="34"/>
+      <c r="C745" s="30"/>
+      <c r="D745" s="30"/>
+      <c r="E745" s="30"/>
+      <c r="F745" s="31"/>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A746" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B746" s="42" t="s">
+      <c r="B746" s="40" t="s">
         <v>895</v>
       </c>
-      <c r="C746" s="33"/>
-      <c r="D746" s="33"/>
-      <c r="E746" s="33"/>
-      <c r="F746" s="34"/>
+      <c r="C746" s="30"/>
+      <c r="D746" s="30"/>
+      <c r="E746" s="30"/>
+      <c r="F746" s="31"/>
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A748" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B748" s="33"/>
-      <c r="C748" s="33"/>
-      <c r="D748" s="33"/>
-      <c r="E748" s="33"/>
-      <c r="F748" s="34"/>
+      <c r="B748" s="30"/>
+      <c r="C748" s="30"/>
+      <c r="D748" s="30"/>
+      <c r="E748" s="30"/>
+      <c r="F748" s="31"/>
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A749" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B749" s="42" t="s">
+      <c r="B749" s="40" t="s">
         <v>896</v>
       </c>
-      <c r="C749" s="33"/>
-      <c r="D749" s="33"/>
-      <c r="E749" s="33"/>
-      <c r="F749" s="34"/>
+      <c r="C749" s="30"/>
+      <c r="D749" s="30"/>
+      <c r="E749" s="30"/>
+      <c r="F749" s="31"/>
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A751" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B751" s="33"/>
-      <c r="C751" s="33"/>
-      <c r="D751" s="33"/>
-      <c r="E751" s="33"/>
-      <c r="F751" s="34"/>
+      <c r="B751" s="30"/>
+      <c r="C751" s="30"/>
+      <c r="D751" s="30"/>
+      <c r="E751" s="30"/>
+      <c r="F751" s="31"/>
     </row>
     <row r="752" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A752" s="26" t="s">
@@ -15132,11 +15135,11 @@
       <c r="A757" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B757" s="33"/>
-      <c r="C757" s="33"/>
-      <c r="D757" s="33"/>
-      <c r="E757" s="33"/>
-      <c r="F757" s="34"/>
+      <c r="B757" s="30"/>
+      <c r="C757" s="30"/>
+      <c r="D757" s="30"/>
+      <c r="E757" s="30"/>
+      <c r="F757" s="31"/>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A758" s="26" t="s">
@@ -15175,11 +15178,11 @@
       <c r="A763" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B763" s="33"/>
-      <c r="C763" s="33"/>
-      <c r="D763" s="33"/>
-      <c r="E763" s="33"/>
-      <c r="F763" s="34"/>
+      <c r="B763" s="30"/>
+      <c r="C763" s="30"/>
+      <c r="D763" s="30"/>
+      <c r="E763" s="30"/>
+      <c r="F763" s="31"/>
     </row>
     <row r="764" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="26" t="s">
@@ -15255,11 +15258,11 @@
       <c r="A770" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B770" s="33"/>
-      <c r="C770" s="33"/>
-      <c r="D770" s="33"/>
-      <c r="E770" s="33"/>
-      <c r="F770" s="34"/>
+      <c r="B770" s="30"/>
+      <c r="C770" s="30"/>
+      <c r="D770" s="30"/>
+      <c r="E770" s="30"/>
+      <c r="F770" s="31"/>
     </row>
     <row r="771" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="26" t="s">
@@ -15301,56 +15304,56 @@
       <c r="A777" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B777" s="33"/>
-      <c r="C777" s="33"/>
-      <c r="D777" s="33"/>
-      <c r="E777" s="33"/>
-      <c r="F777" s="34"/>
+      <c r="B777" s="30"/>
+      <c r="C777" s="30"/>
+      <c r="D777" s="30"/>
+      <c r="E777" s="30"/>
+      <c r="F777" s="31"/>
     </row>
     <row r="778" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B778" s="42" t="s">
+      <c r="B778" s="40" t="s">
         <v>922</v>
       </c>
-      <c r="C778" s="33"/>
-      <c r="D778" s="33"/>
-      <c r="E778" s="33"/>
-      <c r="F778" s="34"/>
+      <c r="C778" s="30"/>
+      <c r="D778" s="30"/>
+      <c r="E778" s="30"/>
+      <c r="F778" s="31"/>
     </row>
     <row r="779" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="780" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A780" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B780" s="33"/>
-      <c r="C780" s="33"/>
-      <c r="D780" s="33"/>
-      <c r="E780" s="33"/>
-      <c r="F780" s="34"/>
+      <c r="B780" s="30"/>
+      <c r="C780" s="30"/>
+      <c r="D780" s="30"/>
+      <c r="E780" s="30"/>
+      <c r="F780" s="31"/>
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A781" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B781" s="42" t="s">
+      <c r="B781" s="40" t="s">
         <v>923</v>
       </c>
-      <c r="C781" s="33"/>
-      <c r="D781" s="33"/>
-      <c r="E781" s="33"/>
-      <c r="F781" s="34"/>
+      <c r="C781" s="30"/>
+      <c r="D781" s="30"/>
+      <c r="E781" s="30"/>
+      <c r="F781" s="31"/>
     </row>
     <row r="783" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A783" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B783" s="33"/>
-      <c r="C783" s="33"/>
-      <c r="D783" s="33"/>
-      <c r="E783" s="33"/>
-      <c r="F783" s="34"/>
+      <c r="B783" s="30"/>
+      <c r="C783" s="30"/>
+      <c r="D783" s="30"/>
+      <c r="E783" s="30"/>
+      <c r="F783" s="31"/>
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A784" s="26" t="s">
@@ -15440,11 +15443,11 @@
       <c r="A791" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B791" s="33"/>
-      <c r="C791" s="33"/>
-      <c r="D791" s="33"/>
-      <c r="E791" s="33"/>
-      <c r="F791" s="34"/>
+      <c r="B791" s="30"/>
+      <c r="C791" s="30"/>
+      <c r="D791" s="30"/>
+      <c r="E791" s="30"/>
+      <c r="F791" s="31"/>
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A792" s="26" t="s">
@@ -15514,11 +15517,11 @@
       <c r="A801" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B801" s="33"/>
-      <c r="C801" s="33"/>
-      <c r="D801" s="33"/>
-      <c r="E801" s="33"/>
-      <c r="F801" s="34"/>
+      <c r="B801" s="30"/>
+      <c r="C801" s="30"/>
+      <c r="D801" s="30"/>
+      <c r="E801" s="30"/>
+      <c r="F801" s="31"/>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A802" s="26" t="s">
@@ -15594,11 +15597,11 @@
       <c r="A808" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B808" s="33"/>
-      <c r="C808" s="33"/>
-      <c r="D808" s="33"/>
-      <c r="E808" s="33"/>
-      <c r="F808" s="34"/>
+      <c r="B808" s="30"/>
+      <c r="C808" s="30"/>
+      <c r="D808" s="30"/>
+      <c r="E808" s="30"/>
+      <c r="F808" s="31"/>
     </row>
     <row r="809" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="26" t="s">
@@ -15659,124 +15662,124 @@
       <c r="A815" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B815" s="33"/>
-      <c r="C815" s="33"/>
-      <c r="D815" s="33"/>
-      <c r="E815" s="33"/>
-      <c r="F815" s="34"/>
+      <c r="B815" s="30"/>
+      <c r="C815" s="30"/>
+      <c r="D815" s="30"/>
+      <c r="E815" s="30"/>
+      <c r="F815" s="31"/>
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A816" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B816" s="42" t="s">
+      <c r="B816" s="40" t="s">
         <v>949</v>
       </c>
-      <c r="C816" s="33"/>
-      <c r="D816" s="33"/>
-      <c r="E816" s="33"/>
-      <c r="F816" s="34"/>
+      <c r="C816" s="30"/>
+      <c r="D816" s="30"/>
+      <c r="E816" s="30"/>
+      <c r="F816" s="31"/>
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A819" s="40" t="s">
+      <c r="A819" s="43" t="s">
         <v>950</v>
       </c>
-      <c r="B819" s="30"/>
-      <c r="C819" s="30"/>
-      <c r="D819" s="30"/>
-      <c r="E819" s="30"/>
-      <c r="F819" s="30"/>
+      <c r="B819" s="33"/>
+      <c r="C819" s="33"/>
+      <c r="D819" s="33"/>
+      <c r="E819" s="33"/>
+      <c r="F819" s="33"/>
     </row>
     <row r="820" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B820" s="33"/>
-      <c r="C820" s="33"/>
-      <c r="D820" s="33"/>
-      <c r="E820" s="33"/>
-      <c r="F820" s="34"/>
+      <c r="B820" s="30"/>
+      <c r="C820" s="30"/>
+      <c r="D820" s="30"/>
+      <c r="E820" s="30"/>
+      <c r="F820" s="31"/>
     </row>
     <row r="821" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B821" s="42" t="s">
+      <c r="B821" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C821" s="33"/>
-      <c r="D821" s="33"/>
-      <c r="E821" s="33"/>
-      <c r="F821" s="34"/>
+      <c r="C821" s="30"/>
+      <c r="D821" s="30"/>
+      <c r="E821" s="30"/>
+      <c r="F821" s="31"/>
     </row>
     <row r="822" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B822" s="42" t="s">
+      <c r="B822" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C822" s="33"/>
-      <c r="D822" s="33"/>
-      <c r="E822" s="33"/>
-      <c r="F822" s="34"/>
+      <c r="C822" s="30"/>
+      <c r="D822" s="30"/>
+      <c r="E822" s="30"/>
+      <c r="F822" s="31"/>
     </row>
     <row r="823" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B823" s="42" t="s">
+      <c r="B823" s="40" t="s">
         <v>951</v>
       </c>
-      <c r="C823" s="33"/>
-      <c r="D823" s="33"/>
-      <c r="E823" s="33"/>
-      <c r="F823" s="34"/>
+      <c r="C823" s="30"/>
+      <c r="D823" s="30"/>
+      <c r="E823" s="30"/>
+      <c r="F823" s="31"/>
     </row>
     <row r="824" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B824" s="42" t="s">
+      <c r="B824" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="C824" s="33"/>
-      <c r="D824" s="33"/>
-      <c r="E824" s="33"/>
-      <c r="F824" s="34"/>
+      <c r="C824" s="30"/>
+      <c r="D824" s="30"/>
+      <c r="E824" s="30"/>
+      <c r="F824" s="31"/>
     </row>
     <row r="826" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A826" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B826" s="33"/>
-      <c r="C826" s="33"/>
-      <c r="D826" s="33"/>
-      <c r="E826" s="33"/>
-      <c r="F826" s="34"/>
+      <c r="B826" s="30"/>
+      <c r="C826" s="30"/>
+      <c r="D826" s="30"/>
+      <c r="E826" s="30"/>
+      <c r="F826" s="31"/>
     </row>
     <row r="827" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A827" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B827" s="42" t="s">
+      <c r="B827" s="40" t="s">
         <v>952</v>
       </c>
-      <c r="C827" s="33"/>
-      <c r="D827" s="33"/>
-      <c r="E827" s="33"/>
-      <c r="F827" s="34"/>
+      <c r="C827" s="30"/>
+      <c r="D827" s="30"/>
+      <c r="E827" s="30"/>
+      <c r="F827" s="31"/>
     </row>
     <row r="828" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="829" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B829" s="33"/>
-      <c r="C829" s="33"/>
-      <c r="D829" s="33"/>
-      <c r="E829" s="33"/>
-      <c r="F829" s="34"/>
+      <c r="B829" s="30"/>
+      <c r="C829" s="30"/>
+      <c r="D829" s="30"/>
+      <c r="E829" s="30"/>
+      <c r="F829" s="31"/>
     </row>
     <row r="830" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="26" t="s">
@@ -15805,11 +15808,11 @@
       <c r="A833" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B833" s="33"/>
-      <c r="C833" s="33"/>
-      <c r="D833" s="33"/>
-      <c r="E833" s="33"/>
-      <c r="F833" s="34"/>
+      <c r="B833" s="30"/>
+      <c r="C833" s="30"/>
+      <c r="D833" s="30"/>
+      <c r="E833" s="30"/>
+      <c r="F833" s="31"/>
     </row>
     <row r="834" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="26" t="s">
@@ -15839,11 +15842,11 @@
       <c r="A838" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B838" s="33"/>
-      <c r="C838" s="33"/>
-      <c r="D838" s="33"/>
-      <c r="E838" s="33"/>
-      <c r="F838" s="34"/>
+      <c r="B838" s="30"/>
+      <c r="C838" s="30"/>
+      <c r="D838" s="30"/>
+      <c r="E838" s="30"/>
+      <c r="F838" s="31"/>
     </row>
     <row r="839" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="26" t="s">
@@ -15947,11 +15950,11 @@
       <c r="A847" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B847" s="33"/>
-      <c r="C847" s="33"/>
-      <c r="D847" s="33"/>
-      <c r="E847" s="33"/>
-      <c r="F847" s="34"/>
+      <c r="B847" s="30"/>
+      <c r="C847" s="30"/>
+      <c r="D847" s="30"/>
+      <c r="E847" s="30"/>
+      <c r="F847" s="31"/>
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A848" s="26" t="s">
@@ -15973,55 +15976,55 @@
       <c r="A851" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B851" s="33"/>
-      <c r="C851" s="33"/>
-      <c r="D851" s="33"/>
-      <c r="E851" s="33"/>
-      <c r="F851" s="34"/>
+      <c r="B851" s="30"/>
+      <c r="C851" s="30"/>
+      <c r="D851" s="30"/>
+      <c r="E851" s="30"/>
+      <c r="F851" s="31"/>
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A852" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B852" s="42" t="s">
+      <c r="B852" s="40" t="s">
         <v>970</v>
       </c>
-      <c r="C852" s="33"/>
-      <c r="D852" s="33"/>
-      <c r="E852" s="33"/>
-      <c r="F852" s="34"/>
+      <c r="C852" s="30"/>
+      <c r="D852" s="30"/>
+      <c r="E852" s="30"/>
+      <c r="F852" s="31"/>
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A854" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B854" s="33"/>
-      <c r="C854" s="33"/>
-      <c r="D854" s="33"/>
-      <c r="E854" s="33"/>
-      <c r="F854" s="34"/>
+      <c r="B854" s="30"/>
+      <c r="C854" s="30"/>
+      <c r="D854" s="30"/>
+      <c r="E854" s="30"/>
+      <c r="F854" s="31"/>
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A855" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B855" s="42" t="s">
+      <c r="B855" s="40" t="s">
         <v>971</v>
       </c>
-      <c r="C855" s="33"/>
-      <c r="D855" s="33"/>
-      <c r="E855" s="33"/>
-      <c r="F855" s="34"/>
+      <c r="C855" s="30"/>
+      <c r="D855" s="30"/>
+      <c r="E855" s="30"/>
+      <c r="F855" s="31"/>
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A857" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B857" s="33"/>
-      <c r="C857" s="33"/>
-      <c r="D857" s="33"/>
-      <c r="E857" s="33"/>
-      <c r="F857" s="34"/>
+      <c r="B857" s="30"/>
+      <c r="C857" s="30"/>
+      <c r="D857" s="30"/>
+      <c r="E857" s="30"/>
+      <c r="F857" s="31"/>
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A858" s="26" t="s">
@@ -16112,11 +16115,11 @@
       <c r="A865" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B865" s="33"/>
-      <c r="C865" s="33"/>
-      <c r="D865" s="33"/>
-      <c r="E865" s="33"/>
-      <c r="F865" s="34"/>
+      <c r="B865" s="30"/>
+      <c r="C865" s="30"/>
+      <c r="D865" s="30"/>
+      <c r="E865" s="30"/>
+      <c r="F865" s="31"/>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A866" s="26" t="s">
@@ -16194,11 +16197,11 @@
       <c r="A876" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B876" s="33"/>
-      <c r="C876" s="33"/>
-      <c r="D876" s="33"/>
-      <c r="E876" s="33"/>
-      <c r="F876" s="34"/>
+      <c r="B876" s="30"/>
+      <c r="C876" s="30"/>
+      <c r="D876" s="30"/>
+      <c r="E876" s="30"/>
+      <c r="F876" s="31"/>
     </row>
     <row r="877" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="26" t="s">
@@ -16274,11 +16277,11 @@
       <c r="A883" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B883" s="33"/>
-      <c r="C883" s="33"/>
-      <c r="D883" s="33"/>
-      <c r="E883" s="33"/>
-      <c r="F883" s="34"/>
+      <c r="B883" s="30"/>
+      <c r="C883" s="30"/>
+      <c r="D883" s="30"/>
+      <c r="E883" s="30"/>
+      <c r="F883" s="31"/>
     </row>
     <row r="884" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A884" s="26" t="s">
@@ -16317,127 +16320,127 @@
       <c r="A888" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B888" s="33"/>
-      <c r="C888" s="33"/>
-      <c r="D888" s="33"/>
-      <c r="E888" s="33"/>
-      <c r="F888" s="34"/>
+      <c r="B888" s="30"/>
+      <c r="C888" s="30"/>
+      <c r="D888" s="30"/>
+      <c r="E888" s="30"/>
+      <c r="F888" s="31"/>
     </row>
     <row r="889" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B889" s="42" t="s">
+      <c r="B889" s="40" t="s">
         <v>998</v>
       </c>
-      <c r="C889" s="33"/>
-      <c r="D889" s="33"/>
-      <c r="E889" s="33"/>
-      <c r="F889" s="34"/>
+      <c r="C889" s="30"/>
+      <c r="D889" s="30"/>
+      <c r="E889" s="30"/>
+      <c r="F889" s="31"/>
     </row>
     <row r="890" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="891" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="892" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A892" s="40" t="s">
+      <c r="A892" s="43" t="s">
         <v>999</v>
       </c>
-      <c r="B892" s="30"/>
-      <c r="C892" s="30"/>
-      <c r="D892" s="30"/>
-      <c r="E892" s="30"/>
-      <c r="F892" s="30"/>
+      <c r="B892" s="33"/>
+      <c r="C892" s="33"/>
+      <c r="D892" s="33"/>
+      <c r="E892" s="33"/>
+      <c r="F892" s="33"/>
     </row>
     <row r="893" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A893" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B893" s="33"/>
-      <c r="C893" s="33"/>
-      <c r="D893" s="33"/>
-      <c r="E893" s="33"/>
-      <c r="F893" s="34"/>
+      <c r="B893" s="30"/>
+      <c r="C893" s="30"/>
+      <c r="D893" s="30"/>
+      <c r="E893" s="30"/>
+      <c r="F893" s="31"/>
     </row>
     <row r="894" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A894" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B894" s="42" t="s">
+      <c r="B894" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C894" s="33"/>
-      <c r="D894" s="33"/>
-      <c r="E894" s="33"/>
-      <c r="F894" s="34"/>
+      <c r="C894" s="30"/>
+      <c r="D894" s="30"/>
+      <c r="E894" s="30"/>
+      <c r="F894" s="31"/>
     </row>
     <row r="895" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A895" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B895" s="42" t="s">
+      <c r="B895" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C895" s="33"/>
-      <c r="D895" s="33"/>
-      <c r="E895" s="33"/>
-      <c r="F895" s="34"/>
+      <c r="C895" s="30"/>
+      <c r="D895" s="30"/>
+      <c r="E895" s="30"/>
+      <c r="F895" s="31"/>
     </row>
     <row r="896" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A896" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B896" s="42" t="s">
+      <c r="B896" s="40" t="s">
         <v>1000</v>
       </c>
-      <c r="C896" s="33"/>
-      <c r="D896" s="33"/>
-      <c r="E896" s="33"/>
-      <c r="F896" s="34"/>
+      <c r="C896" s="30"/>
+      <c r="D896" s="30"/>
+      <c r="E896" s="30"/>
+      <c r="F896" s="31"/>
     </row>
     <row r="897" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B897" s="42" t="s">
+      <c r="B897" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="C897" s="33"/>
-      <c r="D897" s="33"/>
-      <c r="E897" s="33"/>
-      <c r="F897" s="34"/>
+      <c r="C897" s="30"/>
+      <c r="D897" s="30"/>
+      <c r="E897" s="30"/>
+      <c r="F897" s="31"/>
     </row>
     <row r="898" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="899" spans="1:6" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B899" s="33"/>
-      <c r="C899" s="33"/>
-      <c r="D899" s="33"/>
-      <c r="E899" s="33"/>
-      <c r="F899" s="34"/>
+      <c r="B899" s="30"/>
+      <c r="C899" s="30"/>
+      <c r="D899" s="30"/>
+      <c r="E899" s="30"/>
+      <c r="F899" s="31"/>
     </row>
     <row r="900" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B900" s="42" t="s">
+      <c r="B900" s="40" t="s">
         <v>952</v>
       </c>
-      <c r="C900" s="33"/>
-      <c r="D900" s="33"/>
-      <c r="E900" s="33"/>
-      <c r="F900" s="34"/>
+      <c r="C900" s="30"/>
+      <c r="D900" s="30"/>
+      <c r="E900" s="30"/>
+      <c r="F900" s="31"/>
     </row>
     <row r="901" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="902" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B902" s="33"/>
-      <c r="C902" s="33"/>
-      <c r="D902" s="33"/>
-      <c r="E902" s="33"/>
-      <c r="F902" s="34"/>
+      <c r="B902" s="30"/>
+      <c r="C902" s="30"/>
+      <c r="D902" s="30"/>
+      <c r="E902" s="30"/>
+      <c r="F902" s="31"/>
     </row>
     <row r="903" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A903" s="26" t="s">
@@ -16465,11 +16468,11 @@
       <c r="A906" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B906" s="33"/>
-      <c r="C906" s="33"/>
-      <c r="D906" s="33"/>
-      <c r="E906" s="33"/>
-      <c r="F906" s="34"/>
+      <c r="B906" s="30"/>
+      <c r="C906" s="30"/>
+      <c r="D906" s="30"/>
+      <c r="E906" s="30"/>
+      <c r="F906" s="31"/>
     </row>
     <row r="907" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="26" t="s">
@@ -16491,11 +16494,11 @@
       <c r="A910" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B910" s="33"/>
-      <c r="C910" s="33"/>
-      <c r="D910" s="33"/>
-      <c r="E910" s="33"/>
-      <c r="F910" s="34"/>
+      <c r="B910" s="30"/>
+      <c r="C910" s="30"/>
+      <c r="D910" s="30"/>
+      <c r="E910" s="30"/>
+      <c r="F910" s="31"/>
     </row>
     <row r="911" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A911" s="26" t="s">
@@ -16529,11 +16532,11 @@
       <c r="A914" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B914" s="33"/>
-      <c r="C914" s="33"/>
-      <c r="D914" s="33"/>
-      <c r="E914" s="33"/>
-      <c r="F914" s="34"/>
+      <c r="B914" s="30"/>
+      <c r="C914" s="30"/>
+      <c r="D914" s="30"/>
+      <c r="E914" s="30"/>
+      <c r="F914" s="31"/>
     </row>
     <row r="915" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A915" s="26" t="s">
@@ -16563,55 +16566,55 @@
       <c r="A919" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B919" s="33"/>
-      <c r="C919" s="33"/>
-      <c r="D919" s="33"/>
-      <c r="E919" s="33"/>
-      <c r="F919" s="34"/>
+      <c r="B919" s="30"/>
+      <c r="C919" s="30"/>
+      <c r="D919" s="30"/>
+      <c r="E919" s="30"/>
+      <c r="F919" s="31"/>
     </row>
     <row r="920" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A920" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B920" s="42" t="s">
+      <c r="B920" s="40" t="s">
         <v>1009</v>
       </c>
-      <c r="C920" s="33"/>
-      <c r="D920" s="33"/>
-      <c r="E920" s="33"/>
-      <c r="F920" s="34"/>
+      <c r="C920" s="30"/>
+      <c r="D920" s="30"/>
+      <c r="E920" s="30"/>
+      <c r="F920" s="31"/>
     </row>
     <row r="922" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A922" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B922" s="33"/>
-      <c r="C922" s="33"/>
-      <c r="D922" s="33"/>
-      <c r="E922" s="33"/>
-      <c r="F922" s="34"/>
+      <c r="B922" s="30"/>
+      <c r="C922" s="30"/>
+      <c r="D922" s="30"/>
+      <c r="E922" s="30"/>
+      <c r="F922" s="31"/>
     </row>
     <row r="923" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A923" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B923" s="42" t="s">
+      <c r="B923" s="40" t="s">
         <v>1010</v>
       </c>
-      <c r="C923" s="33"/>
-      <c r="D923" s="33"/>
-      <c r="E923" s="33"/>
-      <c r="F923" s="34"/>
+      <c r="C923" s="30"/>
+      <c r="D923" s="30"/>
+      <c r="E923" s="30"/>
+      <c r="F923" s="31"/>
     </row>
     <row r="925" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A925" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B925" s="33"/>
-      <c r="C925" s="33"/>
-      <c r="D925" s="33"/>
-      <c r="E925" s="33"/>
-      <c r="F925" s="34"/>
+      <c r="B925" s="30"/>
+      <c r="C925" s="30"/>
+      <c r="D925" s="30"/>
+      <c r="E925" s="30"/>
+      <c r="F925" s="31"/>
     </row>
     <row r="926" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A926" s="26" t="s">
@@ -16702,11 +16705,11 @@
       <c r="A933" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B933" s="33"/>
-      <c r="C933" s="33"/>
-      <c r="D933" s="33"/>
-      <c r="E933" s="33"/>
-      <c r="F933" s="34"/>
+      <c r="B933" s="30"/>
+      <c r="C933" s="30"/>
+      <c r="D933" s="30"/>
+      <c r="E933" s="30"/>
+      <c r="F933" s="31"/>
     </row>
     <row r="934" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A934" s="26" t="s">
@@ -16777,11 +16780,11 @@
       <c r="A943" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B943" s="33"/>
-      <c r="C943" s="33"/>
-      <c r="D943" s="33"/>
-      <c r="E943" s="33"/>
-      <c r="F943" s="34"/>
+      <c r="B943" s="30"/>
+      <c r="C943" s="30"/>
+      <c r="D943" s="30"/>
+      <c r="E943" s="30"/>
+      <c r="F943" s="31"/>
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A944" s="26" t="s">
@@ -16844,11 +16847,11 @@
       <c r="A949" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B949" s="33"/>
-      <c r="C949" s="33"/>
-      <c r="D949" s="33"/>
-      <c r="E949" s="33"/>
-      <c r="F949" s="34"/>
+      <c r="B949" s="30"/>
+      <c r="C949" s="30"/>
+      <c r="D949" s="30"/>
+      <c r="E949" s="30"/>
+      <c r="F949" s="31"/>
     </row>
     <row r="950" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A950" s="26" t="s">
@@ -16887,124 +16890,124 @@
       <c r="A954" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B954" s="33"/>
-      <c r="C954" s="33"/>
-      <c r="D954" s="33"/>
-      <c r="E954" s="33"/>
-      <c r="F954" s="34"/>
+      <c r="B954" s="30"/>
+      <c r="C954" s="30"/>
+      <c r="D954" s="30"/>
+      <c r="E954" s="30"/>
+      <c r="F954" s="31"/>
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A955" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B955" s="42" t="s">
+      <c r="B955" s="40" t="s">
         <v>1034</v>
       </c>
-      <c r="C955" s="33"/>
-      <c r="D955" s="33"/>
-      <c r="E955" s="33"/>
-      <c r="F955" s="34"/>
+      <c r="C955" s="30"/>
+      <c r="D955" s="30"/>
+      <c r="E955" s="30"/>
+      <c r="F955" s="31"/>
     </row>
     <row r="958" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A958" s="40" t="s">
+      <c r="A958" s="43" t="s">
         <v>1035</v>
       </c>
-      <c r="B958" s="30"/>
-      <c r="C958" s="30"/>
-      <c r="D958" s="30"/>
-      <c r="E958" s="30"/>
-      <c r="F958" s="30"/>
+      <c r="B958" s="33"/>
+      <c r="C958" s="33"/>
+      <c r="D958" s="33"/>
+      <c r="E958" s="33"/>
+      <c r="F958" s="33"/>
     </row>
     <row r="959" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A959" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B959" s="33"/>
-      <c r="C959" s="33"/>
-      <c r="D959" s="33"/>
-      <c r="E959" s="33"/>
-      <c r="F959" s="34"/>
+      <c r="B959" s="30"/>
+      <c r="C959" s="30"/>
+      <c r="D959" s="30"/>
+      <c r="E959" s="30"/>
+      <c r="F959" s="31"/>
     </row>
     <row r="960" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A960" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B960" s="42" t="s">
+      <c r="B960" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C960" s="33"/>
-      <c r="D960" s="33"/>
-      <c r="E960" s="33"/>
-      <c r="F960" s="34"/>
+      <c r="C960" s="30"/>
+      <c r="D960" s="30"/>
+      <c r="E960" s="30"/>
+      <c r="F960" s="31"/>
     </row>
     <row r="961" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A961" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B961" s="42" t="s">
+      <c r="B961" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C961" s="33"/>
-      <c r="D961" s="33"/>
-      <c r="E961" s="33"/>
-      <c r="F961" s="34"/>
+      <c r="C961" s="30"/>
+      <c r="D961" s="30"/>
+      <c r="E961" s="30"/>
+      <c r="F961" s="31"/>
     </row>
     <row r="962" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A962" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B962" s="42" t="s">
+      <c r="B962" s="40" t="s">
         <v>1036</v>
       </c>
-      <c r="C962" s="33"/>
-      <c r="D962" s="33"/>
-      <c r="E962" s="33"/>
-      <c r="F962" s="34"/>
+      <c r="C962" s="30"/>
+      <c r="D962" s="30"/>
+      <c r="E962" s="30"/>
+      <c r="F962" s="31"/>
     </row>
     <row r="963" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A963" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B963" s="42" t="s">
+      <c r="B963" s="40" t="s">
         <v>486</v>
       </c>
-      <c r="C963" s="33"/>
-      <c r="D963" s="33"/>
-      <c r="E963" s="33"/>
-      <c r="F963" s="34"/>
+      <c r="C963" s="30"/>
+      <c r="D963" s="30"/>
+      <c r="E963" s="30"/>
+      <c r="F963" s="31"/>
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A965" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B965" s="33"/>
-      <c r="C965" s="33"/>
-      <c r="D965" s="33"/>
-      <c r="E965" s="33"/>
-      <c r="F965" s="34"/>
+      <c r="B965" s="30"/>
+      <c r="C965" s="30"/>
+      <c r="D965" s="30"/>
+      <c r="E965" s="30"/>
+      <c r="F965" s="31"/>
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A966" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B966" s="42" t="s">
+      <c r="B966" s="40" t="s">
         <v>487</v>
       </c>
-      <c r="C966" s="33"/>
-      <c r="D966" s="33"/>
-      <c r="E966" s="33"/>
-      <c r="F966" s="34"/>
+      <c r="C966" s="30"/>
+      <c r="D966" s="30"/>
+      <c r="E966" s="30"/>
+      <c r="F966" s="31"/>
     </row>
     <row r="967" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="968" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A968" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B968" s="33"/>
-      <c r="C968" s="33"/>
-      <c r="D968" s="33"/>
-      <c r="E968" s="33"/>
-      <c r="F968" s="34"/>
+      <c r="B968" s="30"/>
+      <c r="C968" s="30"/>
+      <c r="D968" s="30"/>
+      <c r="E968" s="30"/>
+      <c r="F968" s="31"/>
     </row>
     <row r="969" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A969" s="26" t="s">
@@ -17055,11 +17058,11 @@
       <c r="A974" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B974" s="33"/>
-      <c r="C974" s="33"/>
-      <c r="D974" s="33"/>
-      <c r="E974" s="33"/>
-      <c r="F974" s="34"/>
+      <c r="B974" s="30"/>
+      <c r="C974" s="30"/>
+      <c r="D974" s="30"/>
+      <c r="E974" s="30"/>
+      <c r="F974" s="31"/>
     </row>
     <row r="975" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A975" s="26" t="s">
@@ -17081,11 +17084,11 @@
       <c r="A978" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B978" s="33"/>
-      <c r="C978" s="33"/>
-      <c r="D978" s="33"/>
-      <c r="E978" s="33"/>
-      <c r="F978" s="34"/>
+      <c r="B978" s="30"/>
+      <c r="C978" s="30"/>
+      <c r="D978" s="30"/>
+      <c r="E978" s="30"/>
+      <c r="F978" s="31"/>
     </row>
     <row r="979" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A979" s="26" t="s">
@@ -17120,11 +17123,11 @@
       <c r="A982" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B982" s="33"/>
-      <c r="C982" s="33"/>
-      <c r="D982" s="33"/>
-      <c r="E982" s="33"/>
-      <c r="F982" s="34"/>
+      <c r="B982" s="30"/>
+      <c r="C982" s="30"/>
+      <c r="D982" s="30"/>
+      <c r="E982" s="30"/>
+      <c r="F982" s="31"/>
     </row>
     <row r="983" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A983" s="26" t="s">
@@ -17162,55 +17165,55 @@
       <c r="A988" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B988" s="33"/>
-      <c r="C988" s="33"/>
-      <c r="D988" s="33"/>
-      <c r="E988" s="33"/>
-      <c r="F988" s="34"/>
+      <c r="B988" s="30"/>
+      <c r="C988" s="30"/>
+      <c r="D988" s="30"/>
+      <c r="E988" s="30"/>
+      <c r="F988" s="31"/>
     </row>
     <row r="989" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A989" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B989" s="42" t="s">
+      <c r="B989" s="40" t="s">
         <v>1047</v>
       </c>
-      <c r="C989" s="33"/>
-      <c r="D989" s="33"/>
-      <c r="E989" s="33"/>
-      <c r="F989" s="34"/>
+      <c r="C989" s="30"/>
+      <c r="D989" s="30"/>
+      <c r="E989" s="30"/>
+      <c r="F989" s="31"/>
     </row>
     <row r="991" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A991" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B991" s="33"/>
-      <c r="C991" s="33"/>
-      <c r="D991" s="33"/>
-      <c r="E991" s="33"/>
-      <c r="F991" s="34"/>
+      <c r="B991" s="30"/>
+      <c r="C991" s="30"/>
+      <c r="D991" s="30"/>
+      <c r="E991" s="30"/>
+      <c r="F991" s="31"/>
     </row>
     <row r="992" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A992" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B992" s="42" t="s">
+      <c r="B992" s="40" t="s">
         <v>1048</v>
       </c>
-      <c r="C992" s="33"/>
-      <c r="D992" s="33"/>
-      <c r="E992" s="33"/>
-      <c r="F992" s="34"/>
+      <c r="C992" s="30"/>
+      <c r="D992" s="30"/>
+      <c r="E992" s="30"/>
+      <c r="F992" s="31"/>
     </row>
     <row r="994" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A994" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B994" s="33"/>
-      <c r="C994" s="33"/>
-      <c r="D994" s="33"/>
-      <c r="E994" s="33"/>
-      <c r="F994" s="34"/>
+      <c r="B994" s="30"/>
+      <c r="C994" s="30"/>
+      <c r="D994" s="30"/>
+      <c r="E994" s="30"/>
+      <c r="F994" s="31"/>
     </row>
     <row r="995" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A995" s="26" t="s">
@@ -17300,11 +17303,11 @@
       <c r="A1002" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B1002" s="33"/>
-      <c r="C1002" s="33"/>
-      <c r="D1002" s="33"/>
-      <c r="E1002" s="33"/>
-      <c r="F1002" s="34"/>
+      <c r="B1002" s="30"/>
+      <c r="C1002" s="30"/>
+      <c r="D1002" s="30"/>
+      <c r="E1002" s="30"/>
+      <c r="F1002" s="31"/>
     </row>
     <row r="1003" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1003" s="26" t="s">
@@ -17366,11 +17369,11 @@
       <c r="A1011" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B1011" s="33"/>
-      <c r="C1011" s="33"/>
-      <c r="D1011" s="33"/>
-      <c r="E1011" s="33"/>
-      <c r="F1011" s="34"/>
+      <c r="B1011" s="30"/>
+      <c r="C1011" s="30"/>
+      <c r="D1011" s="30"/>
+      <c r="E1011" s="30"/>
+      <c r="F1011" s="31"/>
     </row>
     <row r="1012" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1012" s="26" t="s">
@@ -17418,11 +17421,11 @@
       <c r="A1016" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B1016" s="33"/>
-      <c r="C1016" s="33"/>
-      <c r="D1016" s="33"/>
-      <c r="E1016" s="33"/>
-      <c r="F1016" s="34"/>
+      <c r="B1016" s="30"/>
+      <c r="C1016" s="30"/>
+      <c r="D1016" s="30"/>
+      <c r="E1016" s="30"/>
+      <c r="F1016" s="31"/>
     </row>
     <row r="1017" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1017" s="26" t="s">
@@ -17461,125 +17464,125 @@
       <c r="A1021" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B1021" s="33"/>
-      <c r="C1021" s="33"/>
-      <c r="D1021" s="33"/>
-      <c r="E1021" s="33"/>
-      <c r="F1021" s="34"/>
+      <c r="B1021" s="30"/>
+      <c r="C1021" s="30"/>
+      <c r="D1021" s="30"/>
+      <c r="E1021" s="30"/>
+      <c r="F1021" s="31"/>
     </row>
     <row r="1022" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1022" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B1022" s="42" t="s">
+      <c r="B1022" s="40" t="s">
         <v>1071</v>
       </c>
-      <c r="C1022" s="33"/>
-      <c r="D1022" s="33"/>
-      <c r="E1022" s="33"/>
-      <c r="F1022" s="34"/>
+      <c r="C1022" s="30"/>
+      <c r="D1022" s="30"/>
+      <c r="E1022" s="30"/>
+      <c r="F1022" s="31"/>
     </row>
     <row r="1023" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1024" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1025" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1025" s="40" t="s">
+      <c r="A1025" s="43" t="s">
         <v>1072</v>
       </c>
-      <c r="B1025" s="30"/>
-      <c r="C1025" s="30"/>
-      <c r="D1025" s="30"/>
-      <c r="E1025" s="30"/>
-      <c r="F1025" s="30"/>
+      <c r="B1025" s="33"/>
+      <c r="C1025" s="33"/>
+      <c r="D1025" s="33"/>
+      <c r="E1025" s="33"/>
+      <c r="F1025" s="33"/>
     </row>
     <row r="1026" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1026" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B1026" s="33"/>
-      <c r="C1026" s="33"/>
-      <c r="D1026" s="33"/>
-      <c r="E1026" s="33"/>
-      <c r="F1026" s="34"/>
+      <c r="B1026" s="30"/>
+      <c r="C1026" s="30"/>
+      <c r="D1026" s="30"/>
+      <c r="E1026" s="30"/>
+      <c r="F1026" s="31"/>
     </row>
     <row r="1027" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1027" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B1027" s="42" t="s">
+      <c r="B1027" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C1027" s="33"/>
-      <c r="D1027" s="33"/>
-      <c r="E1027" s="33"/>
-      <c r="F1027" s="34"/>
+      <c r="C1027" s="30"/>
+      <c r="D1027" s="30"/>
+      <c r="E1027" s="30"/>
+      <c r="F1027" s="31"/>
     </row>
     <row r="1028" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1028" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B1028" s="42" t="s">
+      <c r="B1028" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C1028" s="33"/>
-      <c r="D1028" s="33"/>
-      <c r="E1028" s="33"/>
-      <c r="F1028" s="34"/>
+      <c r="C1028" s="30"/>
+      <c r="D1028" s="30"/>
+      <c r="E1028" s="30"/>
+      <c r="F1028" s="31"/>
     </row>
     <row r="1029" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1029" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B1029" s="42" t="s">
+      <c r="B1029" s="40" t="s">
         <v>1073</v>
       </c>
-      <c r="C1029" s="33"/>
-      <c r="D1029" s="33"/>
-      <c r="E1029" s="33"/>
-      <c r="F1029" s="34"/>
+      <c r="C1029" s="30"/>
+      <c r="D1029" s="30"/>
+      <c r="E1029" s="30"/>
+      <c r="F1029" s="31"/>
     </row>
     <row r="1030" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1030" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B1030" s="42" t="s">
+      <c r="B1030" s="40" t="s">
         <v>486</v>
       </c>
-      <c r="C1030" s="33"/>
-      <c r="D1030" s="33"/>
-      <c r="E1030" s="33"/>
-      <c r="F1030" s="34"/>
+      <c r="C1030" s="30"/>
+      <c r="D1030" s="30"/>
+      <c r="E1030" s="30"/>
+      <c r="F1030" s="31"/>
     </row>
     <row r="1032" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1032" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B1032" s="33"/>
-      <c r="C1032" s="33"/>
-      <c r="D1032" s="33"/>
-      <c r="E1032" s="33"/>
-      <c r="F1032" s="34"/>
+      <c r="B1032" s="30"/>
+      <c r="C1032" s="30"/>
+      <c r="D1032" s="30"/>
+      <c r="E1032" s="30"/>
+      <c r="F1032" s="31"/>
     </row>
     <row r="1033" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1033" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B1033" s="42" t="s">
+      <c r="B1033" s="40" t="s">
         <v>1074</v>
       </c>
-      <c r="C1033" s="33"/>
-      <c r="D1033" s="33"/>
-      <c r="E1033" s="33"/>
-      <c r="F1033" s="34"/>
+      <c r="C1033" s="30"/>
+      <c r="D1033" s="30"/>
+      <c r="E1033" s="30"/>
+      <c r="F1033" s="31"/>
     </row>
     <row r="1035" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1035" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B1035" s="33"/>
-      <c r="C1035" s="33"/>
-      <c r="D1035" s="33"/>
-      <c r="E1035" s="33"/>
-      <c r="F1035" s="34"/>
+      <c r="B1035" s="30"/>
+      <c r="C1035" s="30"/>
+      <c r="D1035" s="30"/>
+      <c r="E1035" s="30"/>
+      <c r="F1035" s="31"/>
     </row>
     <row r="1036" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1036" s="26" t="s">
@@ -17629,11 +17632,11 @@
       <c r="A1041" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B1041" s="33"/>
-      <c r="C1041" s="33"/>
-      <c r="D1041" s="33"/>
-      <c r="E1041" s="33"/>
-      <c r="F1041" s="34"/>
+      <c r="B1041" s="30"/>
+      <c r="C1041" s="30"/>
+      <c r="D1041" s="30"/>
+      <c r="E1041" s="30"/>
+      <c r="F1041" s="31"/>
     </row>
     <row r="1042" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1042" s="26" t="s">
@@ -17664,11 +17667,11 @@
       <c r="A1046" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B1046" s="33"/>
-      <c r="C1046" s="33"/>
-      <c r="D1046" s="33"/>
-      <c r="E1046" s="33"/>
-      <c r="F1046" s="34"/>
+      <c r="B1046" s="30"/>
+      <c r="C1046" s="30"/>
+      <c r="D1046" s="30"/>
+      <c r="E1046" s="30"/>
+      <c r="F1046" s="31"/>
     </row>
     <row r="1047" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1047" s="26" t="s">
@@ -17716,11 +17719,11 @@
       <c r="A1051" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B1051" s="33"/>
-      <c r="C1051" s="33"/>
-      <c r="D1051" s="33"/>
-      <c r="E1051" s="33"/>
-      <c r="F1051" s="34"/>
+      <c r="B1051" s="30"/>
+      <c r="C1051" s="30"/>
+      <c r="D1051" s="30"/>
+      <c r="E1051" s="30"/>
+      <c r="F1051" s="31"/>
     </row>
     <row r="1052" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1052" s="26" t="s">
@@ -17758,56 +17761,56 @@
       <c r="A1057" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B1057" s="33"/>
-      <c r="C1057" s="33"/>
-      <c r="D1057" s="33"/>
-      <c r="E1057" s="33"/>
-      <c r="F1057" s="34"/>
+      <c r="B1057" s="30"/>
+      <c r="C1057" s="30"/>
+      <c r="D1057" s="30"/>
+      <c r="E1057" s="30"/>
+      <c r="F1057" s="31"/>
     </row>
     <row r="1058" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1058" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B1058" s="42" t="s">
+      <c r="B1058" s="40" t="s">
         <v>1089</v>
       </c>
-      <c r="C1058" s="33"/>
-      <c r="D1058" s="33"/>
-      <c r="E1058" s="33"/>
-      <c r="F1058" s="34"/>
+      <c r="C1058" s="30"/>
+      <c r="D1058" s="30"/>
+      <c r="E1058" s="30"/>
+      <c r="F1058" s="31"/>
     </row>
     <row r="1059" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1060" spans="1:6" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1060" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B1060" s="33"/>
-      <c r="C1060" s="33"/>
-      <c r="D1060" s="33"/>
-      <c r="E1060" s="33"/>
-      <c r="F1060" s="34"/>
+      <c r="B1060" s="30"/>
+      <c r="C1060" s="30"/>
+      <c r="D1060" s="30"/>
+      <c r="E1060" s="30"/>
+      <c r="F1060" s="31"/>
     </row>
     <row r="1061" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1061" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B1061" s="42" t="s">
+      <c r="B1061" s="40" t="s">
         <v>1090</v>
       </c>
-      <c r="C1061" s="33"/>
-      <c r="D1061" s="33"/>
-      <c r="E1061" s="33"/>
-      <c r="F1061" s="34"/>
+      <c r="C1061" s="30"/>
+      <c r="D1061" s="30"/>
+      <c r="E1061" s="30"/>
+      <c r="F1061" s="31"/>
     </row>
     <row r="1063" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1063" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B1063" s="33"/>
-      <c r="C1063" s="33"/>
-      <c r="D1063" s="33"/>
-      <c r="E1063" s="33"/>
-      <c r="F1063" s="34"/>
+      <c r="B1063" s="30"/>
+      <c r="C1063" s="30"/>
+      <c r="D1063" s="30"/>
+      <c r="E1063" s="30"/>
+      <c r="F1063" s="31"/>
     </row>
     <row r="1064" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1064" s="26" t="s">
@@ -17911,11 +17914,11 @@
       <c r="A1072" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B1072" s="33"/>
-      <c r="C1072" s="33"/>
-      <c r="D1072" s="33"/>
-      <c r="E1072" s="33"/>
-      <c r="F1072" s="34"/>
+      <c r="B1072" s="30"/>
+      <c r="C1072" s="30"/>
+      <c r="D1072" s="30"/>
+      <c r="E1072" s="30"/>
+      <c r="F1072" s="31"/>
     </row>
     <row r="1073" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1073" s="26" t="s">
@@ -17993,11 +17996,11 @@
       <c r="A1083" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B1083" s="33"/>
-      <c r="C1083" s="33"/>
-      <c r="D1083" s="33"/>
-      <c r="E1083" s="33"/>
-      <c r="F1083" s="34"/>
+      <c r="B1083" s="30"/>
+      <c r="C1083" s="30"/>
+      <c r="D1083" s="30"/>
+      <c r="E1083" s="30"/>
+      <c r="F1083" s="31"/>
     </row>
     <row r="1084" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1084" s="26" t="s">
@@ -18074,11 +18077,11 @@
       <c r="A1090" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B1090" s="33"/>
-      <c r="C1090" s="33"/>
-      <c r="D1090" s="33"/>
-      <c r="E1090" s="33"/>
-      <c r="F1090" s="34"/>
+      <c r="B1090" s="30"/>
+      <c r="C1090" s="30"/>
+      <c r="D1090" s="30"/>
+      <c r="E1090" s="30"/>
+      <c r="F1090" s="31"/>
     </row>
     <row r="1091" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1091" s="26" t="s">
@@ -18117,125 +18120,125 @@
       <c r="A1095" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B1095" s="33"/>
-      <c r="C1095" s="33"/>
-      <c r="D1095" s="33"/>
-      <c r="E1095" s="33"/>
-      <c r="F1095" s="34"/>
+      <c r="B1095" s="30"/>
+      <c r="C1095" s="30"/>
+      <c r="D1095" s="30"/>
+      <c r="E1095" s="30"/>
+      <c r="F1095" s="31"/>
     </row>
     <row r="1096" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1096" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B1096" s="42" t="s">
+      <c r="B1096" s="40" t="s">
         <v>1115</v>
       </c>
-      <c r="C1096" s="33"/>
-      <c r="D1096" s="33"/>
-      <c r="E1096" s="33"/>
-      <c r="F1096" s="34"/>
+      <c r="C1096" s="30"/>
+      <c r="D1096" s="30"/>
+      <c r="E1096" s="30"/>
+      <c r="F1096" s="31"/>
     </row>
     <row r="1097" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1099" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1099" s="40" t="s">
+      <c r="A1099" s="43" t="s">
         <v>1116</v>
       </c>
-      <c r="B1099" s="30"/>
-      <c r="C1099" s="30"/>
-      <c r="D1099" s="30"/>
-      <c r="E1099" s="30"/>
-      <c r="F1099" s="30"/>
+      <c r="B1099" s="33"/>
+      <c r="C1099" s="33"/>
+      <c r="D1099" s="33"/>
+      <c r="E1099" s="33"/>
+      <c r="F1099" s="33"/>
     </row>
     <row r="1100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1100" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B1100" s="33"/>
-      <c r="C1100" s="33"/>
-      <c r="D1100" s="33"/>
-      <c r="E1100" s="33"/>
-      <c r="F1100" s="34"/>
+      <c r="B1100" s="30"/>
+      <c r="C1100" s="30"/>
+      <c r="D1100" s="30"/>
+      <c r="E1100" s="30"/>
+      <c r="F1100" s="31"/>
     </row>
     <row r="1101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1101" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B1101" s="42" t="s">
+      <c r="B1101" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C1101" s="33"/>
-      <c r="D1101" s="33"/>
-      <c r="E1101" s="33"/>
-      <c r="F1101" s="34"/>
+      <c r="C1101" s="30"/>
+      <c r="D1101" s="30"/>
+      <c r="E1101" s="30"/>
+      <c r="F1101" s="31"/>
     </row>
     <row r="1102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1102" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B1102" s="42" t="s">
+      <c r="B1102" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C1102" s="33"/>
-      <c r="D1102" s="33"/>
-      <c r="E1102" s="33"/>
-      <c r="F1102" s="34"/>
+      <c r="C1102" s="30"/>
+      <c r="D1102" s="30"/>
+      <c r="E1102" s="30"/>
+      <c r="F1102" s="31"/>
     </row>
     <row r="1103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1103" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B1103" s="42" t="s">
+      <c r="B1103" s="40" t="s">
         <v>1117</v>
       </c>
-      <c r="C1103" s="33"/>
-      <c r="D1103" s="33"/>
-      <c r="E1103" s="33"/>
-      <c r="F1103" s="34"/>
+      <c r="C1103" s="30"/>
+      <c r="D1103" s="30"/>
+      <c r="E1103" s="30"/>
+      <c r="F1103" s="31"/>
     </row>
     <row r="1104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1104" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B1104" s="42" t="s">
+      <c r="B1104" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="C1104" s="33"/>
-      <c r="D1104" s="33"/>
-      <c r="E1104" s="33"/>
-      <c r="F1104" s="34"/>
+      <c r="C1104" s="30"/>
+      <c r="D1104" s="30"/>
+      <c r="E1104" s="30"/>
+      <c r="F1104" s="31"/>
     </row>
     <row r="1106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1106" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B1106" s="33"/>
-      <c r="C1106" s="33"/>
-      <c r="D1106" s="33"/>
-      <c r="E1106" s="33"/>
-      <c r="F1106" s="34"/>
+      <c r="B1106" s="30"/>
+      <c r="C1106" s="30"/>
+      <c r="D1106" s="30"/>
+      <c r="E1106" s="30"/>
+      <c r="F1106" s="31"/>
     </row>
     <row r="1107" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1107" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B1107" s="42" t="s">
+      <c r="B1107" s="40" t="s">
         <v>704</v>
       </c>
-      <c r="C1107" s="33"/>
-      <c r="D1107" s="33"/>
-      <c r="E1107" s="33"/>
-      <c r="F1107" s="34"/>
+      <c r="C1107" s="30"/>
+      <c r="D1107" s="30"/>
+      <c r="E1107" s="30"/>
+      <c r="F1107" s="31"/>
     </row>
     <row r="1108" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1109" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1109" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B1109" s="33"/>
-      <c r="C1109" s="33"/>
-      <c r="D1109" s="33"/>
-      <c r="E1109" s="33"/>
-      <c r="F1109" s="34"/>
+      <c r="B1109" s="30"/>
+      <c r="C1109" s="30"/>
+      <c r="D1109" s="30"/>
+      <c r="E1109" s="30"/>
+      <c r="F1109" s="31"/>
     </row>
     <row r="1110" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1110" s="26" t="s">
@@ -18308,11 +18311,11 @@
       <c r="A1117" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B1117" s="33"/>
-      <c r="C1117" s="33"/>
-      <c r="D1117" s="33"/>
-      <c r="E1117" s="33"/>
-      <c r="F1117" s="34"/>
+      <c r="B1117" s="30"/>
+      <c r="C1117" s="30"/>
+      <c r="D1117" s="30"/>
+      <c r="E1117" s="30"/>
+      <c r="F1117" s="31"/>
     </row>
     <row r="1118" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1118" s="26" t="s">
@@ -18343,11 +18346,11 @@
       <c r="A1122" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B1122" s="33"/>
-      <c r="C1122" s="33"/>
-      <c r="D1122" s="33"/>
-      <c r="E1122" s="33"/>
-      <c r="F1122" s="34"/>
+      <c r="B1122" s="30"/>
+      <c r="C1122" s="30"/>
+      <c r="D1122" s="30"/>
+      <c r="E1122" s="30"/>
+      <c r="F1122" s="31"/>
     </row>
     <row r="1123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1123" s="26" t="s">
@@ -18410,11 +18413,11 @@
       <c r="A1128" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B1128" s="33"/>
-      <c r="C1128" s="33"/>
-      <c r="D1128" s="33"/>
-      <c r="E1128" s="33"/>
-      <c r="F1128" s="34"/>
+      <c r="B1128" s="30"/>
+      <c r="C1128" s="30"/>
+      <c r="D1128" s="30"/>
+      <c r="E1128" s="30"/>
+      <c r="F1128" s="31"/>
     </row>
     <row r="1129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1129" s="26" t="s">
@@ -18452,55 +18455,55 @@
       <c r="A1134" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B1134" s="33"/>
-      <c r="C1134" s="33"/>
-      <c r="D1134" s="33"/>
-      <c r="E1134" s="33"/>
-      <c r="F1134" s="34"/>
+      <c r="B1134" s="30"/>
+      <c r="C1134" s="30"/>
+      <c r="D1134" s="30"/>
+      <c r="E1134" s="30"/>
+      <c r="F1134" s="31"/>
     </row>
     <row r="1135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1135" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B1135" s="42" t="s">
+      <c r="B1135" s="40" t="s">
         <v>1137</v>
       </c>
-      <c r="C1135" s="33"/>
-      <c r="D1135" s="33"/>
-      <c r="E1135" s="33"/>
-      <c r="F1135" s="34"/>
+      <c r="C1135" s="30"/>
+      <c r="D1135" s="30"/>
+      <c r="E1135" s="30"/>
+      <c r="F1135" s="31"/>
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1137" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B1137" s="33"/>
-      <c r="C1137" s="33"/>
-      <c r="D1137" s="33"/>
-      <c r="E1137" s="33"/>
-      <c r="F1137" s="34"/>
+      <c r="B1137" s="30"/>
+      <c r="C1137" s="30"/>
+      <c r="D1137" s="30"/>
+      <c r="E1137" s="30"/>
+      <c r="F1137" s="31"/>
     </row>
     <row r="1138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1138" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B1138" s="42" t="s">
+      <c r="B1138" s="40" t="s">
         <v>1138</v>
       </c>
-      <c r="C1138" s="33"/>
-      <c r="D1138" s="33"/>
-      <c r="E1138" s="33"/>
-      <c r="F1138" s="34"/>
+      <c r="C1138" s="30"/>
+      <c r="D1138" s="30"/>
+      <c r="E1138" s="30"/>
+      <c r="F1138" s="31"/>
     </row>
     <row r="1140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1140" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B1140" s="33"/>
-      <c r="C1140" s="33"/>
-      <c r="D1140" s="33"/>
-      <c r="E1140" s="33"/>
-      <c r="F1140" s="34"/>
+      <c r="B1140" s="30"/>
+      <c r="C1140" s="30"/>
+      <c r="D1140" s="30"/>
+      <c r="E1140" s="30"/>
+      <c r="F1140" s="31"/>
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1141" s="26" t="s">
@@ -18590,11 +18593,11 @@
       <c r="A1148" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B1148" s="33"/>
-      <c r="C1148" s="33"/>
-      <c r="D1148" s="33"/>
-      <c r="E1148" s="33"/>
-      <c r="F1148" s="34"/>
+      <c r="B1148" s="30"/>
+      <c r="C1148" s="30"/>
+      <c r="D1148" s="30"/>
+      <c r="E1148" s="30"/>
+      <c r="F1148" s="31"/>
     </row>
     <row r="1149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1149" s="26" t="s">
@@ -18656,11 +18659,11 @@
       <c r="A1157" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B1157" s="33"/>
-      <c r="C1157" s="33"/>
-      <c r="D1157" s="33"/>
-      <c r="E1157" s="33"/>
-      <c r="F1157" s="34"/>
+      <c r="B1157" s="30"/>
+      <c r="C1157" s="30"/>
+      <c r="D1157" s="30"/>
+      <c r="E1157" s="30"/>
+      <c r="F1157" s="31"/>
     </row>
     <row r="1158" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1158" s="26" t="s">
@@ -18737,11 +18740,11 @@
       <c r="A1164" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B1164" s="33"/>
-      <c r="C1164" s="33"/>
-      <c r="D1164" s="33"/>
-      <c r="E1164" s="33"/>
-      <c r="F1164" s="34"/>
+      <c r="B1164" s="30"/>
+      <c r="C1164" s="30"/>
+      <c r="D1164" s="30"/>
+      <c r="E1164" s="30"/>
+      <c r="F1164" s="31"/>
     </row>
     <row r="1165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1165" s="26" t="s">
@@ -18780,124 +18783,124 @@
       <c r="A1169" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B1169" s="33"/>
-      <c r="C1169" s="33"/>
-      <c r="D1169" s="33"/>
-      <c r="E1169" s="33"/>
-      <c r="F1169" s="34"/>
+      <c r="B1169" s="30"/>
+      <c r="C1169" s="30"/>
+      <c r="D1169" s="30"/>
+      <c r="E1169" s="30"/>
+      <c r="F1169" s="31"/>
     </row>
     <row r="1170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1170" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B1170" s="42" t="s">
+      <c r="B1170" s="40" t="s">
         <v>1165</v>
       </c>
-      <c r="C1170" s="33"/>
-      <c r="D1170" s="33"/>
-      <c r="E1170" s="33"/>
-      <c r="F1170" s="34"/>
+      <c r="C1170" s="30"/>
+      <c r="D1170" s="30"/>
+      <c r="E1170" s="30"/>
+      <c r="F1170" s="31"/>
     </row>
     <row r="1173" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1173" s="40" t="s">
+      <c r="A1173" s="43" t="s">
         <v>1166</v>
       </c>
-      <c r="B1173" s="30"/>
-      <c r="C1173" s="30"/>
-      <c r="D1173" s="30"/>
-      <c r="E1173" s="30"/>
-      <c r="F1173" s="30"/>
+      <c r="B1173" s="33"/>
+      <c r="C1173" s="33"/>
+      <c r="D1173" s="33"/>
+      <c r="E1173" s="33"/>
+      <c r="F1173" s="33"/>
     </row>
     <row r="1174" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B1174" s="33"/>
-      <c r="C1174" s="33"/>
-      <c r="D1174" s="33"/>
-      <c r="E1174" s="33"/>
-      <c r="F1174" s="34"/>
+      <c r="B1174" s="30"/>
+      <c r="C1174" s="30"/>
+      <c r="D1174" s="30"/>
+      <c r="E1174" s="30"/>
+      <c r="F1174" s="31"/>
     </row>
     <row r="1175" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1175" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B1175" s="42" t="s">
+      <c r="B1175" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C1175" s="33"/>
-      <c r="D1175" s="33"/>
-      <c r="E1175" s="33"/>
-      <c r="F1175" s="34"/>
+      <c r="C1175" s="30"/>
+      <c r="D1175" s="30"/>
+      <c r="E1175" s="30"/>
+      <c r="F1175" s="31"/>
     </row>
     <row r="1176" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B1176" s="42" t="s">
+      <c r="B1176" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C1176" s="33"/>
-      <c r="D1176" s="33"/>
-      <c r="E1176" s="33"/>
-      <c r="F1176" s="34"/>
+      <c r="C1176" s="30"/>
+      <c r="D1176" s="30"/>
+      <c r="E1176" s="30"/>
+      <c r="F1176" s="31"/>
     </row>
     <row r="1177" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1177" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B1177" s="42" t="s">
+      <c r="B1177" s="40" t="s">
         <v>1167</v>
       </c>
-      <c r="C1177" s="33"/>
-      <c r="D1177" s="33"/>
-      <c r="E1177" s="33"/>
-      <c r="F1177" s="34"/>
+      <c r="C1177" s="30"/>
+      <c r="D1177" s="30"/>
+      <c r="E1177" s="30"/>
+      <c r="F1177" s="31"/>
     </row>
     <row r="1178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1178" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B1178" s="42" t="s">
+      <c r="B1178" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="C1178" s="33"/>
-      <c r="D1178" s="33"/>
-      <c r="E1178" s="33"/>
-      <c r="F1178" s="34"/>
+      <c r="C1178" s="30"/>
+      <c r="D1178" s="30"/>
+      <c r="E1178" s="30"/>
+      <c r="F1178" s="31"/>
     </row>
     <row r="1180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1180" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B1180" s="33"/>
-      <c r="C1180" s="33"/>
-      <c r="D1180" s="33"/>
-      <c r="E1180" s="33"/>
-      <c r="F1180" s="34"/>
+      <c r="B1180" s="30"/>
+      <c r="C1180" s="30"/>
+      <c r="D1180" s="30"/>
+      <c r="E1180" s="30"/>
+      <c r="F1180" s="31"/>
     </row>
     <row r="1181" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1181" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B1181" s="42" t="s">
+      <c r="B1181" s="40" t="s">
         <v>704</v>
       </c>
-      <c r="C1181" s="33"/>
-      <c r="D1181" s="33"/>
-      <c r="E1181" s="33"/>
-      <c r="F1181" s="34"/>
+      <c r="C1181" s="30"/>
+      <c r="D1181" s="30"/>
+      <c r="E1181" s="30"/>
+      <c r="F1181" s="31"/>
     </row>
     <row r="1182" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1183" spans="1:6" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1183" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B1183" s="33"/>
-      <c r="C1183" s="33"/>
-      <c r="D1183" s="33"/>
-      <c r="E1183" s="33"/>
-      <c r="F1183" s="34"/>
+      <c r="B1183" s="30"/>
+      <c r="C1183" s="30"/>
+      <c r="D1183" s="30"/>
+      <c r="E1183" s="30"/>
+      <c r="F1183" s="31"/>
     </row>
     <row r="1184" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1184" s="26" t="s">
@@ -18947,11 +18950,11 @@
       <c r="A1189" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B1189" s="33"/>
-      <c r="C1189" s="33"/>
-      <c r="D1189" s="33"/>
-      <c r="E1189" s="33"/>
-      <c r="F1189" s="34"/>
+      <c r="B1189" s="30"/>
+      <c r="C1189" s="30"/>
+      <c r="D1189" s="30"/>
+      <c r="E1189" s="30"/>
+      <c r="F1189" s="31"/>
     </row>
     <row r="1190" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1190" s="26" t="s">
@@ -18981,11 +18984,11 @@
       <c r="A1194" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B1194" s="33"/>
-      <c r="C1194" s="33"/>
-      <c r="D1194" s="33"/>
-      <c r="E1194" s="33"/>
-      <c r="F1194" s="34"/>
+      <c r="B1194" s="30"/>
+      <c r="C1194" s="30"/>
+      <c r="D1194" s="30"/>
+      <c r="E1194" s="30"/>
+      <c r="F1194" s="31"/>
     </row>
     <row r="1195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1195" s="26" t="s">
@@ -19047,11 +19050,11 @@
       <c r="A1200" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B1200" s="33"/>
-      <c r="C1200" s="33"/>
-      <c r="D1200" s="33"/>
-      <c r="E1200" s="33"/>
-      <c r="F1200" s="34"/>
+      <c r="B1200" s="30"/>
+      <c r="C1200" s="30"/>
+      <c r="D1200" s="30"/>
+      <c r="E1200" s="30"/>
+      <c r="F1200" s="31"/>
     </row>
     <row r="1201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1201" s="26" t="s">
@@ -19089,55 +19092,55 @@
       <c r="A1206" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B1206" s="33"/>
-      <c r="C1206" s="33"/>
-      <c r="D1206" s="33"/>
-      <c r="E1206" s="33"/>
-      <c r="F1206" s="34"/>
+      <c r="B1206" s="30"/>
+      <c r="C1206" s="30"/>
+      <c r="D1206" s="30"/>
+      <c r="E1206" s="30"/>
+      <c r="F1206" s="31"/>
     </row>
     <row r="1207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1207" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B1207" s="42" t="s">
+      <c r="B1207" s="40" t="s">
         <v>1185</v>
       </c>
-      <c r="C1207" s="33"/>
-      <c r="D1207" s="33"/>
-      <c r="E1207" s="33"/>
-      <c r="F1207" s="34"/>
+      <c r="C1207" s="30"/>
+      <c r="D1207" s="30"/>
+      <c r="E1207" s="30"/>
+      <c r="F1207" s="31"/>
     </row>
     <row r="1209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1209" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B1209" s="33"/>
-      <c r="C1209" s="33"/>
-      <c r="D1209" s="33"/>
-      <c r="E1209" s="33"/>
-      <c r="F1209" s="34"/>
+      <c r="B1209" s="30"/>
+      <c r="C1209" s="30"/>
+      <c r="D1209" s="30"/>
+      <c r="E1209" s="30"/>
+      <c r="F1209" s="31"/>
     </row>
     <row r="1210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1210" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B1210" s="42" t="s">
+      <c r="B1210" s="40" t="s">
         <v>1186</v>
       </c>
-      <c r="C1210" s="33"/>
-      <c r="D1210" s="33"/>
-      <c r="E1210" s="33"/>
-      <c r="F1210" s="34"/>
+      <c r="C1210" s="30"/>
+      <c r="D1210" s="30"/>
+      <c r="E1210" s="30"/>
+      <c r="F1210" s="31"/>
     </row>
     <row r="1212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1212" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B1212" s="33"/>
-      <c r="C1212" s="33"/>
-      <c r="D1212" s="33"/>
-      <c r="E1212" s="33"/>
-      <c r="F1212" s="34"/>
+      <c r="B1212" s="30"/>
+      <c r="C1212" s="30"/>
+      <c r="D1212" s="30"/>
+      <c r="E1212" s="30"/>
+      <c r="F1212" s="31"/>
     </row>
     <row r="1213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1213" s="26" t="s">
@@ -19228,11 +19231,11 @@
       <c r="A1220" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B1220" s="33"/>
-      <c r="C1220" s="33"/>
-      <c r="D1220" s="33"/>
-      <c r="E1220" s="33"/>
-      <c r="F1220" s="34"/>
+      <c r="B1220" s="30"/>
+      <c r="C1220" s="30"/>
+      <c r="D1220" s="30"/>
+      <c r="E1220" s="30"/>
+      <c r="F1220" s="31"/>
     </row>
     <row r="1221" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1221" s="26" t="s">
@@ -19302,11 +19305,11 @@
       <c r="A1230" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B1230" s="33"/>
-      <c r="C1230" s="33"/>
-      <c r="D1230" s="33"/>
-      <c r="E1230" s="33"/>
-      <c r="F1230" s="34"/>
+      <c r="B1230" s="30"/>
+      <c r="C1230" s="30"/>
+      <c r="D1230" s="30"/>
+      <c r="E1230" s="30"/>
+      <c r="F1230" s="31"/>
     </row>
     <row r="1231" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1231" s="26" t="s">
@@ -19368,11 +19371,11 @@
       <c r="A1236" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B1236" s="33"/>
-      <c r="C1236" s="33"/>
-      <c r="D1236" s="33"/>
-      <c r="E1236" s="33"/>
-      <c r="F1236" s="34"/>
+      <c r="B1236" s="30"/>
+      <c r="C1236" s="30"/>
+      <c r="D1236" s="30"/>
+      <c r="E1236" s="30"/>
+      <c r="F1236" s="31"/>
     </row>
     <row r="1237" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1237" s="26" t="s">
@@ -19412,125 +19415,125 @@
       <c r="A1241" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B1241" s="33"/>
-      <c r="C1241" s="33"/>
-      <c r="D1241" s="33"/>
-      <c r="E1241" s="33"/>
-      <c r="F1241" s="34"/>
+      <c r="B1241" s="30"/>
+      <c r="C1241" s="30"/>
+      <c r="D1241" s="30"/>
+      <c r="E1241" s="30"/>
+      <c r="F1241" s="31"/>
     </row>
     <row r="1242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1242" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B1242" s="42" t="s">
+      <c r="B1242" s="40" t="s">
         <v>1206</v>
       </c>
-      <c r="C1242" s="33"/>
-      <c r="D1242" s="33"/>
-      <c r="E1242" s="33"/>
-      <c r="F1242" s="34"/>
+      <c r="C1242" s="30"/>
+      <c r="D1242" s="30"/>
+      <c r="E1242" s="30"/>
+      <c r="F1242" s="31"/>
     </row>
     <row r="1245" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1245" s="40" t="s">
+      <c r="A1245" s="43" t="s">
         <v>1207</v>
       </c>
-      <c r="B1245" s="30"/>
-      <c r="C1245" s="30"/>
-      <c r="D1245" s="30"/>
-      <c r="E1245" s="30"/>
-      <c r="F1245" s="30"/>
+      <c r="B1245" s="33"/>
+      <c r="C1245" s="33"/>
+      <c r="D1245" s="33"/>
+      <c r="E1245" s="33"/>
+      <c r="F1245" s="33"/>
     </row>
     <row r="1246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1246" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B1246" s="33"/>
-      <c r="C1246" s="33"/>
-      <c r="D1246" s="33"/>
-      <c r="E1246" s="33"/>
-      <c r="F1246" s="34"/>
+      <c r="B1246" s="30"/>
+      <c r="C1246" s="30"/>
+      <c r="D1246" s="30"/>
+      <c r="E1246" s="30"/>
+      <c r="F1246" s="31"/>
     </row>
     <row r="1247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1247" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B1247" s="42" t="s">
+      <c r="B1247" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C1247" s="33"/>
-      <c r="D1247" s="33"/>
-      <c r="E1247" s="33"/>
-      <c r="F1247" s="34"/>
+      <c r="C1247" s="30"/>
+      <c r="D1247" s="30"/>
+      <c r="E1247" s="30"/>
+      <c r="F1247" s="31"/>
     </row>
     <row r="1248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1248" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B1248" s="42" t="s">
+      <c r="B1248" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C1248" s="33"/>
-      <c r="D1248" s="33"/>
-      <c r="E1248" s="33"/>
-      <c r="F1248" s="34"/>
+      <c r="C1248" s="30"/>
+      <c r="D1248" s="30"/>
+      <c r="E1248" s="30"/>
+      <c r="F1248" s="31"/>
     </row>
     <row r="1249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1249" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B1249" s="42" t="s">
+      <c r="B1249" s="40" t="s">
         <v>1208</v>
       </c>
-      <c r="C1249" s="33"/>
-      <c r="D1249" s="33"/>
-      <c r="E1249" s="33"/>
-      <c r="F1249" s="34"/>
+      <c r="C1249" s="30"/>
+      <c r="D1249" s="30"/>
+      <c r="E1249" s="30"/>
+      <c r="F1249" s="31"/>
     </row>
     <row r="1250" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1250" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B1250" s="42" t="s">
+      <c r="B1250" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="C1250" s="33"/>
-      <c r="D1250" s="33"/>
-      <c r="E1250" s="33"/>
-      <c r="F1250" s="34"/>
+      <c r="C1250" s="30"/>
+      <c r="D1250" s="30"/>
+      <c r="E1250" s="30"/>
+      <c r="F1250" s="31"/>
     </row>
     <row r="1251" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1252" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1252" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B1252" s="33"/>
-      <c r="C1252" s="33"/>
-      <c r="D1252" s="33"/>
-      <c r="E1252" s="33"/>
-      <c r="F1252" s="34"/>
+      <c r="B1252" s="30"/>
+      <c r="C1252" s="30"/>
+      <c r="D1252" s="30"/>
+      <c r="E1252" s="30"/>
+      <c r="F1252" s="31"/>
     </row>
     <row r="1253" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1253" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B1253" s="42" t="s">
+      <c r="B1253" s="40" t="s">
         <v>704</v>
       </c>
-      <c r="C1253" s="33"/>
-      <c r="D1253" s="33"/>
-      <c r="E1253" s="33"/>
-      <c r="F1253" s="34"/>
+      <c r="C1253" s="30"/>
+      <c r="D1253" s="30"/>
+      <c r="E1253" s="30"/>
+      <c r="F1253" s="31"/>
     </row>
     <row r="1254" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1255" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1255" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B1255" s="33"/>
-      <c r="C1255" s="33"/>
-      <c r="D1255" s="33"/>
-      <c r="E1255" s="33"/>
-      <c r="F1255" s="34"/>
+      <c r="B1255" s="30"/>
+      <c r="C1255" s="30"/>
+      <c r="D1255" s="30"/>
+      <c r="E1255" s="30"/>
+      <c r="F1255" s="31"/>
     </row>
     <row r="1256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1256" s="26" t="s">
@@ -19558,11 +19561,11 @@
       <c r="A1259" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B1259" s="33"/>
-      <c r="C1259" s="33"/>
-      <c r="D1259" s="33"/>
-      <c r="E1259" s="33"/>
-      <c r="F1259" s="34"/>
+      <c r="B1259" s="30"/>
+      <c r="C1259" s="30"/>
+      <c r="D1259" s="30"/>
+      <c r="E1259" s="30"/>
+      <c r="F1259" s="31"/>
     </row>
     <row r="1260" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1260" s="26" t="s">
@@ -19585,11 +19588,11 @@
       <c r="A1263" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B1263" s="33"/>
-      <c r="C1263" s="33"/>
-      <c r="D1263" s="33"/>
-      <c r="E1263" s="33"/>
-      <c r="F1263" s="34"/>
+      <c r="B1263" s="30"/>
+      <c r="C1263" s="30"/>
+      <c r="D1263" s="30"/>
+      <c r="E1263" s="30"/>
+      <c r="F1263" s="31"/>
     </row>
     <row r="1264" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1264" s="26" t="s">
@@ -19637,11 +19640,11 @@
       <c r="A1268" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B1268" s="33"/>
-      <c r="C1268" s="33"/>
-      <c r="D1268" s="33"/>
-      <c r="E1268" s="33"/>
-      <c r="F1268" s="34"/>
+      <c r="B1268" s="30"/>
+      <c r="C1268" s="30"/>
+      <c r="D1268" s="30"/>
+      <c r="E1268" s="30"/>
+      <c r="F1268" s="31"/>
     </row>
     <row r="1269" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1269" s="26" t="s">
@@ -19664,56 +19667,56 @@
       <c r="A1272" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B1272" s="33"/>
-      <c r="C1272" s="33"/>
-      <c r="D1272" s="33"/>
-      <c r="E1272" s="33"/>
-      <c r="F1272" s="34"/>
+      <c r="B1272" s="30"/>
+      <c r="C1272" s="30"/>
+      <c r="D1272" s="30"/>
+      <c r="E1272" s="30"/>
+      <c r="F1272" s="31"/>
     </row>
     <row r="1273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1273" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B1273" s="42" t="s">
+      <c r="B1273" s="40" t="s">
         <v>1218</v>
       </c>
-      <c r="C1273" s="33"/>
-      <c r="D1273" s="33"/>
-      <c r="E1273" s="33"/>
-      <c r="F1273" s="34"/>
+      <c r="C1273" s="30"/>
+      <c r="D1273" s="30"/>
+      <c r="E1273" s="30"/>
+      <c r="F1273" s="31"/>
     </row>
     <row r="1275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1275" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B1275" s="33"/>
-      <c r="C1275" s="33"/>
-      <c r="D1275" s="33"/>
-      <c r="E1275" s="33"/>
-      <c r="F1275" s="34"/>
+      <c r="B1275" s="30"/>
+      <c r="C1275" s="30"/>
+      <c r="D1275" s="30"/>
+      <c r="E1275" s="30"/>
+      <c r="F1275" s="31"/>
     </row>
     <row r="1276" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1276" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B1276" s="42" t="s">
+      <c r="B1276" s="40" t="s">
         <v>1219</v>
       </c>
-      <c r="C1276" s="33"/>
-      <c r="D1276" s="33"/>
-      <c r="E1276" s="33"/>
-      <c r="F1276" s="34"/>
+      <c r="C1276" s="30"/>
+      <c r="D1276" s="30"/>
+      <c r="E1276" s="30"/>
+      <c r="F1276" s="31"/>
     </row>
     <row r="1277" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1278" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B1278" s="33"/>
-      <c r="C1278" s="33"/>
-      <c r="D1278" s="33"/>
-      <c r="E1278" s="33"/>
-      <c r="F1278" s="34"/>
+      <c r="B1278" s="30"/>
+      <c r="C1278" s="30"/>
+      <c r="D1278" s="30"/>
+      <c r="E1278" s="30"/>
+      <c r="F1278" s="31"/>
     </row>
     <row r="1279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1279" s="26" t="s">
@@ -19803,11 +19806,11 @@
       <c r="A1286" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B1286" s="33"/>
-      <c r="C1286" s="33"/>
-      <c r="D1286" s="33"/>
-      <c r="E1286" s="33"/>
-      <c r="F1286" s="34"/>
+      <c r="B1286" s="30"/>
+      <c r="C1286" s="30"/>
+      <c r="D1286" s="30"/>
+      <c r="E1286" s="30"/>
+      <c r="F1286" s="31"/>
     </row>
     <row r="1287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1287" s="26" t="s">
@@ -19869,11 +19872,11 @@
       <c r="A1295" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B1295" s="33"/>
-      <c r="C1295" s="33"/>
-      <c r="D1295" s="33"/>
-      <c r="E1295" s="33"/>
-      <c r="F1295" s="34"/>
+      <c r="B1295" s="30"/>
+      <c r="C1295" s="30"/>
+      <c r="D1295" s="30"/>
+      <c r="E1295" s="30"/>
+      <c r="F1295" s="31"/>
     </row>
     <row r="1296" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1296" s="26" t="s">
@@ -19935,11 +19938,11 @@
       <c r="A1301" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B1301" s="33"/>
-      <c r="C1301" s="33"/>
-      <c r="D1301" s="33"/>
-      <c r="E1301" s="33"/>
-      <c r="F1301" s="34"/>
+      <c r="B1301" s="30"/>
+      <c r="C1301" s="30"/>
+      <c r="D1301" s="30"/>
+      <c r="E1301" s="30"/>
+      <c r="F1301" s="31"/>
     </row>
     <row r="1302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1302" s="26" t="s">
@@ -19979,123 +19982,123 @@
       <c r="A1306" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B1306" s="33"/>
-      <c r="C1306" s="33"/>
-      <c r="D1306" s="33"/>
-      <c r="E1306" s="33"/>
-      <c r="F1306" s="34"/>
+      <c r="B1306" s="30"/>
+      <c r="C1306" s="30"/>
+      <c r="D1306" s="30"/>
+      <c r="E1306" s="30"/>
+      <c r="F1306" s="31"/>
     </row>
     <row r="1307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1307" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B1307" s="42" t="s">
+      <c r="B1307" s="40" t="s">
         <v>1248</v>
       </c>
-      <c r="C1307" s="33"/>
-      <c r="D1307" s="33"/>
-      <c r="E1307" s="33"/>
-      <c r="F1307" s="34"/>
+      <c r="C1307" s="30"/>
+      <c r="D1307" s="30"/>
+      <c r="E1307" s="30"/>
+      <c r="F1307" s="31"/>
     </row>
     <row r="1310" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1310" s="40" t="s">
+      <c r="A1310" s="43" t="s">
         <v>1249</v>
       </c>
-      <c r="B1310" s="30"/>
-      <c r="C1310" s="30"/>
-      <c r="D1310" s="30"/>
-      <c r="E1310" s="30"/>
-      <c r="F1310" s="30"/>
+      <c r="B1310" s="33"/>
+      <c r="C1310" s="33"/>
+      <c r="D1310" s="33"/>
+      <c r="E1310" s="33"/>
+      <c r="F1310" s="33"/>
     </row>
     <row r="1311" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1311" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B1311" s="33"/>
-      <c r="C1311" s="33"/>
-      <c r="D1311" s="33"/>
-      <c r="E1311" s="33"/>
-      <c r="F1311" s="34"/>
+      <c r="B1311" s="30"/>
+      <c r="C1311" s="30"/>
+      <c r="D1311" s="30"/>
+      <c r="E1311" s="30"/>
+      <c r="F1311" s="31"/>
     </row>
     <row r="1312" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1312" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B1312" s="42" t="s">
+      <c r="B1312" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C1312" s="33"/>
-      <c r="D1312" s="33"/>
-      <c r="E1312" s="33"/>
-      <c r="F1312" s="34"/>
+      <c r="C1312" s="30"/>
+      <c r="D1312" s="30"/>
+      <c r="E1312" s="30"/>
+      <c r="F1312" s="31"/>
     </row>
     <row r="1313" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1313" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B1313" s="42" t="s">
+      <c r="B1313" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C1313" s="33"/>
-      <c r="D1313" s="33"/>
-      <c r="E1313" s="33"/>
-      <c r="F1313" s="34"/>
+      <c r="C1313" s="30"/>
+      <c r="D1313" s="30"/>
+      <c r="E1313" s="30"/>
+      <c r="F1313" s="31"/>
     </row>
     <row r="1314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1314" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B1314" s="42" t="s">
+      <c r="B1314" s="40" t="s">
         <v>1250</v>
       </c>
-      <c r="C1314" s="33"/>
-      <c r="D1314" s="33"/>
-      <c r="E1314" s="33"/>
-      <c r="F1314" s="34"/>
+      <c r="C1314" s="30"/>
+      <c r="D1314" s="30"/>
+      <c r="E1314" s="30"/>
+      <c r="F1314" s="31"/>
     </row>
     <row r="1315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1315" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B1315" s="42" t="s">
+      <c r="B1315" s="40" t="s">
         <v>486</v>
       </c>
-      <c r="C1315" s="33"/>
-      <c r="D1315" s="33"/>
-      <c r="E1315" s="33"/>
-      <c r="F1315" s="34"/>
+      <c r="C1315" s="30"/>
+      <c r="D1315" s="30"/>
+      <c r="E1315" s="30"/>
+      <c r="F1315" s="31"/>
     </row>
     <row r="1317" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1317" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B1317" s="33"/>
-      <c r="C1317" s="33"/>
-      <c r="D1317" s="33"/>
-      <c r="E1317" s="33"/>
-      <c r="F1317" s="34"/>
+      <c r="B1317" s="30"/>
+      <c r="C1317" s="30"/>
+      <c r="D1317" s="30"/>
+      <c r="E1317" s="30"/>
+      <c r="F1317" s="31"/>
     </row>
     <row r="1318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1318" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B1318" s="42" t="s">
+      <c r="B1318" s="40" t="s">
         <v>1251</v>
       </c>
-      <c r="C1318" s="33"/>
-      <c r="D1318" s="33"/>
-      <c r="E1318" s="33"/>
-      <c r="F1318" s="34"/>
+      <c r="C1318" s="30"/>
+      <c r="D1318" s="30"/>
+      <c r="E1318" s="30"/>
+      <c r="F1318" s="31"/>
     </row>
     <row r="1320" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1320" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B1320" s="33"/>
-      <c r="C1320" s="33"/>
-      <c r="D1320" s="33"/>
-      <c r="E1320" s="33"/>
-      <c r="F1320" s="34"/>
+      <c r="B1320" s="30"/>
+      <c r="C1320" s="30"/>
+      <c r="D1320" s="30"/>
+      <c r="E1320" s="30"/>
+      <c r="F1320" s="31"/>
     </row>
     <row r="1321" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1321" s="26" t="s">
@@ -20189,11 +20192,11 @@
       <c r="A1330" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B1330" s="33"/>
-      <c r="C1330" s="33"/>
-      <c r="D1330" s="33"/>
-      <c r="E1330" s="33"/>
-      <c r="F1330" s="34"/>
+      <c r="B1330" s="30"/>
+      <c r="C1330" s="30"/>
+      <c r="D1330" s="30"/>
+      <c r="E1330" s="30"/>
+      <c r="F1330" s="31"/>
     </row>
     <row r="1331" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1331" s="26" t="s">
@@ -20224,11 +20227,11 @@
       <c r="A1335" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B1335" s="33"/>
-      <c r="C1335" s="33"/>
-      <c r="D1335" s="33"/>
-      <c r="E1335" s="33"/>
-      <c r="F1335" s="34"/>
+      <c r="B1335" s="30"/>
+      <c r="C1335" s="30"/>
+      <c r="D1335" s="30"/>
+      <c r="E1335" s="30"/>
+      <c r="F1335" s="31"/>
     </row>
     <row r="1336" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1336" s="26" t="s">
@@ -20305,11 +20308,11 @@
       <c r="A1342" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B1342" s="33"/>
-      <c r="C1342" s="33"/>
-      <c r="D1342" s="33"/>
-      <c r="E1342" s="33"/>
-      <c r="F1342" s="34"/>
+      <c r="B1342" s="30"/>
+      <c r="C1342" s="30"/>
+      <c r="D1342" s="30"/>
+      <c r="E1342" s="30"/>
+      <c r="F1342" s="31"/>
     </row>
     <row r="1343" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1343" s="26" t="s">
@@ -20355,55 +20358,55 @@
       <c r="A1349" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B1349" s="33"/>
-      <c r="C1349" s="33"/>
-      <c r="D1349" s="33"/>
-      <c r="E1349" s="33"/>
-      <c r="F1349" s="34"/>
+      <c r="B1349" s="30"/>
+      <c r="C1349" s="30"/>
+      <c r="D1349" s="30"/>
+      <c r="E1349" s="30"/>
+      <c r="F1349" s="31"/>
     </row>
     <row r="1350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1350" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B1350" s="42" t="s">
+      <c r="B1350" s="40" t="s">
         <v>1275</v>
       </c>
-      <c r="C1350" s="33"/>
-      <c r="D1350" s="33"/>
-      <c r="E1350" s="33"/>
-      <c r="F1350" s="34"/>
+      <c r="C1350" s="30"/>
+      <c r="D1350" s="30"/>
+      <c r="E1350" s="30"/>
+      <c r="F1350" s="31"/>
     </row>
     <row r="1352" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1352" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B1352" s="33"/>
-      <c r="C1352" s="33"/>
-      <c r="D1352" s="33"/>
-      <c r="E1352" s="33"/>
-      <c r="F1352" s="34"/>
+      <c r="B1352" s="30"/>
+      <c r="C1352" s="30"/>
+      <c r="D1352" s="30"/>
+      <c r="E1352" s="30"/>
+      <c r="F1352" s="31"/>
     </row>
     <row r="1353" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1353" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B1353" s="42" t="s">
+      <c r="B1353" s="40" t="s">
         <v>1276</v>
       </c>
-      <c r="C1353" s="33"/>
-      <c r="D1353" s="33"/>
-      <c r="E1353" s="33"/>
-      <c r="F1353" s="34"/>
+      <c r="C1353" s="30"/>
+      <c r="D1353" s="30"/>
+      <c r="E1353" s="30"/>
+      <c r="F1353" s="31"/>
     </row>
     <row r="1355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1355" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B1355" s="33"/>
-      <c r="C1355" s="33"/>
-      <c r="D1355" s="33"/>
-      <c r="E1355" s="33"/>
-      <c r="F1355" s="34"/>
+      <c r="B1355" s="30"/>
+      <c r="C1355" s="30"/>
+      <c r="D1355" s="30"/>
+      <c r="E1355" s="30"/>
+      <c r="F1355" s="31"/>
     </row>
     <row r="1356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1356" s="26" t="s">
@@ -20507,11 +20510,11 @@
       <c r="A1364" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B1364" s="33"/>
-      <c r="C1364" s="33"/>
-      <c r="D1364" s="33"/>
-      <c r="E1364" s="33"/>
-      <c r="F1364" s="34"/>
+      <c r="B1364" s="30"/>
+      <c r="C1364" s="30"/>
+      <c r="D1364" s="30"/>
+      <c r="E1364" s="30"/>
+      <c r="F1364" s="31"/>
     </row>
     <row r="1365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1365" s="26" t="s">
@@ -20581,11 +20584,11 @@
       <c r="A1374" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B1374" s="33"/>
-      <c r="C1374" s="33"/>
-      <c r="D1374" s="33"/>
-      <c r="E1374" s="33"/>
-      <c r="F1374" s="34"/>
+      <c r="B1374" s="30"/>
+      <c r="C1374" s="30"/>
+      <c r="D1374" s="30"/>
+      <c r="E1374" s="30"/>
+      <c r="F1374" s="31"/>
     </row>
     <row r="1375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1375" s="26" t="s">
@@ -20661,11 +20664,11 @@
       <c r="A1381" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B1381" s="33"/>
-      <c r="C1381" s="33"/>
-      <c r="D1381" s="33"/>
-      <c r="E1381" s="33"/>
-      <c r="F1381" s="34"/>
+      <c r="B1381" s="30"/>
+      <c r="C1381" s="30"/>
+      <c r="D1381" s="30"/>
+      <c r="E1381" s="30"/>
+      <c r="F1381" s="31"/>
     </row>
     <row r="1382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1382" s="26" t="s">
@@ -20704,123 +20707,123 @@
       <c r="A1386" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B1386" s="33"/>
-      <c r="C1386" s="33"/>
-      <c r="D1386" s="33"/>
-      <c r="E1386" s="33"/>
-      <c r="F1386" s="34"/>
+      <c r="B1386" s="30"/>
+      <c r="C1386" s="30"/>
+      <c r="D1386" s="30"/>
+      <c r="E1386" s="30"/>
+      <c r="F1386" s="31"/>
     </row>
     <row r="1387" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1387" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B1387" s="42" t="s">
+      <c r="B1387" s="40" t="s">
         <v>1308</v>
       </c>
-      <c r="C1387" s="33"/>
-      <c r="D1387" s="33"/>
-      <c r="E1387" s="33"/>
-      <c r="F1387" s="34"/>
+      <c r="C1387" s="30"/>
+      <c r="D1387" s="30"/>
+      <c r="E1387" s="30"/>
+      <c r="F1387" s="31"/>
     </row>
     <row r="1390" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1390" s="40" t="s">
+      <c r="A1390" s="43" t="s">
         <v>1309</v>
       </c>
-      <c r="B1390" s="30"/>
-      <c r="C1390" s="30"/>
-      <c r="D1390" s="30"/>
-      <c r="E1390" s="30"/>
-      <c r="F1390" s="30"/>
+      <c r="B1390" s="33"/>
+      <c r="C1390" s="33"/>
+      <c r="D1390" s="33"/>
+      <c r="E1390" s="33"/>
+      <c r="F1390" s="33"/>
     </row>
     <row r="1391" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1391" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B1391" s="33"/>
-      <c r="C1391" s="33"/>
-      <c r="D1391" s="33"/>
-      <c r="E1391" s="33"/>
-      <c r="F1391" s="34"/>
+      <c r="B1391" s="30"/>
+      <c r="C1391" s="30"/>
+      <c r="D1391" s="30"/>
+      <c r="E1391" s="30"/>
+      <c r="F1391" s="31"/>
     </row>
     <row r="1392" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1392" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B1392" s="42" t="s">
+      <c r="B1392" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C1392" s="33"/>
-      <c r="D1392" s="33"/>
-      <c r="E1392" s="33"/>
-      <c r="F1392" s="34"/>
+      <c r="C1392" s="30"/>
+      <c r="D1392" s="30"/>
+      <c r="E1392" s="30"/>
+      <c r="F1392" s="31"/>
     </row>
     <row r="1393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1393" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B1393" s="42" t="s">
+      <c r="B1393" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C1393" s="33"/>
-      <c r="D1393" s="33"/>
-      <c r="E1393" s="33"/>
-      <c r="F1393" s="34"/>
+      <c r="C1393" s="30"/>
+      <c r="D1393" s="30"/>
+      <c r="E1393" s="30"/>
+      <c r="F1393" s="31"/>
     </row>
     <row r="1394" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1394" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B1394" s="42" t="s">
+      <c r="B1394" s="40" t="s">
         <v>1310</v>
       </c>
-      <c r="C1394" s="33"/>
-      <c r="D1394" s="33"/>
-      <c r="E1394" s="33"/>
-      <c r="F1394" s="34"/>
+      <c r="C1394" s="30"/>
+      <c r="D1394" s="30"/>
+      <c r="E1394" s="30"/>
+      <c r="F1394" s="31"/>
     </row>
     <row r="1395" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1395" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B1395" s="42" t="s">
+      <c r="B1395" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="C1395" s="33"/>
-      <c r="D1395" s="33"/>
-      <c r="E1395" s="33"/>
-      <c r="F1395" s="34"/>
+      <c r="C1395" s="30"/>
+      <c r="D1395" s="30"/>
+      <c r="E1395" s="30"/>
+      <c r="F1395" s="31"/>
     </row>
     <row r="1397" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1397" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B1397" s="33"/>
-      <c r="C1397" s="33"/>
-      <c r="D1397" s="33"/>
-      <c r="E1397" s="33"/>
-      <c r="F1397" s="34"/>
+      <c r="B1397" s="30"/>
+      <c r="C1397" s="30"/>
+      <c r="D1397" s="30"/>
+      <c r="E1397" s="30"/>
+      <c r="F1397" s="31"/>
     </row>
     <row r="1398" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1398" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B1398" s="42" t="s">
+      <c r="B1398" s="40" t="s">
         <v>704</v>
       </c>
-      <c r="C1398" s="33"/>
-      <c r="D1398" s="33"/>
-      <c r="E1398" s="33"/>
-      <c r="F1398" s="34"/>
+      <c r="C1398" s="30"/>
+      <c r="D1398" s="30"/>
+      <c r="E1398" s="30"/>
+      <c r="F1398" s="31"/>
     </row>
     <row r="1400" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1400" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B1400" s="33"/>
-      <c r="C1400" s="33"/>
-      <c r="D1400" s="33"/>
-      <c r="E1400" s="33"/>
-      <c r="F1400" s="34"/>
+      <c r="B1400" s="30"/>
+      <c r="C1400" s="30"/>
+      <c r="D1400" s="30"/>
+      <c r="E1400" s="30"/>
+      <c r="F1400" s="31"/>
     </row>
     <row r="1401" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1401" s="26" t="s">
@@ -20870,11 +20873,11 @@
       <c r="A1406" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B1406" s="33"/>
-      <c r="C1406" s="33"/>
-      <c r="D1406" s="33"/>
-      <c r="E1406" s="33"/>
-      <c r="F1406" s="34"/>
+      <c r="B1406" s="30"/>
+      <c r="C1406" s="30"/>
+      <c r="D1406" s="30"/>
+      <c r="E1406" s="30"/>
+      <c r="F1406" s="31"/>
     </row>
     <row r="1407" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1407" s="26" t="s">
@@ -20896,11 +20899,11 @@
       <c r="A1410" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B1410" s="33"/>
-      <c r="C1410" s="33"/>
-      <c r="D1410" s="33"/>
-      <c r="E1410" s="33"/>
-      <c r="F1410" s="34"/>
+      <c r="B1410" s="30"/>
+      <c r="C1410" s="30"/>
+      <c r="D1410" s="30"/>
+      <c r="E1410" s="30"/>
+      <c r="F1410" s="31"/>
     </row>
     <row r="1411" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1411" s="26" t="s">
@@ -20948,11 +20951,11 @@
       <c r="A1415" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B1415" s="33"/>
-      <c r="C1415" s="33"/>
-      <c r="D1415" s="33"/>
-      <c r="E1415" s="33"/>
-      <c r="F1415" s="34"/>
+      <c r="B1415" s="30"/>
+      <c r="C1415" s="30"/>
+      <c r="D1415" s="30"/>
+      <c r="E1415" s="30"/>
+      <c r="F1415" s="31"/>
     </row>
     <row r="1416" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1416" s="26" t="s">
@@ -20990,55 +20993,55 @@
       <c r="A1421" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B1421" s="33"/>
-      <c r="C1421" s="33"/>
-      <c r="D1421" s="33"/>
-      <c r="E1421" s="33"/>
-      <c r="F1421" s="34"/>
+      <c r="B1421" s="30"/>
+      <c r="C1421" s="30"/>
+      <c r="D1421" s="30"/>
+      <c r="E1421" s="30"/>
+      <c r="F1421" s="31"/>
     </row>
     <row r="1422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1422" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="B1422" s="42" t="s">
+      <c r="B1422" s="40" t="s">
         <v>1323</v>
       </c>
-      <c r="C1422" s="33"/>
-      <c r="D1422" s="33"/>
-      <c r="E1422" s="33"/>
-      <c r="F1422" s="34"/>
+      <c r="C1422" s="30"/>
+      <c r="D1422" s="30"/>
+      <c r="E1422" s="30"/>
+      <c r="F1422" s="31"/>
     </row>
     <row r="1424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1424" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B1424" s="33"/>
-      <c r="C1424" s="33"/>
-      <c r="D1424" s="33"/>
-      <c r="E1424" s="33"/>
-      <c r="F1424" s="34"/>
+      <c r="B1424" s="30"/>
+      <c r="C1424" s="30"/>
+      <c r="D1424" s="30"/>
+      <c r="E1424" s="30"/>
+      <c r="F1424" s="31"/>
     </row>
     <row r="1425" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1425" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B1425" s="42" t="s">
+      <c r="B1425" s="40" t="s">
         <v>1324</v>
       </c>
-      <c r="C1425" s="33"/>
-      <c r="D1425" s="33"/>
-      <c r="E1425" s="33"/>
-      <c r="F1425" s="34"/>
+      <c r="C1425" s="30"/>
+      <c r="D1425" s="30"/>
+      <c r="E1425" s="30"/>
+      <c r="F1425" s="31"/>
     </row>
     <row r="1427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1427" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B1427" s="33"/>
-      <c r="C1427" s="33"/>
-      <c r="D1427" s="33"/>
-      <c r="E1427" s="33"/>
-      <c r="F1427" s="34"/>
+      <c r="B1427" s="30"/>
+      <c r="C1427" s="30"/>
+      <c r="D1427" s="30"/>
+      <c r="E1427" s="30"/>
+      <c r="F1427" s="31"/>
     </row>
     <row r="1428" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1428" s="26" t="s">
@@ -21128,11 +21131,11 @@
       <c r="A1435" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B1435" s="33"/>
-      <c r="C1435" s="33"/>
-      <c r="D1435" s="33"/>
-      <c r="E1435" s="33"/>
-      <c r="F1435" s="34"/>
+      <c r="B1435" s="30"/>
+      <c r="C1435" s="30"/>
+      <c r="D1435" s="30"/>
+      <c r="E1435" s="30"/>
+      <c r="F1435" s="31"/>
     </row>
     <row r="1436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1436" s="26" t="s">
@@ -21210,11 +21213,11 @@
       <c r="A1446" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B1446" s="33"/>
-      <c r="C1446" s="33"/>
-      <c r="D1446" s="33"/>
-      <c r="E1446" s="33"/>
-      <c r="F1446" s="34"/>
+      <c r="B1446" s="30"/>
+      <c r="C1446" s="30"/>
+      <c r="D1446" s="30"/>
+      <c r="E1446" s="30"/>
+      <c r="F1446" s="31"/>
     </row>
     <row r="1447" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1447" s="26" t="s">
@@ -21262,11 +21265,11 @@
       <c r="A1451" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B1451" s="33"/>
-      <c r="C1451" s="33"/>
-      <c r="D1451" s="33"/>
-      <c r="E1451" s="33"/>
-      <c r="F1451" s="34"/>
+      <c r="B1451" s="30"/>
+      <c r="C1451" s="30"/>
+      <c r="D1451" s="30"/>
+      <c r="E1451" s="30"/>
+      <c r="F1451" s="31"/>
     </row>
     <row r="1452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1452" s="26" t="s">
@@ -21305,55 +21308,55 @@
       <c r="A1456" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="B1456" s="33"/>
-      <c r="C1456" s="33"/>
-      <c r="D1456" s="33"/>
-      <c r="E1456" s="33"/>
-      <c r="F1456" s="34"/>
+      <c r="B1456" s="30"/>
+      <c r="C1456" s="30"/>
+      <c r="D1456" s="30"/>
+      <c r="E1456" s="30"/>
+      <c r="F1456" s="31"/>
     </row>
     <row r="1457" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1457" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B1457" s="42" t="s">
+      <c r="B1457" s="40" t="s">
         <v>1347</v>
       </c>
-      <c r="C1457" s="33"/>
-      <c r="D1457" s="33"/>
-      <c r="E1457" s="33"/>
-      <c r="F1457" s="34"/>
+      <c r="C1457" s="30"/>
+      <c r="D1457" s="30"/>
+      <c r="E1457" s="30"/>
+      <c r="F1457" s="31"/>
     </row>
     <row r="1460" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1460" s="40" t="s">
+      <c r="A1460" s="43" t="s">
         <v>1348</v>
       </c>
-      <c r="B1460" s="30"/>
-      <c r="C1460" s="30"/>
-      <c r="D1460" s="30"/>
-      <c r="E1460" s="30"/>
-      <c r="F1460" s="30"/>
+      <c r="B1460" s="33"/>
+      <c r="C1460" s="33"/>
+      <c r="D1460" s="33"/>
+      <c r="E1460" s="33"/>
+      <c r="F1460" s="33"/>
     </row>
     <row r="1461" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1461" s="41" t="s">
         <v>1349</v>
       </c>
-      <c r="B1461" s="33"/>
-      <c r="C1461" s="33"/>
-      <c r="D1461" s="33"/>
-      <c r="E1461" s="33"/>
-      <c r="F1461" s="34"/>
+      <c r="B1461" s="30"/>
+      <c r="C1461" s="30"/>
+      <c r="D1461" s="30"/>
+      <c r="E1461" s="30"/>
+      <c r="F1461" s="31"/>
     </row>
     <row r="1462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1462" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B1462" s="42" t="s">
+      <c r="B1462" s="40" t="s">
         <v>1350</v>
       </c>
-      <c r="C1462" s="33"/>
-      <c r="D1462" s="33"/>
-      <c r="E1462" s="33"/>
-      <c r="F1462" s="34"/>
+      <c r="C1462" s="30"/>
+      <c r="D1462" s="30"/>
+      <c r="E1462" s="30"/>
+      <c r="F1462" s="31"/>
     </row>
     <row r="1463" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1463" s="26" t="s">
@@ -21447,35 +21450,35 @@
       <c r="A1471" s="24" t="s">
         <v>1374</v>
       </c>
-      <c r="B1471" s="42" t="s">
+      <c r="B1471" s="40" t="s">
         <v>1375</v>
       </c>
-      <c r="C1471" s="33"/>
-      <c r="D1471" s="33"/>
-      <c r="E1471" s="33"/>
-      <c r="F1471" s="34"/>
+      <c r="C1471" s="30"/>
+      <c r="D1471" s="30"/>
+      <c r="E1471" s="30"/>
+      <c r="F1471" s="31"/>
     </row>
     <row r="1473" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1473" s="41" t="s">
         <v>1376</v>
       </c>
-      <c r="B1473" s="33"/>
-      <c r="C1473" s="33"/>
-      <c r="D1473" s="33"/>
-      <c r="E1473" s="33"/>
-      <c r="F1473" s="34"/>
+      <c r="B1473" s="30"/>
+      <c r="C1473" s="30"/>
+      <c r="D1473" s="30"/>
+      <c r="E1473" s="30"/>
+      <c r="F1473" s="31"/>
     </row>
     <row r="1474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1474" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B1474" s="42" t="s">
+      <c r="B1474" s="40" t="s">
         <v>1377</v>
       </c>
-      <c r="C1474" s="33"/>
-      <c r="D1474" s="33"/>
-      <c r="E1474" s="33"/>
-      <c r="F1474" s="34"/>
+      <c r="C1474" s="30"/>
+      <c r="D1474" s="30"/>
+      <c r="E1474" s="30"/>
+      <c r="F1474" s="31"/>
     </row>
     <row r="1475" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1475" s="26" t="s">
@@ -21521,54 +21524,59 @@
       <c r="A1480" s="24" t="s">
         <v>1388</v>
       </c>
-      <c r="B1480" s="42" t="s">
+      <c r="B1480" s="40" t="s">
         <v>1389</v>
       </c>
-      <c r="C1480" s="33"/>
-      <c r="D1480" s="33"/>
-      <c r="E1480" s="33"/>
-      <c r="F1480" s="34"/>
+      <c r="C1480" s="30"/>
+      <c r="D1480" s="30"/>
+      <c r="E1480" s="30"/>
+      <c r="F1480" s="31"/>
     </row>
     <row r="1482" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1482" s="41" t="s">
         <v>1390</v>
       </c>
-      <c r="B1482" s="33"/>
-      <c r="C1482" s="33"/>
-      <c r="D1482" s="33"/>
-      <c r="E1482" s="33"/>
-      <c r="F1482" s="34"/>
+      <c r="B1482" s="30"/>
+      <c r="C1482" s="30"/>
+      <c r="D1482" s="30"/>
+      <c r="E1482" s="30"/>
+      <c r="F1482" s="31"/>
     </row>
     <row r="1483" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1483" s="24" t="s">
         <v>1391</v>
       </c>
-      <c r="B1483" s="42" t="s">
+      <c r="B1483" s="40" t="s">
         <v>1392</v>
       </c>
-      <c r="C1483" s="33"/>
-      <c r="D1483" s="33"/>
-      <c r="E1483" s="33"/>
-      <c r="F1483" s="34"/>
+      <c r="C1483" s="30"/>
+      <c r="D1483" s="30"/>
+      <c r="E1483" s="30"/>
+      <c r="F1483" s="31"/>
     </row>
     <row r="1484" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1484" s="24" t="s">
         <v>1393</v>
       </c>
-      <c r="B1484" s="42" t="s">
+      <c r="B1484" s="40" t="s">
         <v>1394</v>
       </c>
-      <c r="C1484" s="33"/>
-      <c r="D1484" s="33"/>
-      <c r="E1484" s="33"/>
-      <c r="F1484" s="34"/>
+      <c r="C1484" s="30"/>
+      <c r="D1484" s="30"/>
+      <c r="E1484" s="30"/>
+      <c r="F1484" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="452">
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B822:F822"/>
-    <mergeCell ref="A597:F597"/>
-    <mergeCell ref="B1107:F1107"/>
+    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="A1057:F1057"/>
+    <mergeCell ref="B1175:F1175"/>
+    <mergeCell ref="B1096:F1096"/>
+    <mergeCell ref="A233:F233"/>
+    <mergeCell ref="A838:F838"/>
+    <mergeCell ref="A1236:F1236"/>
+    <mergeCell ref="A248:F248"/>
     <mergeCell ref="A833:F833"/>
     <mergeCell ref="B1178:F1178"/>
     <mergeCell ref="B824:F824"/>
@@ -21580,19 +21588,6 @@
     <mergeCell ref="A130:F130"/>
     <mergeCell ref="B298:F298"/>
     <mergeCell ref="A325:F325"/>
-    <mergeCell ref="A119:F119"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="A1057:F1057"/>
-    <mergeCell ref="B1175:F1175"/>
-    <mergeCell ref="B1096:F1096"/>
-    <mergeCell ref="A233:F233"/>
-    <mergeCell ref="A838:F838"/>
-    <mergeCell ref="A1236:F1236"/>
-    <mergeCell ref="A248:F248"/>
-    <mergeCell ref="B1103:F1103"/>
-    <mergeCell ref="A297:F297"/>
-    <mergeCell ref="A1002:F1002"/>
-    <mergeCell ref="A902:F902"/>
     <mergeCell ref="B117:F117"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A98:F98"/>
@@ -21601,6 +21596,22 @@
     <mergeCell ref="B1248:F1248"/>
     <mergeCell ref="A1194:F1194"/>
     <mergeCell ref="B343:F343"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="A1364:F1364"/>
+    <mergeCell ref="B269:F269"/>
+    <mergeCell ref="A888:F888"/>
+    <mergeCell ref="A182:F182"/>
+    <mergeCell ref="A1352:F1352"/>
+    <mergeCell ref="A1041:F1041"/>
+    <mergeCell ref="A633:F633"/>
+    <mergeCell ref="A1410:F1410"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B822:F822"/>
+    <mergeCell ref="A597:F597"/>
+    <mergeCell ref="B1107:F1107"/>
     <mergeCell ref="B1484:F1484"/>
     <mergeCell ref="A1286:F1286"/>
     <mergeCell ref="B821:F821"/>
@@ -21613,34 +21624,18 @@
     <mergeCell ref="B749:F749"/>
     <mergeCell ref="B1101:F1101"/>
     <mergeCell ref="B346:F346"/>
-    <mergeCell ref="A116:F116"/>
-    <mergeCell ref="A53:F53"/>
     <mergeCell ref="A180:F180"/>
     <mergeCell ref="A1060:F1060"/>
     <mergeCell ref="B961:F961"/>
-    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A1275:F1275"/>
     <mergeCell ref="A1446:F1446"/>
     <mergeCell ref="B421:F421"/>
     <mergeCell ref="B1393:F1393"/>
     <mergeCell ref="A893:F893"/>
-    <mergeCell ref="B162:F162"/>
     <mergeCell ref="B267:F267"/>
     <mergeCell ref="A230:F230"/>
     <mergeCell ref="A1128:F1128"/>
     <mergeCell ref="A922:F922"/>
-    <mergeCell ref="A1364:F1364"/>
-    <mergeCell ref="B269:F269"/>
-    <mergeCell ref="A888:F888"/>
-    <mergeCell ref="A182:F182"/>
-    <mergeCell ref="A1352:F1352"/>
-    <mergeCell ref="A1041:F1041"/>
-    <mergeCell ref="A633:F633"/>
-    <mergeCell ref="A1410:F1410"/>
-    <mergeCell ref="A820:F820"/>
-    <mergeCell ref="A991:F991"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B1027:F1027"/>
     <mergeCell ref="A1212:F1212"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A159:F159"/>
@@ -21650,6 +21645,21 @@
     <mergeCell ref="A1122:F1122"/>
     <mergeCell ref="A459:F459"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A212:F212"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A215:F215"/>
+    <mergeCell ref="A142:F142"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="A730:F730"/>
+    <mergeCell ref="A801:F801"/>
+    <mergeCell ref="B992:F992"/>
+    <mergeCell ref="B1103:F1103"/>
+    <mergeCell ref="A297:F297"/>
+    <mergeCell ref="A1002:F1002"/>
+    <mergeCell ref="A902:F902"/>
     <mergeCell ref="B1273:F1273"/>
     <mergeCell ref="A751:F751"/>
     <mergeCell ref="A1011:F1011"/>
@@ -21659,13 +21669,21 @@
     <mergeCell ref="A1051:F1051"/>
     <mergeCell ref="A777:F777"/>
     <mergeCell ref="A606:F606"/>
-    <mergeCell ref="A212:F212"/>
     <mergeCell ref="A1209:F1209"/>
-    <mergeCell ref="A108:F108"/>
     <mergeCell ref="A988:F988"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A341:F341"/>
     <mergeCell ref="A583:F583"/>
+    <mergeCell ref="A709:F709"/>
+    <mergeCell ref="A538:F538"/>
+    <mergeCell ref="A780:F780"/>
+    <mergeCell ref="B852:F852"/>
+    <mergeCell ref="A1016:F1016"/>
+    <mergeCell ref="A490:F490"/>
+    <mergeCell ref="B664:F664"/>
+    <mergeCell ref="A477:F477"/>
+    <mergeCell ref="B372:F372"/>
+    <mergeCell ref="B900:F900"/>
+    <mergeCell ref="B595:F595"/>
     <mergeCell ref="A1482:F1482"/>
     <mergeCell ref="A279:F279"/>
     <mergeCell ref="A819:F819"/>
@@ -21714,35 +21732,30 @@
     <mergeCell ref="A1095:F1095"/>
     <mergeCell ref="A661:F661"/>
     <mergeCell ref="A742:F742"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A215:F215"/>
-    <mergeCell ref="A709:F709"/>
-    <mergeCell ref="A538:F538"/>
-    <mergeCell ref="A780:F780"/>
-    <mergeCell ref="B852:F852"/>
-    <mergeCell ref="A1016:F1016"/>
-    <mergeCell ref="A490:F490"/>
-    <mergeCell ref="B664:F664"/>
-    <mergeCell ref="A477:F477"/>
-    <mergeCell ref="A142:F142"/>
-    <mergeCell ref="B372:F372"/>
-    <mergeCell ref="B900:F900"/>
-    <mergeCell ref="B595:F595"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="A730:F730"/>
-    <mergeCell ref="A801:F801"/>
-    <mergeCell ref="B992:F992"/>
-    <mergeCell ref="A965:F965"/>
-    <mergeCell ref="A148:F148"/>
-    <mergeCell ref="A275:F275"/>
-    <mergeCell ref="A446:F446"/>
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A914:F914"/>
     <mergeCell ref="B955:F955"/>
     <mergeCell ref="B1253:F1253"/>
     <mergeCell ref="A1137:F1137"/>
+    <mergeCell ref="A202:F202"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B213:F213"/>
+    <mergeCell ref="A434:F434"/>
+    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="B426:F426"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B589:F589"/>
+    <mergeCell ref="A337:F337"/>
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="B428:F428"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A820:F820"/>
+    <mergeCell ref="A991:F991"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B1027:F1027"/>
     <mergeCell ref="A1435:F1435"/>
     <mergeCell ref="A645:F645"/>
     <mergeCell ref="A943:F943"/>
@@ -21756,18 +21769,17 @@
     <mergeCell ref="A550:F550"/>
     <mergeCell ref="A1090:F1090"/>
     <mergeCell ref="A919:F919"/>
-    <mergeCell ref="A202:F202"/>
     <mergeCell ref="A1255:F1255"/>
     <mergeCell ref="B668:F668"/>
     <mergeCell ref="A1301:F1301"/>
-    <mergeCell ref="A73:F73"/>
     <mergeCell ref="B618:F618"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="B1394:F1394"/>
     <mergeCell ref="B1242:F1242"/>
     <mergeCell ref="B1387:F1387"/>
     <mergeCell ref="A617:F617"/>
+    <mergeCell ref="A266:F266"/>
+    <mergeCell ref="B663:F663"/>
+    <mergeCell ref="A360:F360"/>
     <mergeCell ref="B1471:F1471"/>
     <mergeCell ref="B1398:F1398"/>
     <mergeCell ref="B1177:F1177"/>
@@ -21777,15 +21789,21 @@
     <mergeCell ref="A1306:F1306"/>
     <mergeCell ref="A1021:F1021"/>
     <mergeCell ref="A1263:F1263"/>
-    <mergeCell ref="A266:F266"/>
     <mergeCell ref="A1148:F1148"/>
-    <mergeCell ref="B213:F213"/>
     <mergeCell ref="B816:F816"/>
-    <mergeCell ref="B663:F663"/>
-    <mergeCell ref="A360:F360"/>
     <mergeCell ref="A925:F925"/>
     <mergeCell ref="B963:F963"/>
-    <mergeCell ref="A434:F434"/>
+    <mergeCell ref="B1181:F1181"/>
+    <mergeCell ref="A829:F829"/>
+    <mergeCell ref="B1312:F1312"/>
+    <mergeCell ref="A1189:F1189"/>
+    <mergeCell ref="B1307:F1307"/>
+    <mergeCell ref="A1460:F1460"/>
+    <mergeCell ref="A1451:F1451"/>
+    <mergeCell ref="A1278:F1278"/>
+    <mergeCell ref="A1400:F1400"/>
+    <mergeCell ref="B1392:F1392"/>
+    <mergeCell ref="A1355:F1355"/>
     <mergeCell ref="B1474:F1474"/>
     <mergeCell ref="A1381:F1381"/>
     <mergeCell ref="B584:F584"/>
@@ -21810,36 +21828,6 @@
     <mergeCell ref="A1335:F1335"/>
     <mergeCell ref="A1109:F1109"/>
     <mergeCell ref="A1272:F1272"/>
-    <mergeCell ref="A173:F173"/>
-    <mergeCell ref="B1181:F1181"/>
-    <mergeCell ref="B426:F426"/>
-    <mergeCell ref="A829:F829"/>
-    <mergeCell ref="B1312:F1312"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="B589:F589"/>
-    <mergeCell ref="A337:F337"/>
-    <mergeCell ref="A166:F166"/>
-    <mergeCell ref="B428:F428"/>
-    <mergeCell ref="A103:F103"/>
-    <mergeCell ref="B344:F344"/>
-    <mergeCell ref="B222:F222"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="B1058:F1058"/>
-    <mergeCell ref="B268:F268"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A351:F351"/>
-    <mergeCell ref="A587:F587"/>
-    <mergeCell ref="A239:F239"/>
-    <mergeCell ref="A331:F331"/>
-    <mergeCell ref="A651:F651"/>
-    <mergeCell ref="B548:F548"/>
-    <mergeCell ref="B1480:F1480"/>
-    <mergeCell ref="A223:F223"/>
-    <mergeCell ref="A294:F294"/>
-    <mergeCell ref="A465:F465"/>
-    <mergeCell ref="A763:F763"/>
-    <mergeCell ref="B1102:F1102"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A311:F311"/>
     <mergeCell ref="B1104:F1104"/>
@@ -21851,37 +21839,43 @@
     <mergeCell ref="A1164:F1164"/>
     <mergeCell ref="A623:F623"/>
     <mergeCell ref="A452:F452"/>
-    <mergeCell ref="B1353:F1353"/>
-    <mergeCell ref="A1421:F1421"/>
     <mergeCell ref="B738:F738"/>
     <mergeCell ref="B1061:F1061"/>
-    <mergeCell ref="B1170:F1170"/>
-    <mergeCell ref="B1395:F1395"/>
     <mergeCell ref="B273:F273"/>
-    <mergeCell ref="B92:F92"/>
-    <mergeCell ref="A226:F226"/>
-    <mergeCell ref="A462:F462"/>
-    <mergeCell ref="B855:F855"/>
-    <mergeCell ref="A1189:F1189"/>
-    <mergeCell ref="A241:F241"/>
-    <mergeCell ref="A355:F355"/>
-    <mergeCell ref="B694:F694"/>
-    <mergeCell ref="B1307:F1307"/>
-    <mergeCell ref="A933:F933"/>
-    <mergeCell ref="A221:F221"/>
-    <mergeCell ref="A899:F899"/>
-    <mergeCell ref="A699:F699"/>
-    <mergeCell ref="A528:F528"/>
-    <mergeCell ref="A826:F826"/>
-    <mergeCell ref="A974:F974"/>
-    <mergeCell ref="A405:F405"/>
-    <mergeCell ref="B1029:F1029"/>
+    <mergeCell ref="B344:F344"/>
+    <mergeCell ref="B222:F222"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B1058:F1058"/>
+    <mergeCell ref="B268:F268"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A351:F351"/>
+    <mergeCell ref="A587:F587"/>
+    <mergeCell ref="A239:F239"/>
     <mergeCell ref="A1241:F1241"/>
     <mergeCell ref="A371:F371"/>
     <mergeCell ref="A342:F342"/>
     <mergeCell ref="A656:F656"/>
     <mergeCell ref="A594:F594"/>
     <mergeCell ref="A892:F892"/>
+    <mergeCell ref="B966:F966"/>
+    <mergeCell ref="B512:F512"/>
+    <mergeCell ref="B1480:F1480"/>
+    <mergeCell ref="A465:F465"/>
+    <mergeCell ref="A763:F763"/>
+    <mergeCell ref="B1102:F1102"/>
+    <mergeCell ref="B1353:F1353"/>
+    <mergeCell ref="A1421:F1421"/>
+    <mergeCell ref="B1170:F1170"/>
+    <mergeCell ref="B1395:F1395"/>
+    <mergeCell ref="A651:F651"/>
+    <mergeCell ref="B548:F548"/>
+    <mergeCell ref="A462:F462"/>
+    <mergeCell ref="B855:F855"/>
+    <mergeCell ref="A355:F355"/>
+    <mergeCell ref="B694:F694"/>
+    <mergeCell ref="A933:F933"/>
+    <mergeCell ref="A899:F899"/>
     <mergeCell ref="A1473:F1473"/>
     <mergeCell ref="A994:F994"/>
     <mergeCell ref="A883:F883"/>
@@ -21906,7 +21900,6 @@
     <mergeCell ref="A815:F815"/>
     <mergeCell ref="B697:F697"/>
     <mergeCell ref="A1100:F1100"/>
-    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A576:F576"/>
     <mergeCell ref="A741:F741"/>
@@ -21930,7 +21923,7 @@
     <mergeCell ref="A696:F696"/>
     <mergeCell ref="B989:F989"/>
     <mergeCell ref="A686:F686"/>
-    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="A528:F528"/>
     <mergeCell ref="A1427:F1427"/>
     <mergeCell ref="A1025:F1025"/>
     <mergeCell ref="B1247:F1247"/>
@@ -21954,8 +21947,7 @@
     <mergeCell ref="B161:F161"/>
     <mergeCell ref="B962:F962"/>
     <mergeCell ref="B1028:F1028"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A1183:F1183"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1310:F1310"/>
     <mergeCell ref="B894:F894"/>
     <mergeCell ref="B6:F6"/>
@@ -21978,6 +21970,39 @@
     <mergeCell ref="A262:F262"/>
     <mergeCell ref="A1259:F1259"/>
     <mergeCell ref="A420:F420"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="A826:F826"/>
+    <mergeCell ref="A544:F544"/>
+    <mergeCell ref="A1117:F1117"/>
+    <mergeCell ref="A1180:F1180"/>
+    <mergeCell ref="A910:F910"/>
+    <mergeCell ref="B743:F743"/>
+    <mergeCell ref="B432:F432"/>
+    <mergeCell ref="A667:F667"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A1183:F1183"/>
+    <mergeCell ref="A974:F974"/>
+    <mergeCell ref="A405:F405"/>
+    <mergeCell ref="B1029:F1029"/>
+    <mergeCell ref="A223:F223"/>
+    <mergeCell ref="A294:F294"/>
+    <mergeCell ref="A331:F331"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="A226:F226"/>
+    <mergeCell ref="A241:F241"/>
+    <mergeCell ref="A221:F221"/>
+    <mergeCell ref="A699:F699"/>
+    <mergeCell ref="A965:F965"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A275:F275"/>
+    <mergeCell ref="A446:F446"/>
+    <mergeCell ref="B1425:F1425"/>
+    <mergeCell ref="A1349:F1349"/>
+    <mergeCell ref="B1457:F1457"/>
+    <mergeCell ref="B1249:F1249"/>
+    <mergeCell ref="B1314:F1314"/>
+    <mergeCell ref="A1320:F1320"/>
+    <mergeCell ref="A1424:F1424"/>
     <mergeCell ref="B238:F238"/>
     <mergeCell ref="B509:F509"/>
     <mergeCell ref="A748:F748"/>
@@ -21995,28 +22020,6 @@
     <mergeCell ref="A1063:F1063"/>
     <mergeCell ref="B349:F349"/>
     <mergeCell ref="A1134:F1134"/>
-    <mergeCell ref="A544:F544"/>
-    <mergeCell ref="A1117:F1117"/>
-    <mergeCell ref="A1460:F1460"/>
-    <mergeCell ref="A1180:F1180"/>
-    <mergeCell ref="A1451:F1451"/>
-    <mergeCell ref="A910:F910"/>
-    <mergeCell ref="B743:F743"/>
-    <mergeCell ref="B432:F432"/>
-    <mergeCell ref="A667:F667"/>
-    <mergeCell ref="B966:F966"/>
-    <mergeCell ref="B512:F512"/>
-    <mergeCell ref="A1278:F1278"/>
-    <mergeCell ref="A1400:F1400"/>
-    <mergeCell ref="B1392:F1392"/>
-    <mergeCell ref="A1355:F1355"/>
-    <mergeCell ref="B1425:F1425"/>
-    <mergeCell ref="A1349:F1349"/>
-    <mergeCell ref="B1457:F1457"/>
-    <mergeCell ref="B1249:F1249"/>
-    <mergeCell ref="B1314:F1314"/>
-    <mergeCell ref="A1320:F1320"/>
-    <mergeCell ref="A1424:F1424"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
